--- a/data/paddy_production_data.xlsx
+++ b/data/paddy_production_data.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\My Research Documents\Research Project\Forecastig_Paddy_Production\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC09BCA0-A6A6-4D5C-8B48-361A68634062}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50957DDE-4F9D-43F6-A754-76260CBA83EA}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{985DDFCC-FB2F-4E8D-9C1B-C306315BC8C0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="46">
   <si>
     <t>Year</t>
   </si>
@@ -210,6 +211,9 @@
       </rPr>
       <t>(HECTARES)</t>
     </r>
+  </si>
+  <si>
+    <t>OTHER--</t>
   </si>
 </sst>
 </file>
@@ -467,6 +471,11 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -481,6 +490,12 @@
     </xf>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -506,17 +521,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -869,37 +873,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="43.8" customHeight="1">
-      <c r="A1" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="47" t="s">
+      <c r="A1" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="48" t="s">
+      <c r="C1" s="53" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="45" t="s">
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="46" t="s">
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="L1" s="46"/>
-      <c r="M1" s="46"/>
-      <c r="N1" s="46"/>
-      <c r="O1" s="44" t="s">
+      <c r="L1" s="51"/>
+      <c r="M1" s="51"/>
+      <c r="N1" s="51"/>
+      <c r="O1" s="49" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="22.2" customHeight="1">
-      <c r="A2" s="47"/>
-      <c r="B2" s="47"/>
+      <c r="A2" s="52"/>
+      <c r="B2" s="52"/>
       <c r="C2" s="33" t="s">
         <v>4</v>
       </c>
@@ -936,7 +940,7 @@
       <c r="N2" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="44"/>
+      <c r="O2" s="49"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="18">
@@ -5373,7 +5377,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA13D30A-5641-4A6D-B73E-6F51D92E786F}">
-  <dimension ref="A1:AC69"/>
+  <dimension ref="A1:AB69"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="2" width="8.8984375" style="2"/>
@@ -5381,77 +5385,77 @@
     <col min="4" max="4" width="14.09765625" style="7" customWidth="1"/>
     <col min="5" max="5" width="11.69921875" style="7" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.59765625" style="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="9.59765625" style="7" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.69921875" style="6" customWidth="1"/>
-    <col min="11" max="12" width="11.69921875" style="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.59765625" style="7" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.69921875" style="13" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.69921875" style="9" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.8984375" style="9" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.59765625" style="9" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.796875" style="13" customWidth="1"/>
-    <col min="19" max="19" width="10.796875" style="14" customWidth="1"/>
-    <col min="20" max="21" width="11.3984375" style="9" customWidth="1"/>
-    <col min="22" max="22" width="11.69921875" style="6" bestFit="1" customWidth="1"/>
-    <col min="23" max="25" width="11.69921875" style="7" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="10.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="10" style="6" customWidth="1"/>
-    <col min="28" max="28" width="10.296875" style="7" customWidth="1"/>
-    <col min="29" max="29" width="13.19921875" style="7" customWidth="1"/>
+    <col min="7" max="7" width="9.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.59765625" style="7" customWidth="1"/>
+    <col min="9" max="9" width="10.69921875" style="6" customWidth="1"/>
+    <col min="10" max="11" width="11.69921875" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.69921875" style="13" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.69921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.8984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.59765625" style="9" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.796875" style="13" customWidth="1"/>
+    <col min="18" max="18" width="10.796875" style="14" customWidth="1"/>
+    <col min="19" max="20" width="11.3984375" style="9" customWidth="1"/>
+    <col min="21" max="21" width="11.69921875" style="6" bestFit="1" customWidth="1"/>
+    <col min="22" max="24" width="11.69921875" style="7" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="10.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10" style="6" customWidth="1"/>
+    <col min="27" max="27" width="10.296875" style="7" customWidth="1"/>
+    <col min="28" max="28" width="13.19921875" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="49" t="s">
+    <row r="1" spans="1:28" s="1" customFormat="1" ht="30" customHeight="1">
+      <c r="A1" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="49" t="s">
+      <c r="B1" s="56" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="51" t="s">
+      <c r="C1" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="51" t="s">
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="58" t="s">
         <v>15</v>
       </c>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="53"/>
-      <c r="N1" s="54" t="s">
+      <c r="J1" s="59"/>
+      <c r="K1" s="59"/>
+      <c r="L1" s="60"/>
+      <c r="M1" s="61" t="s">
         <v>40</v>
       </c>
-      <c r="O1" s="55"/>
-      <c r="P1" s="55"/>
-      <c r="Q1" s="56"/>
-      <c r="R1" s="54" t="s">
+      <c r="N1" s="62"/>
+      <c r="O1" s="62"/>
+      <c r="P1" s="63"/>
+      <c r="Q1" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="S1" s="56"/>
-      <c r="T1" s="54" t="s">
+      <c r="R1" s="63"/>
+      <c r="S1" s="61" t="s">
         <v>38</v>
       </c>
-      <c r="U1" s="56"/>
-      <c r="V1" s="51" t="s">
+      <c r="T1" s="63"/>
+      <c r="U1" s="58" t="s">
         <v>27</v>
       </c>
-      <c r="W1" s="52"/>
-      <c r="X1" s="52"/>
-      <c r="Y1" s="52"/>
-      <c r="Z1" s="53"/>
-      <c r="AA1" s="57" t="s">
+      <c r="V1" s="59"/>
+      <c r="W1" s="59"/>
+      <c r="X1" s="59"/>
+      <c r="Y1" s="60"/>
+      <c r="Z1" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="AB1" s="58"/>
-      <c r="AC1" s="58"/>
-    </row>
-    <row r="2" spans="1:29" s="1" customFormat="1" ht="66.599999999999994" customHeight="1">
-      <c r="A2" s="50"/>
-      <c r="B2" s="50"/>
+      <c r="AA1" s="55"/>
+      <c r="AB1" s="55"/>
+    </row>
+    <row r="2" spans="1:28" s="1" customFormat="1" ht="66.599999999999994" customHeight="1">
+      <c r="A2" s="57"/>
+      <c r="B2" s="57"/>
       <c r="C2" s="3" t="s">
         <v>10</v>
       </c>
@@ -5470,71 +5474,68 @@
       <c r="H2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="J2" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="J2" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="K2" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="M2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="N2" s="15" t="s">
+      <c r="M2" s="15" t="s">
         <v>20</v>
       </c>
+      <c r="N2" s="16" t="s">
+        <v>21</v>
+      </c>
       <c r="O2" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P2" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q2" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="R2" s="15" t="s">
+      <c r="Q2" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="S2" s="17" t="s">
+      <c r="R2" s="17" t="s">
         <v>26</v>
       </c>
+      <c r="S2" s="16" t="s">
+        <v>25</v>
+      </c>
       <c r="T2" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="U2" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="V2" s="3" t="s">
+      <c r="U2" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="V2" s="4" t="s">
+        <v>29</v>
+      </c>
       <c r="W2" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="Y2" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="Z2" s="5" t="s">
+      <c r="Y2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="AA2" s="3" t="s">
+      <c r="Z2" s="3" t="s">
         <v>35</v>
       </c>
+      <c r="AA2" s="4" t="s">
+        <v>36</v>
+      </c>
       <c r="AB2" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC2" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:29">
+    <row r="3" spans="1:28">
       <c r="A3" s="2">
         <v>1992</v>
       </c>
@@ -5557,46 +5558,46 @@
         <v>0</v>
       </c>
       <c r="H3" s="39">
-        <v>1.7807235968932567</v>
+        <v>1.8015742222115294</v>
       </c>
       <c r="I3" s="39">
-        <v>2.0850625318272767E-2</v>
+        <v>92.746101520888146</v>
       </c>
       <c r="J3" s="39">
-        <v>92.746101520888146</v>
+        <v>0.73477507540268239</v>
       </c>
       <c r="K3" s="39">
-        <v>0.73477507540268239</v>
+        <v>2.3122152345504716</v>
       </c>
       <c r="L3" s="39">
-        <v>2.3122152345504716</v>
+        <v>4.206908169158698</v>
       </c>
       <c r="M3" s="39">
-        <v>4.206908169158698</v>
+        <v>26.450487305980026</v>
       </c>
       <c r="N3" s="39">
-        <v>26.450487305980026</v>
+        <v>56.689527934865438</v>
       </c>
       <c r="O3" s="39">
-        <v>56.689527934865438</v>
+        <v>2.1180764448722575</v>
       </c>
       <c r="P3" s="39">
-        <v>2.1180764448722575</v>
-      </c>
-      <c r="Q3" s="39">
         <v>14.741908314282275</v>
       </c>
-      <c r="R3" s="42">
+      <c r="Q3" s="42">
         <v>67.828852640487071</v>
       </c>
-      <c r="S3" s="43">
+      <c r="R3" s="43">
         <v>32.171147359512929</v>
       </c>
+      <c r="S3" s="39">
+        <v>24.103092700808972</v>
+      </c>
       <c r="T3" s="39">
-        <v>24.103092700808972</v>
+        <v>75.896907299191028</v>
       </c>
       <c r="U3" s="39">
-        <v>75.896907299191028</v>
+        <v>0</v>
       </c>
       <c r="V3" s="39">
         <v>0</v>
@@ -5610,20 +5611,17 @@
       <c r="Y3" s="39">
         <v>0</v>
       </c>
-      <c r="Z3" s="39">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="40">
+      <c r="Z3" s="40">
         <v>90.549911563343514</v>
       </c>
+      <c r="AA3" s="41">
+        <v>0.80575620360083589</v>
+      </c>
       <c r="AB3" s="41">
-        <v>0.80575620360083589</v>
-      </c>
-      <c r="AC3" s="41">
         <v>8.6443322330556569</v>
       </c>
     </row>
-    <row r="4" spans="1:29">
+    <row r="4" spans="1:28">
       <c r="A4" s="2">
         <v>1993</v>
       </c>
@@ -5646,46 +5644,46 @@
         <v>0</v>
       </c>
       <c r="H4" s="39">
-        <v>0.17779541881564306</v>
+        <v>0.5392088923952274</v>
       </c>
       <c r="I4" s="39">
-        <v>0.36141347357958437</v>
+        <v>91.702927115995323</v>
       </c>
       <c r="J4" s="39">
-        <v>91.702927115995323</v>
+        <v>1.3109932855477786</v>
       </c>
       <c r="K4" s="39">
-        <v>1.3109932855477786</v>
+        <v>2.1310913041123261</v>
       </c>
       <c r="L4" s="39">
-        <v>2.1310913041123261</v>
+        <v>4.8549882943445732</v>
       </c>
       <c r="M4" s="39">
-        <v>4.8549882943445732</v>
+        <v>25.036420103897349</v>
       </c>
       <c r="N4" s="39">
-        <v>25.036420103897349</v>
+        <v>60.673091546533684</v>
       </c>
       <c r="O4" s="39">
-        <v>60.673091546533684</v>
+        <v>2.4143327116568343</v>
       </c>
       <c r="P4" s="39">
-        <v>2.4143327116568343</v>
-      </c>
-      <c r="Q4" s="39">
         <v>11.876155637912127</v>
       </c>
-      <c r="R4" s="42">
+      <c r="Q4" s="42">
         <v>72.797751681220518</v>
       </c>
-      <c r="S4" s="43">
+      <c r="R4" s="43">
         <v>27.202248318779482</v>
       </c>
+      <c r="S4" s="39">
+        <v>24.317677247059962</v>
+      </c>
       <c r="T4" s="39">
-        <v>24.317677247059962</v>
+        <v>75.682322752940053</v>
       </c>
       <c r="U4" s="39">
-        <v>75.682322752940053</v>
+        <v>0</v>
       </c>
       <c r="V4" s="39">
         <v>0</v>
@@ -5699,20 +5697,17 @@
       <c r="Y4" s="39">
         <v>0</v>
       </c>
-      <c r="Z4" s="39">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="40">
+      <c r="Z4" s="40">
         <v>89.891208621460976</v>
       </c>
+      <c r="AA4" s="41">
+        <v>1.4261440347297869</v>
+      </c>
       <c r="AB4" s="41">
-        <v>1.4261440347297869</v>
-      </c>
-      <c r="AC4" s="41">
         <v>8.6826473438092417</v>
       </c>
     </row>
-    <row r="5" spans="1:29">
+    <row r="5" spans="1:28">
       <c r="A5" s="2">
         <v>1993</v>
       </c>
@@ -5735,46 +5730,46 @@
         <v>0</v>
       </c>
       <c r="H5" s="39">
-        <v>0.62187709545543035</v>
+        <v>0.73976336224611194</v>
       </c>
       <c r="I5" s="39">
-        <v>0.11788626679068157</v>
+        <v>91.488755741097236</v>
       </c>
       <c r="J5" s="39">
-        <v>91.488755741097236</v>
+        <v>0.3727657488121246</v>
       </c>
       <c r="K5" s="39">
-        <v>0.3727657488121246</v>
+        <v>3.8715003641135457</v>
       </c>
       <c r="L5" s="39">
-        <v>3.8715003641135457</v>
+        <v>4.2669781459770864</v>
       </c>
       <c r="M5" s="39">
-        <v>4.2669781459770864</v>
+        <v>22.049656972489302</v>
       </c>
       <c r="N5" s="39">
-        <v>22.049656972489302</v>
+        <v>62.599726731630987</v>
       </c>
       <c r="O5" s="39">
-        <v>62.599726731630987</v>
+        <v>2.2593309611620036</v>
       </c>
       <c r="P5" s="39">
-        <v>2.2593309611620036</v>
-      </c>
-      <c r="Q5" s="39">
         <v>13.0912853347177</v>
       </c>
-      <c r="R5" s="42">
+      <c r="Q5" s="42">
         <v>69.629795195881556</v>
       </c>
-      <c r="S5" s="43">
+      <c r="R5" s="43">
         <v>30.370204804118433</v>
       </c>
+      <c r="S5" s="39">
+        <v>18.266537364764751</v>
+      </c>
       <c r="T5" s="39">
-        <v>18.266537364764751</v>
+        <v>81.733462635235256</v>
       </c>
       <c r="U5" s="39">
-        <v>81.733462635235256</v>
+        <v>0</v>
       </c>
       <c r="V5" s="39">
         <v>0</v>
@@ -5788,20 +5783,17 @@
       <c r="Y5" s="39">
         <v>0</v>
       </c>
-      <c r="Z5" s="39">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="40">
+      <c r="Z5" s="40">
         <v>90.248606634797724</v>
       </c>
+      <c r="AA5" s="41">
+        <v>1.1222628395088432</v>
+      </c>
       <c r="AB5" s="41">
-        <v>1.1222628395088432</v>
-      </c>
-      <c r="AC5" s="41">
         <v>8.6291305256934372</v>
       </c>
     </row>
-    <row r="6" spans="1:29">
+    <row r="6" spans="1:28">
       <c r="A6" s="2">
         <v>1994</v>
       </c>
@@ -5824,46 +5816,46 @@
         <v>0</v>
       </c>
       <c r="H6" s="39">
-        <v>0.66048161665691552</v>
+        <v>0.95673251051737118</v>
       </c>
       <c r="I6" s="39">
-        <v>0.29625089386045561</v>
+        <v>90.139767271241382</v>
       </c>
       <c r="J6" s="39">
-        <v>90.139767271241382</v>
+        <v>0.79216931806573243</v>
       </c>
       <c r="K6" s="39">
-        <v>0.79216931806573243</v>
+        <v>3.5890006407934694</v>
       </c>
       <c r="L6" s="39">
-        <v>3.5890006407934694</v>
+        <v>5.4790627698994232</v>
       </c>
       <c r="M6" s="39">
-        <v>5.4790627698994232</v>
+        <v>22.771799091371747</v>
       </c>
       <c r="N6" s="39">
-        <v>22.771799091371747</v>
+        <v>62.620125781490877</v>
       </c>
       <c r="O6" s="39">
-        <v>62.620125781490877</v>
+        <v>2.5659647024298189</v>
       </c>
       <c r="P6" s="39">
-        <v>2.5659647024298189</v>
-      </c>
-      <c r="Q6" s="39">
         <v>12.042110424707555</v>
       </c>
-      <c r="R6" s="42">
+      <c r="Q6" s="42">
         <v>70.40834331670986</v>
       </c>
-      <c r="S6" s="43">
+      <c r="R6" s="43">
         <v>29.59165668329015</v>
       </c>
+      <c r="S6" s="39">
+        <v>23.461399158610313</v>
+      </c>
       <c r="T6" s="39">
-        <v>23.461399158610313</v>
+        <v>76.53860084138968</v>
       </c>
       <c r="U6" s="39">
-        <v>76.53860084138968</v>
+        <v>0</v>
       </c>
       <c r="V6" s="39">
         <v>0</v>
@@ -5877,20 +5869,17 @@
       <c r="Y6" s="39">
         <v>0</v>
       </c>
-      <c r="Z6" s="39">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="40">
+      <c r="Z6" s="40">
         <v>87.389718310382364</v>
       </c>
+      <c r="AA6" s="41">
+        <v>3.4437605173906101</v>
+      </c>
       <c r="AB6" s="41">
-        <v>3.4437605173906101</v>
-      </c>
-      <c r="AC6" s="41">
         <v>9.1665211722270303</v>
       </c>
     </row>
-    <row r="7" spans="1:29">
+    <row r="7" spans="1:28">
       <c r="A7" s="2">
         <v>1994</v>
       </c>
@@ -5913,46 +5902,46 @@
         <v>0</v>
       </c>
       <c r="H7" s="39">
-        <v>0</v>
+        <v>0.11158638646085177</v>
       </c>
       <c r="I7" s="39">
-        <v>0.11158638646085177</v>
+        <v>91.499637044280604</v>
       </c>
       <c r="J7" s="39">
-        <v>91.499637044280604</v>
+        <v>0.84769658101711587</v>
       </c>
       <c r="K7" s="39">
-        <v>0.84769658101711587</v>
+        <v>3.863828612909225</v>
       </c>
       <c r="L7" s="39">
-        <v>3.863828612909225</v>
+        <v>3.7888377617930611</v>
       </c>
       <c r="M7" s="39">
-        <v>3.7888377617930611</v>
+        <v>25.907539280207814</v>
       </c>
       <c r="N7" s="39">
-        <v>25.907539280207814</v>
+        <v>61.101045672427965</v>
       </c>
       <c r="O7" s="39">
-        <v>61.101045672427965</v>
+        <v>2.7956589296105876</v>
       </c>
       <c r="P7" s="39">
-        <v>2.7956589296105876</v>
-      </c>
-      <c r="Q7" s="39">
         <v>10.195756117753634</v>
       </c>
-      <c r="R7" s="42">
+      <c r="Q7" s="42">
         <v>74.091483113509497</v>
       </c>
-      <c r="S7" s="43">
+      <c r="R7" s="43">
         <v>25.908516886490506</v>
       </c>
+      <c r="S7" s="39">
+        <v>19.805083779778869</v>
+      </c>
       <c r="T7" s="39">
-        <v>19.805083779778869</v>
+        <v>80.194916220221131</v>
       </c>
       <c r="U7" s="39">
-        <v>80.194916220221131</v>
+        <v>0</v>
       </c>
       <c r="V7" s="39">
         <v>0</v>
@@ -5966,20 +5955,17 @@
       <c r="Y7" s="39">
         <v>0</v>
       </c>
-      <c r="Z7" s="39">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="40">
+      <c r="Z7" s="40">
         <v>92.783180451984862</v>
       </c>
+      <c r="AA7" s="41">
+        <v>1.2826435174908661</v>
+      </c>
       <c r="AB7" s="41">
-        <v>1.2826435174908661</v>
-      </c>
-      <c r="AC7" s="41">
         <v>5.9341760305242763</v>
       </c>
     </row>
-    <row r="8" spans="1:29">
+    <row r="8" spans="1:28">
       <c r="A8" s="2">
         <v>1995</v>
       </c>
@@ -6002,46 +5988,46 @@
         <v>0</v>
       </c>
       <c r="H8" s="39">
-        <v>0</v>
+        <v>0.13166779203241052</v>
       </c>
       <c r="I8" s="39">
-        <v>0.13166779203241052</v>
+        <v>93.223622883144117</v>
       </c>
       <c r="J8" s="39">
-        <v>93.223622883144117</v>
+        <v>0.64839701328491761</v>
       </c>
       <c r="K8" s="39">
-        <v>0.64839701328491761</v>
+        <v>3.5191996413841222</v>
       </c>
       <c r="L8" s="39">
-        <v>3.5191996413841222</v>
+        <v>2.6087804621868442</v>
       </c>
       <c r="M8" s="39">
-        <v>2.6087804621868442</v>
+        <v>26.51159213973963</v>
       </c>
       <c r="N8" s="39">
-        <v>26.51159213973963</v>
+        <v>62.549539259100875</v>
       </c>
       <c r="O8" s="39">
-        <v>62.549539259100875</v>
+        <v>1.4873500224134082</v>
       </c>
       <c r="P8" s="39">
-        <v>1.4873500224134082</v>
-      </c>
-      <c r="Q8" s="39">
         <v>9.4515185787460876</v>
       </c>
-      <c r="R8" s="42">
+      <c r="Q8" s="42">
         <v>75.340191876658764</v>
       </c>
-      <c r="S8" s="43">
+      <c r="R8" s="43">
         <v>24.659808123341243</v>
       </c>
+      <c r="S8" s="39">
+        <v>27.043801028207238</v>
+      </c>
       <c r="T8" s="39">
-        <v>27.043801028207238</v>
+        <v>72.956198971792759</v>
       </c>
       <c r="U8" s="39">
-        <v>72.956198971792759</v>
+        <v>0</v>
       </c>
       <c r="V8" s="39">
         <v>0</v>
@@ -6055,20 +6041,17 @@
       <c r="Y8" s="39">
         <v>0</v>
       </c>
-      <c r="Z8" s="39">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="40">
+      <c r="Z8" s="40">
         <v>94.038209774890177</v>
       </c>
+      <c r="AA8" s="41">
+        <v>2.6719833746591091</v>
+      </c>
       <c r="AB8" s="41">
-        <v>2.6719833746591091</v>
-      </c>
-      <c r="AC8" s="41">
         <v>3.2898068504507072</v>
       </c>
     </row>
-    <row r="9" spans="1:29">
+    <row r="9" spans="1:28">
       <c r="A9" s="2">
         <v>1995</v>
       </c>
@@ -6091,46 +6074,46 @@
         <v>0</v>
       </c>
       <c r="H9" s="39">
-        <v>0</v>
+        <v>0.11504483721155535</v>
       </c>
       <c r="I9" s="39">
-        <v>0.11504483721155535</v>
+        <v>92.147584361168128</v>
       </c>
       <c r="J9" s="39">
-        <v>92.147584361168128</v>
+        <v>0.84406580564688505</v>
       </c>
       <c r="K9" s="39">
-        <v>0.84406580564688505</v>
+        <v>3.9511846590737072</v>
       </c>
       <c r="L9" s="39">
-        <v>3.9511846590737072</v>
+        <v>3.0571651741112786</v>
       </c>
       <c r="M9" s="39">
-        <v>3.0571651741112786</v>
+        <v>23.653218530695781</v>
       </c>
       <c r="N9" s="39">
-        <v>23.653218530695781</v>
+        <v>62.491144575030418</v>
       </c>
       <c r="O9" s="39">
-        <v>62.491144575030418</v>
+        <v>1.932147766010911</v>
       </c>
       <c r="P9" s="39">
-        <v>1.932147766010911</v>
-      </c>
-      <c r="Q9" s="39">
         <v>11.923489128262883</v>
       </c>
-      <c r="R9" s="42">
+      <c r="Q9" s="42">
         <v>76.706447960376138</v>
       </c>
-      <c r="S9" s="43">
+      <c r="R9" s="43">
         <v>23.293552039623862</v>
       </c>
+      <c r="S9" s="39">
+        <v>25.393423068306358</v>
+      </c>
       <c r="T9" s="39">
-        <v>25.393423068306358</v>
+        <v>74.606576931693652</v>
       </c>
       <c r="U9" s="39">
-        <v>74.606576931693652</v>
+        <v>0</v>
       </c>
       <c r="V9" s="39">
         <v>0</v>
@@ -6144,20 +6127,17 @@
       <c r="Y9" s="39">
         <v>0</v>
       </c>
-      <c r="Z9" s="39">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="40">
+      <c r="Z9" s="40">
         <v>97.555902708397667</v>
       </c>
+      <c r="AA9" s="41">
+        <v>0.98000036329948592</v>
+      </c>
       <c r="AB9" s="41">
-        <v>0.98000036329948592</v>
-      </c>
-      <c r="AC9" s="41">
         <v>1.4640969283028464</v>
       </c>
     </row>
-    <row r="10" spans="1:29">
+    <row r="10" spans="1:28">
       <c r="A10" s="2">
         <v>1996</v>
       </c>
@@ -6180,46 +6160,46 @@
         <v>0</v>
       </c>
       <c r="H10" s="39">
-        <v>0</v>
+        <v>0.14585726640248861</v>
       </c>
       <c r="I10" s="39">
-        <v>0.14585726640248861</v>
+        <v>92.704340006625969</v>
       </c>
       <c r="J10" s="39">
-        <v>92.704340006625969</v>
+        <v>0.89837749925780597</v>
       </c>
       <c r="K10" s="39">
-        <v>0.89837749925780597</v>
+        <v>3.5980276999728935</v>
       </c>
       <c r="L10" s="39">
-        <v>3.5980276999728935</v>
+        <v>2.7992547941433359</v>
       </c>
       <c r="M10" s="39">
-        <v>2.7992547941433359</v>
+        <v>24.929975604404113</v>
       </c>
       <c r="N10" s="39">
-        <v>24.929975604404113</v>
+        <v>62.97269156136116</v>
       </c>
       <c r="O10" s="39">
-        <v>62.97269156136116</v>
+        <v>1.4032845851673055</v>
       </c>
       <c r="P10" s="39">
-        <v>1.4032845851673055</v>
-      </c>
-      <c r="Q10" s="39">
         <v>10.694048249067418</v>
       </c>
-      <c r="R10" s="42">
+      <c r="Q10" s="42">
         <v>65.672341762076243</v>
       </c>
-      <c r="S10" s="43">
+      <c r="R10" s="43">
         <v>34.32765823792375</v>
       </c>
+      <c r="S10" s="39">
+        <v>19.967816744758387</v>
+      </c>
       <c r="T10" s="39">
-        <v>19.967816744758387</v>
+        <v>80.032183255241605</v>
       </c>
       <c r="U10" s="39">
-        <v>80.032183255241605</v>
+        <v>0</v>
       </c>
       <c r="V10" s="39">
         <v>0</v>
@@ -6233,20 +6213,17 @@
       <c r="Y10" s="39">
         <v>0</v>
       </c>
-      <c r="Z10" s="39">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="40">
+      <c r="Z10" s="40">
         <v>97.258829957963854</v>
       </c>
+      <c r="AA10" s="41">
+        <v>1.3243323480438347</v>
+      </c>
       <c r="AB10" s="41">
-        <v>1.3243323480438347</v>
-      </c>
-      <c r="AC10" s="41">
         <v>1.4168376939923157</v>
       </c>
     </row>
-    <row r="11" spans="1:29">
+    <row r="11" spans="1:28">
       <c r="A11" s="2">
         <v>1996</v>
       </c>
@@ -6269,46 +6246,46 @@
         <v>0</v>
       </c>
       <c r="H11" s="39">
-        <v>0</v>
+        <v>0.13602031675063489</v>
       </c>
       <c r="I11" s="39">
-        <v>0.13602031675063489</v>
+        <v>94.687810771494085</v>
       </c>
       <c r="J11" s="39">
-        <v>94.687810771494085</v>
+        <v>0.39860938745654334</v>
       </c>
       <c r="K11" s="39">
-        <v>0.39860938745654334</v>
+        <v>3.9865048120782753</v>
       </c>
       <c r="L11" s="39">
-        <v>3.9865048120782753</v>
+        <v>0.92707502897109473</v>
       </c>
       <c r="M11" s="39">
-        <v>0.92707502897109473</v>
+        <v>27.245157101411159</v>
       </c>
       <c r="N11" s="39">
-        <v>27.245157101411159</v>
+        <v>58.454217451694291</v>
       </c>
       <c r="O11" s="39">
-        <v>58.454217451694291</v>
+        <v>1.9983891249496601</v>
       </c>
       <c r="P11" s="39">
-        <v>1.9983891249496601</v>
-      </c>
-      <c r="Q11" s="39">
         <v>12.302236321944884</v>
       </c>
-      <c r="R11" s="42">
+      <c r="Q11" s="42">
         <v>66.298603634331371</v>
       </c>
-      <c r="S11" s="43">
+      <c r="R11" s="43">
         <v>33.701396365668636</v>
       </c>
+      <c r="S11" s="39">
+        <v>21.426692857084152</v>
+      </c>
       <c r="T11" s="39">
-        <v>21.426692857084152</v>
+        <v>78.573307142915851</v>
       </c>
       <c r="U11" s="39">
-        <v>78.573307142915851</v>
+        <v>0</v>
       </c>
       <c r="V11" s="39">
         <v>0</v>
@@ -6322,20 +6299,17 @@
       <c r="Y11" s="39">
         <v>0</v>
       </c>
-      <c r="Z11" s="39">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="40">
+      <c r="Z11" s="40">
         <v>97.783813993244181</v>
       </c>
+      <c r="AA11" s="41">
+        <v>0.95625159238286217</v>
+      </c>
       <c r="AB11" s="41">
-        <v>0.95625159238286217</v>
-      </c>
-      <c r="AC11" s="41">
         <v>1.2599344143729505</v>
       </c>
     </row>
-    <row r="12" spans="1:29">
+    <row r="12" spans="1:28">
       <c r="A12" s="2">
         <v>1997</v>
       </c>
@@ -6358,46 +6332,46 @@
         <v>0</v>
       </c>
       <c r="H12" s="39">
-        <v>0</v>
+        <v>0.11073760063888864</v>
       </c>
       <c r="I12" s="39">
-        <v>0.11073760063888864</v>
+        <v>95.137539495158435</v>
       </c>
       <c r="J12" s="39">
-        <v>95.137539495158435</v>
+        <v>0.29228158393867426</v>
       </c>
       <c r="K12" s="39">
-        <v>0.29228158393867426</v>
+        <v>3.5456843776770235</v>
       </c>
       <c r="L12" s="39">
-        <v>3.5456843776770235</v>
+        <v>1.0244945432258694</v>
       </c>
       <c r="M12" s="39">
-        <v>1.0244945432258694</v>
+        <v>25.767674446139168</v>
       </c>
       <c r="N12" s="39">
-        <v>25.767674446139168</v>
+        <v>63.103802910743845</v>
       </c>
       <c r="O12" s="39">
-        <v>63.103802910743845</v>
+        <v>1.8309967057381442</v>
       </c>
       <c r="P12" s="39">
-        <v>1.8309967057381442</v>
-      </c>
-      <c r="Q12" s="39">
         <v>9.297525937378845</v>
       </c>
-      <c r="R12" s="42">
+      <c r="Q12" s="42">
         <v>65.896844798246775</v>
       </c>
-      <c r="S12" s="43">
+      <c r="R12" s="43">
         <v>34.103155201753225</v>
       </c>
+      <c r="S12" s="39">
+        <v>21.323787170718912</v>
+      </c>
       <c r="T12" s="39">
-        <v>21.323787170718912</v>
+        <v>78.676212829281084</v>
       </c>
       <c r="U12" s="39">
-        <v>78.676212829281084</v>
+        <v>0</v>
       </c>
       <c r="V12" s="39">
         <v>0</v>
@@ -6411,20 +6385,17 @@
       <c r="Y12" s="39">
         <v>0</v>
       </c>
-      <c r="Z12" s="39">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="40">
+      <c r="Z12" s="40">
         <v>97.143812289755743</v>
       </c>
+      <c r="AA12" s="41">
+        <v>1.1675012594341485</v>
+      </c>
       <c r="AB12" s="41">
-        <v>1.1675012594341485</v>
-      </c>
-      <c r="AC12" s="41">
         <v>1.6886864508101007</v>
       </c>
     </row>
-    <row r="13" spans="1:29">
+    <row r="13" spans="1:28">
       <c r="A13" s="2">
         <v>1997</v>
       </c>
@@ -6447,46 +6418,46 @@
         <v>0</v>
       </c>
       <c r="H13" s="39">
-        <v>0</v>
+        <v>0.12686663649880406</v>
       </c>
       <c r="I13" s="39">
-        <v>0.12686663649880406</v>
+        <v>92.31443659268777</v>
       </c>
       <c r="J13" s="39">
-        <v>92.31443659268777</v>
+        <v>0.96604889637701363</v>
       </c>
       <c r="K13" s="39">
-        <v>0.96604889637701363</v>
+        <v>4.921960541892421</v>
       </c>
       <c r="L13" s="39">
-        <v>4.921960541892421</v>
+        <v>1.7975539690427995</v>
       </c>
       <c r="M13" s="39">
-        <v>1.7975539690427995</v>
+        <v>27.212599443239071</v>
       </c>
       <c r="N13" s="39">
-        <v>27.212599443239071</v>
+        <v>61.00370500559589</v>
       </c>
       <c r="O13" s="39">
-        <v>61.00370500559589</v>
+        <v>1.9688650238582968</v>
       </c>
       <c r="P13" s="39">
-        <v>1.9688650238582968</v>
-      </c>
-      <c r="Q13" s="39">
         <v>9.8148305273067393</v>
       </c>
-      <c r="R13" s="42">
+      <c r="Q13" s="42">
         <v>63.196554399120821</v>
       </c>
-      <c r="S13" s="43">
+      <c r="R13" s="43">
         <v>36.803445600879172</v>
       </c>
+      <c r="S13" s="39">
+        <v>20.590374296981061</v>
+      </c>
       <c r="T13" s="39">
-        <v>20.590374296981061</v>
+        <v>79.409625703018932</v>
       </c>
       <c r="U13" s="39">
-        <v>79.409625703018932</v>
+        <v>0</v>
       </c>
       <c r="V13" s="39">
         <v>0</v>
@@ -6500,20 +6471,17 @@
       <c r="Y13" s="39">
         <v>0</v>
       </c>
-      <c r="Z13" s="39">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="40">
+      <c r="Z13" s="40">
         <v>98.446887512474603</v>
       </c>
+      <c r="AA13" s="41">
+        <v>0.98382645866918783</v>
+      </c>
       <c r="AB13" s="41">
-        <v>0.98382645866918783</v>
-      </c>
-      <c r="AC13" s="41">
         <v>0.56928602885621582</v>
       </c>
     </row>
-    <row r="14" spans="1:29">
+    <row r="14" spans="1:28">
       <c r="A14" s="2">
         <v>1998</v>
       </c>
@@ -6536,46 +6504,46 @@
         <v>0</v>
       </c>
       <c r="H14" s="39">
-        <v>0</v>
+        <v>0.3581699444302982</v>
       </c>
       <c r="I14" s="39">
-        <v>0.3581699444302982</v>
+        <v>91.470881203097619</v>
       </c>
       <c r="J14" s="39">
-        <v>91.470881203097619</v>
+        <v>0.53212204730306611</v>
       </c>
       <c r="K14" s="39">
-        <v>0.53212204730306611</v>
+        <v>6.997535986578991</v>
       </c>
       <c r="L14" s="39">
-        <v>6.997535986578991</v>
+        <v>0.99946076302032616</v>
       </c>
       <c r="M14" s="39">
-        <v>0.99946076302032616</v>
+        <v>25.503148363468874</v>
       </c>
       <c r="N14" s="39">
-        <v>25.503148363468874</v>
+        <v>65.988874471762088</v>
       </c>
       <c r="O14" s="39">
-        <v>65.988874471762088</v>
+        <v>1.8086940891652483</v>
       </c>
       <c r="P14" s="39">
-        <v>1.8086940891652483</v>
-      </c>
-      <c r="Q14" s="39">
         <v>6.6992830756037876</v>
       </c>
-      <c r="R14" s="42">
+      <c r="Q14" s="42">
         <v>77.367400128817721</v>
       </c>
-      <c r="S14" s="43">
+      <c r="R14" s="43">
         <v>22.632599871182276</v>
       </c>
+      <c r="S14" s="39">
+        <v>28.771288626593371</v>
+      </c>
       <c r="T14" s="39">
-        <v>28.771288626593371</v>
+        <v>71.228711373406625</v>
       </c>
       <c r="U14" s="39">
-        <v>71.228711373406625</v>
+        <v>0</v>
       </c>
       <c r="V14" s="39">
         <v>0</v>
@@ -6589,20 +6557,17 @@
       <c r="Y14" s="39">
         <v>0</v>
       </c>
-      <c r="Z14" s="39">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="40">
+      <c r="Z14" s="40">
         <v>98.874717275055801</v>
       </c>
+      <c r="AA14" s="41">
+        <v>0.67030152334446758</v>
+      </c>
       <c r="AB14" s="41">
-        <v>0.67030152334446758</v>
-      </c>
-      <c r="AC14" s="41">
         <v>0.45498120159973632</v>
       </c>
     </row>
-    <row r="15" spans="1:29">
+    <row r="15" spans="1:28">
       <c r="A15" s="2">
         <v>1998</v>
       </c>
@@ -6625,46 +6590,46 @@
         <v>0</v>
       </c>
       <c r="H15" s="39">
-        <v>0</v>
+        <v>0.46466213582491039</v>
       </c>
       <c r="I15" s="39">
-        <v>0.46466213582491039</v>
+        <v>93.816597391871497</v>
       </c>
       <c r="J15" s="39">
-        <v>93.816597391871497</v>
+        <v>0.5541983613327004</v>
       </c>
       <c r="K15" s="39">
-        <v>0.5541983613327004</v>
+        <v>4.5439634445203447</v>
       </c>
       <c r="L15" s="39">
-        <v>4.5439634445203447</v>
+        <v>1.0852408022754552</v>
       </c>
       <c r="M15" s="39">
-        <v>1.0852408022754552</v>
+        <v>28.64348759035633</v>
       </c>
       <c r="N15" s="39">
-        <v>28.64348759035633</v>
+        <v>62.444956447573063</v>
       </c>
       <c r="O15" s="39">
-        <v>62.444956447573063</v>
+        <v>2.7397313141370754</v>
       </c>
       <c r="P15" s="39">
-        <v>2.7397313141370754</v>
-      </c>
-      <c r="Q15" s="39">
         <v>6.1718246479335273</v>
       </c>
-      <c r="R15" s="42">
+      <c r="Q15" s="42">
         <v>72.525886389335923</v>
       </c>
-      <c r="S15" s="43">
+      <c r="R15" s="43">
         <v>27.474113610664077</v>
       </c>
+      <c r="S15" s="39">
+        <v>27.390366365253772</v>
+      </c>
       <c r="T15" s="39">
-        <v>27.390366365253772</v>
+        <v>72.609633634746231</v>
       </c>
       <c r="U15" s="39">
-        <v>72.609633634746231</v>
+        <v>0</v>
       </c>
       <c r="V15" s="39">
         <v>0</v>
@@ -6678,20 +6643,17 @@
       <c r="Y15" s="39">
         <v>0</v>
       </c>
-      <c r="Z15" s="39">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="40">
+      <c r="Z15" s="40">
         <v>98.869892896579941</v>
       </c>
+      <c r="AA15" s="41">
+        <v>0.78725260808796849</v>
+      </c>
       <c r="AB15" s="41">
-        <v>0.78725260808796849</v>
-      </c>
-      <c r="AC15" s="41">
         <v>0.34285449533208234</v>
       </c>
     </row>
-    <row r="16" spans="1:29">
+    <row r="16" spans="1:28">
       <c r="A16" s="2">
         <v>1999</v>
       </c>
@@ -6714,46 +6676,46 @@
         <v>0</v>
       </c>
       <c r="H16" s="39">
-        <v>0</v>
+        <v>0.23333522115874722</v>
       </c>
       <c r="I16" s="39">
-        <v>0.23333522115874722</v>
+        <v>89.569933680568013</v>
       </c>
       <c r="J16" s="39">
-        <v>89.569933680568013</v>
+        <v>0.98903360146797592</v>
       </c>
       <c r="K16" s="39">
-        <v>0.98903360146797592</v>
+        <v>7.7601097961333494</v>
       </c>
       <c r="L16" s="39">
-        <v>7.7601097961333494</v>
+        <v>1.6809229218306656</v>
       </c>
       <c r="M16" s="39">
-        <v>1.6809229218306656</v>
+        <v>25.899076853372598</v>
       </c>
       <c r="N16" s="39">
-        <v>25.899076853372598</v>
+        <v>65.961941439655661</v>
       </c>
       <c r="O16" s="39">
-        <v>65.961941439655661</v>
+        <v>2.026958146910574</v>
       </c>
       <c r="P16" s="39">
-        <v>2.026958146910574</v>
-      </c>
-      <c r="Q16" s="39">
         <v>6.1120235600611652</v>
       </c>
-      <c r="R16" s="42">
+      <c r="Q16" s="42">
         <v>71.353382039229004</v>
       </c>
-      <c r="S16" s="43">
+      <c r="R16" s="43">
         <v>28.646617960770985</v>
       </c>
+      <c r="S16" s="39">
+        <v>30.93158344833315</v>
+      </c>
       <c r="T16" s="39">
-        <v>30.93158344833315</v>
+        <v>69.068416551666857</v>
       </c>
       <c r="U16" s="39">
-        <v>69.068416551666857</v>
+        <v>0</v>
       </c>
       <c r="V16" s="39">
         <v>0</v>
@@ -6767,20 +6729,17 @@
       <c r="Y16" s="39">
         <v>0</v>
       </c>
-      <c r="Z16" s="39">
-        <v>0</v>
-      </c>
-      <c r="AA16" s="40">
+      <c r="Z16" s="40">
         <v>96.538294538521072</v>
       </c>
+      <c r="AA16" s="41">
+        <v>2.3882879311321288</v>
+      </c>
       <c r="AB16" s="41">
-        <v>2.3882879311321288</v>
-      </c>
-      <c r="AC16" s="41">
         <v>1.0734175303467934</v>
       </c>
     </row>
-    <row r="17" spans="1:29" s="12" customFormat="1">
+    <row r="17" spans="1:28" s="12" customFormat="1">
       <c r="A17" s="11">
         <v>1999</v>
       </c>
@@ -6803,46 +6762,46 @@
         <v>0</v>
       </c>
       <c r="H17" s="39">
-        <v>0</v>
+        <v>0.14339508259789921</v>
       </c>
       <c r="I17" s="39">
-        <v>0.14339508259789921</v>
+        <v>90.534731148009215</v>
       </c>
       <c r="J17" s="39">
-        <v>90.534731148009215</v>
+        <v>0.69307825255678257</v>
       </c>
       <c r="K17" s="39">
-        <v>0.69307825255678257</v>
+        <v>5.9835561501222649</v>
       </c>
       <c r="L17" s="39">
-        <v>5.9835561501222649</v>
+        <v>2.788634449311731</v>
       </c>
       <c r="M17" s="39">
-        <v>2.788634449311731</v>
+        <v>23.294414586660761</v>
       </c>
       <c r="N17" s="39">
-        <v>23.294414586660761</v>
+        <v>68.833137088030597</v>
       </c>
       <c r="O17" s="39">
-        <v>68.833137088030597</v>
+        <v>1.7338563950709398</v>
       </c>
       <c r="P17" s="39">
-        <v>1.7338563950709398</v>
-      </c>
-      <c r="Q17" s="39">
         <v>6.138591930237709</v>
       </c>
-      <c r="R17" s="42">
+      <c r="Q17" s="42">
         <v>68.279283139079055</v>
       </c>
-      <c r="S17" s="43">
+      <c r="R17" s="43">
         <v>31.720716860920938</v>
       </c>
+      <c r="S17" s="39">
+        <v>29.80761103679027</v>
+      </c>
       <c r="T17" s="39">
-        <v>29.80761103679027</v>
+        <v>70.192388963209723</v>
       </c>
       <c r="U17" s="39">
-        <v>70.192388963209723</v>
+        <v>0</v>
       </c>
       <c r="V17" s="39">
         <v>0</v>
@@ -6856,20 +6815,17 @@
       <c r="Y17" s="39">
         <v>0</v>
       </c>
-      <c r="Z17" s="39">
-        <v>0</v>
-      </c>
-      <c r="AA17" s="40">
+      <c r="Z17" s="40">
         <v>98.92162234631661</v>
       </c>
+      <c r="AA17" s="41">
+        <v>0.99706214952726258</v>
+      </c>
       <c r="AB17" s="41">
-        <v>0.99706214952726258</v>
-      </c>
-      <c r="AC17" s="41">
         <v>8.1315504156125762E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:29">
+    <row r="18" spans="1:28">
       <c r="A18" s="2">
         <v>2000</v>
       </c>
@@ -6892,46 +6848,46 @@
         <v>0</v>
       </c>
       <c r="H18" s="39">
-        <v>0</v>
+        <v>3.7342903074627926E-2</v>
       </c>
       <c r="I18" s="39">
-        <v>3.7342903074627926E-2</v>
+        <v>89.574028709277485</v>
       </c>
       <c r="J18" s="39">
-        <v>89.574028709277485</v>
+        <v>0.5855378134942566</v>
       </c>
       <c r="K18" s="39">
-        <v>0.5855378134942566</v>
+        <v>8.2626928764545085</v>
       </c>
       <c r="L18" s="39">
-        <v>8.2626928764545085</v>
+        <v>1.5777406007737464</v>
       </c>
       <c r="M18" s="39">
-        <v>1.5777406007737464</v>
+        <v>19.60580757912976</v>
       </c>
       <c r="N18" s="39">
-        <v>19.60580757912976</v>
+        <v>72.277883997789289</v>
       </c>
       <c r="O18" s="39">
-        <v>72.277883997789289</v>
+        <v>1.9179350829760855</v>
       </c>
       <c r="P18" s="39">
-        <v>1.9179350829760855</v>
-      </c>
-      <c r="Q18" s="39">
         <v>6.1983733401048591</v>
       </c>
-      <c r="R18" s="42">
+      <c r="Q18" s="42">
         <v>69.699165011128201</v>
       </c>
-      <c r="S18" s="43">
+      <c r="R18" s="43">
         <v>30.300834988871795</v>
       </c>
+      <c r="S18" s="39">
+        <v>29.219942641193779</v>
+      </c>
       <c r="T18" s="39">
-        <v>29.219942641193779</v>
+        <v>70.780057358806218</v>
       </c>
       <c r="U18" s="39">
-        <v>70.780057358806218</v>
+        <v>0</v>
       </c>
       <c r="V18" s="39">
         <v>0</v>
@@ -6945,20 +6901,17 @@
       <c r="Y18" s="39">
         <v>0</v>
       </c>
-      <c r="Z18" s="39">
-        <v>0</v>
-      </c>
-      <c r="AA18" s="40">
+      <c r="Z18" s="40">
         <v>97.586897097704153</v>
       </c>
+      <c r="AA18" s="41">
+        <v>2.0796301551973948</v>
+      </c>
       <c r="AB18" s="41">
-        <v>2.0796301551973948</v>
-      </c>
-      <c r="AC18" s="41">
         <v>0.33347274709845098</v>
       </c>
     </row>
-    <row r="19" spans="1:29">
+    <row r="19" spans="1:28">
       <c r="A19" s="2">
         <v>2000</v>
       </c>
@@ -6981,46 +6934,46 @@
         <v>0</v>
       </c>
       <c r="H19" s="39">
-        <v>0</v>
+        <v>5.0263577295574353E-2</v>
       </c>
       <c r="I19" s="39">
-        <v>5.0263577295574353E-2</v>
+        <v>89.256193281251441</v>
       </c>
       <c r="J19" s="39">
-        <v>89.256193281251441</v>
+        <v>0.37881458007055269</v>
       </c>
       <c r="K19" s="39">
-        <v>0.37881458007055269</v>
+        <v>9.4158102984850487</v>
       </c>
       <c r="L19" s="39">
-        <v>9.4158102984850487</v>
+        <v>0.94918184019296259</v>
       </c>
       <c r="M19" s="39">
-        <v>0.94918184019296259</v>
+        <v>19.284851754004205</v>
       </c>
       <c r="N19" s="39">
-        <v>19.284851754004205</v>
+        <v>74.221685535824847</v>
       </c>
       <c r="O19" s="39">
-        <v>74.221685535824847</v>
+        <v>1.926247846954475</v>
       </c>
       <c r="P19" s="39">
-        <v>1.926247846954475</v>
-      </c>
-      <c r="Q19" s="39">
         <v>4.5672148632164813</v>
       </c>
-      <c r="R19" s="42">
+      <c r="Q19" s="42">
         <v>70.174481505205634</v>
       </c>
-      <c r="S19" s="43">
+      <c r="R19" s="43">
         <v>29.825518494794363</v>
       </c>
+      <c r="S19" s="39">
+        <v>25.282424405882026</v>
+      </c>
       <c r="T19" s="39">
-        <v>25.282424405882026</v>
+        <v>74.717575594117974</v>
       </c>
       <c r="U19" s="39">
-        <v>74.717575594117974</v>
+        <v>0</v>
       </c>
       <c r="V19" s="39">
         <v>0</v>
@@ -7034,20 +6987,17 @@
       <c r="Y19" s="39">
         <v>0</v>
       </c>
-      <c r="Z19" s="39">
-        <v>0</v>
-      </c>
-      <c r="AA19" s="40">
+      <c r="Z19" s="40">
         <v>98.749850588909567</v>
       </c>
+      <c r="AA19" s="41">
+        <v>0.77019501595250717</v>
+      </c>
       <c r="AB19" s="41">
-        <v>0.77019501595250717</v>
-      </c>
-      <c r="AC19" s="41">
         <v>0.47995439513793325</v>
       </c>
     </row>
-    <row r="20" spans="1:29">
+    <row r="20" spans="1:28">
       <c r="A20" s="2">
         <v>2001</v>
       </c>
@@ -7070,46 +7020,46 @@
         <v>0</v>
       </c>
       <c r="H20" s="39">
-        <v>0</v>
+        <v>0.13491043263472396</v>
       </c>
       <c r="I20" s="39">
-        <v>0.13491043263472396</v>
+        <v>86.673042921260574</v>
       </c>
       <c r="J20" s="39">
-        <v>86.673042921260574</v>
+        <v>0.36502595106370839</v>
       </c>
       <c r="K20" s="39">
-        <v>0.36502595106370839</v>
+        <v>11.159834860855792</v>
       </c>
       <c r="L20" s="39">
-        <v>11.159834860855792</v>
+        <v>1.8020962668199307</v>
       </c>
       <c r="M20" s="39">
-        <v>1.8020962668199307</v>
+        <v>16.513914420718734</v>
       </c>
       <c r="N20" s="39">
-        <v>16.513914420718734</v>
+        <v>76.366543967639046</v>
       </c>
       <c r="O20" s="39">
-        <v>76.366543967639046</v>
+        <v>1.5691289831482609</v>
       </c>
       <c r="P20" s="39">
-        <v>1.5691289831482609</v>
-      </c>
-      <c r="Q20" s="39">
         <v>5.5504126284939606</v>
       </c>
-      <c r="R20" s="42">
+      <c r="Q20" s="42">
         <v>69.71513058891145</v>
       </c>
-      <c r="S20" s="43">
+      <c r="R20" s="43">
         <v>30.28486941108854</v>
       </c>
+      <c r="S20" s="39">
+        <v>29.95055477802298</v>
+      </c>
       <c r="T20" s="39">
-        <v>29.95055477802298</v>
+        <v>70.04944522197701</v>
       </c>
       <c r="U20" s="39">
-        <v>70.04944522197701</v>
+        <v>0</v>
       </c>
       <c r="V20" s="39">
         <v>0</v>
@@ -7123,20 +7073,17 @@
       <c r="Y20" s="39">
         <v>0</v>
       </c>
-      <c r="Z20" s="39">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="40">
+      <c r="Z20" s="40">
         <v>97.556475920133025</v>
       </c>
+      <c r="AA20" s="41">
+        <v>1.3333099342339061</v>
+      </c>
       <c r="AB20" s="41">
-        <v>1.3333099342339061</v>
-      </c>
-      <c r="AC20" s="41">
         <v>1.1102141456330701</v>
       </c>
     </row>
-    <row r="21" spans="1:29">
+    <row r="21" spans="1:28">
       <c r="A21" s="2">
         <v>2001</v>
       </c>
@@ -7159,46 +7106,46 @@
         <v>0</v>
       </c>
       <c r="H21" s="39">
-        <v>0</v>
+        <v>4.2137145319291844E-2</v>
       </c>
       <c r="I21" s="39">
-        <v>4.2137145319291844E-2</v>
+        <v>82.171552040958574</v>
       </c>
       <c r="J21" s="39">
-        <v>82.171552040958574</v>
+        <v>0.76417138729422507</v>
       </c>
       <c r="K21" s="39">
-        <v>0.76417138729422507</v>
+        <v>14.106122242076315</v>
       </c>
       <c r="L21" s="39">
-        <v>14.106122242076315</v>
+        <v>2.9581543296708865</v>
       </c>
       <c r="M21" s="39">
-        <v>2.9581543296708865</v>
+        <v>16.475623819843111</v>
       </c>
       <c r="N21" s="39">
-        <v>16.475623819843111</v>
+        <v>76.99343547630815</v>
       </c>
       <c r="O21" s="39">
-        <v>76.99343547630815</v>
+        <v>1.4301283757239354</v>
       </c>
       <c r="P21" s="39">
-        <v>1.4301283757239354</v>
-      </c>
-      <c r="Q21" s="39">
         <v>5.1008123281248023</v>
       </c>
-      <c r="R21" s="42">
+      <c r="Q21" s="42">
         <v>72.695763474381877</v>
       </c>
-      <c r="S21" s="43">
+      <c r="R21" s="43">
         <v>27.304236525618119</v>
       </c>
+      <c r="S21" s="39">
+        <v>20.648785309660493</v>
+      </c>
       <c r="T21" s="39">
-        <v>20.648785309660493</v>
+        <v>79.351214690339503</v>
       </c>
       <c r="U21" s="39">
-        <v>79.351214690339503</v>
+        <v>0</v>
       </c>
       <c r="V21" s="39">
         <v>0</v>
@@ -7212,20 +7159,17 @@
       <c r="Y21" s="39">
         <v>0</v>
       </c>
-      <c r="Z21" s="39">
-        <v>0</v>
-      </c>
-      <c r="AA21" s="40">
+      <c r="Z21" s="40">
         <v>99.437960181981779</v>
       </c>
+      <c r="AA21" s="41">
+        <v>0.42232191511741379</v>
+      </c>
       <c r="AB21" s="41">
-        <v>0.42232191511741379</v>
-      </c>
-      <c r="AC21" s="41">
         <v>0.13971790290080979</v>
       </c>
     </row>
-    <row r="22" spans="1:29">
+    <row r="22" spans="1:28">
       <c r="A22" s="2">
         <v>2002</v>
       </c>
@@ -7248,46 +7192,46 @@
         <v>0</v>
       </c>
       <c r="H22" s="39">
-        <v>0</v>
+        <v>0.35531549105871313</v>
       </c>
       <c r="I22" s="39">
-        <v>0.35531549105871313</v>
+        <v>84.671640537112438</v>
       </c>
       <c r="J22" s="39">
-        <v>84.671640537112438</v>
+        <v>0.5282602860146266</v>
       </c>
       <c r="K22" s="39">
-        <v>0.5282602860146266</v>
+        <v>12.843609956210541</v>
       </c>
       <c r="L22" s="39">
-        <v>12.843609956210541</v>
+        <v>1.9564892206623952</v>
       </c>
       <c r="M22" s="39">
-        <v>1.9564892206623952</v>
+        <v>17.446728290203005</v>
       </c>
       <c r="N22" s="39">
-        <v>17.446728290203005</v>
+        <v>76.649993750217718</v>
       </c>
       <c r="O22" s="39">
-        <v>76.649993750217718</v>
+        <v>1.4431874299460878</v>
       </c>
       <c r="P22" s="39">
-        <v>1.4431874299460878</v>
-      </c>
-      <c r="Q22" s="39">
         <v>4.460090529633189</v>
       </c>
-      <c r="R22" s="42">
+      <c r="Q22" s="42">
         <v>68.050908062628963</v>
       </c>
-      <c r="S22" s="43">
+      <c r="R22" s="43">
         <v>31.949091937371033</v>
       </c>
+      <c r="S22" s="39">
+        <v>30.515535319466331</v>
+      </c>
       <c r="T22" s="39">
-        <v>30.515535319466331</v>
+        <v>69.484464680533677</v>
       </c>
       <c r="U22" s="39">
-        <v>69.484464680533677</v>
+        <v>0</v>
       </c>
       <c r="V22" s="39">
         <v>0</v>
@@ -7301,20 +7245,17 @@
       <c r="Y22" s="39">
         <v>0</v>
       </c>
-      <c r="Z22" s="39">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="40">
+      <c r="Z22" s="40">
         <v>98.261126149293972</v>
       </c>
+      <c r="AA22" s="41">
+        <v>1.5550687783417381</v>
+      </c>
       <c r="AB22" s="41">
-        <v>1.5550687783417381</v>
-      </c>
-      <c r="AC22" s="41">
         <v>0.1838050723642824</v>
       </c>
     </row>
-    <row r="23" spans="1:29">
+    <row r="23" spans="1:28">
       <c r="A23" s="2">
         <v>2002</v>
       </c>
@@ -7337,46 +7278,46 @@
         <v>0</v>
       </c>
       <c r="H23" s="39">
-        <v>0</v>
+        <v>3.880201048556655E-2</v>
       </c>
       <c r="I23" s="39">
-        <v>3.880201048556655E-2</v>
+        <v>83.690823174124773</v>
       </c>
       <c r="J23" s="39">
-        <v>83.690823174124773</v>
+        <v>0.62023058621114913</v>
       </c>
       <c r="K23" s="39">
-        <v>0.62023058621114913</v>
+        <v>12.727360230044788</v>
       </c>
       <c r="L23" s="39">
-        <v>12.727360230044788</v>
+        <v>2.961586009619289</v>
       </c>
       <c r="M23" s="39">
-        <v>2.961586009619289</v>
+        <v>15.899198994155636</v>
       </c>
       <c r="N23" s="39">
-        <v>15.899198994155636</v>
+        <v>78.175222660374118</v>
       </c>
       <c r="O23" s="39">
-        <v>78.175222660374118</v>
+        <v>1.356867203878998</v>
       </c>
       <c r="P23" s="39">
-        <v>1.356867203878998</v>
-      </c>
-      <c r="Q23" s="39">
         <v>4.5687111415912431</v>
       </c>
-      <c r="R23" s="42">
+      <c r="Q23" s="42">
         <v>72.916497471853503</v>
       </c>
-      <c r="S23" s="43">
+      <c r="R23" s="43">
         <v>27.083502528146497</v>
       </c>
+      <c r="S23" s="39">
+        <v>32.439984719828431</v>
+      </c>
       <c r="T23" s="39">
-        <v>32.439984719828431</v>
+        <v>67.560015280171569</v>
       </c>
       <c r="U23" s="39">
-        <v>67.560015280171569</v>
+        <v>0</v>
       </c>
       <c r="V23" s="39">
         <v>0</v>
@@ -7390,20 +7331,17 @@
       <c r="Y23" s="39">
         <v>0</v>
       </c>
-      <c r="Z23" s="39">
-        <v>0</v>
-      </c>
-      <c r="AA23" s="40">
+      <c r="Z23" s="40">
         <v>98.770668086399141</v>
       </c>
+      <c r="AA23" s="41">
+        <v>0.66655236617066271</v>
+      </c>
       <c r="AB23" s="41">
-        <v>0.66655236617066271</v>
-      </c>
-      <c r="AC23" s="41">
         <v>0.56277954743019398</v>
       </c>
     </row>
-    <row r="24" spans="1:29">
+    <row r="24" spans="1:28">
       <c r="A24" s="2">
         <v>2003</v>
       </c>
@@ -7426,46 +7364,46 @@
         <v>0</v>
       </c>
       <c r="H24" s="39">
-        <v>0</v>
+        <v>2.5968735679006059E-2</v>
       </c>
       <c r="I24" s="39">
-        <v>2.5968735679006059E-2</v>
+        <v>82.691583074494616</v>
       </c>
       <c r="J24" s="39">
-        <v>82.691583074494616</v>
+        <v>0.52395743164112218</v>
       </c>
       <c r="K24" s="39">
-        <v>0.52395743164112218</v>
+        <v>15.253322470594224</v>
       </c>
       <c r="L24" s="39">
-        <v>15.253322470594224</v>
+        <v>1.5311370232700239</v>
       </c>
       <c r="M24" s="39">
-        <v>1.5311370232700239</v>
+        <v>16.13286487770932</v>
       </c>
       <c r="N24" s="39">
-        <v>16.13286487770932</v>
+        <v>77.389717738513497</v>
       </c>
       <c r="O24" s="39">
-        <v>77.389717738513497</v>
+        <v>2.4101702394894513</v>
       </c>
       <c r="P24" s="39">
-        <v>2.4101702394894513</v>
-      </c>
-      <c r="Q24" s="39">
         <v>4.0672471442877267</v>
       </c>
-      <c r="R24" s="42">
+      <c r="Q24" s="42">
         <v>75.179150330125438</v>
       </c>
-      <c r="S24" s="43">
+      <c r="R24" s="43">
         <v>24.820849669874569</v>
       </c>
+      <c r="S24" s="39">
+        <v>32.042194952220918</v>
+      </c>
       <c r="T24" s="39">
-        <v>32.042194952220918</v>
+        <v>67.957805047779075</v>
       </c>
       <c r="U24" s="39">
-        <v>67.957805047779075</v>
+        <v>0</v>
       </c>
       <c r="V24" s="39">
         <v>0</v>
@@ -7479,20 +7417,17 @@
       <c r="Y24" s="39">
         <v>0</v>
       </c>
-      <c r="Z24" s="39">
-        <v>0</v>
-      </c>
-      <c r="AA24" s="40">
+      <c r="Z24" s="40">
         <v>98.254154149057143</v>
       </c>
+      <c r="AA24" s="41">
+        <v>1.0699798020944717</v>
+      </c>
       <c r="AB24" s="41">
-        <v>1.0699798020944717</v>
-      </c>
-      <c r="AC24" s="41">
         <v>0.67586604884837986</v>
       </c>
     </row>
-    <row r="25" spans="1:29">
+    <row r="25" spans="1:28">
       <c r="A25" s="2">
         <v>2003</v>
       </c>
@@ -7515,46 +7450,46 @@
         <v>0</v>
       </c>
       <c r="H25" s="39">
-        <v>0</v>
+        <v>0.12957248963157258</v>
       </c>
       <c r="I25" s="39">
-        <v>0.12957248963157258</v>
+        <v>77.582382346602458</v>
       </c>
       <c r="J25" s="39">
-        <v>77.582382346602458</v>
+        <v>0.80739693336347051</v>
       </c>
       <c r="K25" s="39">
-        <v>0.80739693336347051</v>
+        <v>18.688137677997908</v>
       </c>
       <c r="L25" s="39">
-        <v>18.688137677997908</v>
+        <v>2.9220830420361539</v>
       </c>
       <c r="M25" s="39">
-        <v>2.9220830420361539</v>
+        <v>12.13145431321324</v>
       </c>
       <c r="N25" s="39">
-        <v>12.13145431321324</v>
+        <v>81.876935045547498</v>
       </c>
       <c r="O25" s="39">
-        <v>81.876935045547498</v>
+        <v>1.5609148395981938</v>
       </c>
       <c r="P25" s="39">
-        <v>1.5609148395981938</v>
-      </c>
-      <c r="Q25" s="39">
         <v>4.4306958016410762</v>
       </c>
-      <c r="R25" s="42">
+      <c r="Q25" s="42">
         <v>73.924127816821823</v>
       </c>
-      <c r="S25" s="43">
+      <c r="R25" s="43">
         <v>26.075872183178177</v>
       </c>
+      <c r="S25" s="39">
+        <v>26.962379297838009</v>
+      </c>
       <c r="T25" s="39">
-        <v>26.962379297838009</v>
+        <v>73.037620702162002</v>
       </c>
       <c r="U25" s="39">
-        <v>73.037620702162002</v>
+        <v>0</v>
       </c>
       <c r="V25" s="39">
         <v>0</v>
@@ -7568,20 +7503,17 @@
       <c r="Y25" s="39">
         <v>0</v>
       </c>
-      <c r="Z25" s="39">
-        <v>0</v>
-      </c>
-      <c r="AA25" s="40">
+      <c r="Z25" s="40">
         <v>98.709005945090695</v>
       </c>
+      <c r="AA25" s="41">
+        <v>0.93118728349829949</v>
+      </c>
       <c r="AB25" s="41">
-        <v>0.93118728349829949</v>
-      </c>
-      <c r="AC25" s="41">
         <v>0.3598067714109997</v>
       </c>
     </row>
-    <row r="26" spans="1:29">
+    <row r="26" spans="1:28">
       <c r="A26" s="2">
         <v>2004</v>
       </c>
@@ -7604,46 +7536,46 @@
         <v>0</v>
       </c>
       <c r="H26" s="39">
-        <v>0</v>
+        <v>5.5506259339072182E-2</v>
       </c>
       <c r="I26" s="39">
-        <v>5.5506259339072182E-2</v>
+        <v>80.630428185655958</v>
       </c>
       <c r="J26" s="39">
-        <v>80.630428185655958</v>
+        <v>0.62727834948584693</v>
       </c>
       <c r="K26" s="39">
-        <v>0.62727834948584693</v>
+        <v>17.81174735240905</v>
       </c>
       <c r="L26" s="39">
-        <v>17.81174735240905</v>
+        <v>0.93054611244915131</v>
       </c>
       <c r="M26" s="39">
-        <v>0.93054611244915131</v>
+        <v>14.18117703999908</v>
       </c>
       <c r="N26" s="39">
-        <v>14.18117703999908</v>
+        <v>80.551298155041081</v>
       </c>
       <c r="O26" s="39">
-        <v>80.551298155041081</v>
+        <v>1.0482808424659376</v>
       </c>
       <c r="P26" s="39">
-        <v>1.0482808424659376</v>
-      </c>
-      <c r="Q26" s="39">
         <v>4.219243962493902</v>
       </c>
-      <c r="R26" s="42">
+      <c r="Q26" s="42">
         <v>67.20463563693913</v>
       </c>
-      <c r="S26" s="43">
+      <c r="R26" s="43">
         <v>32.795364363060877</v>
       </c>
+      <c r="S26" s="39">
+        <v>29.411019048826304</v>
+      </c>
       <c r="T26" s="39">
-        <v>29.411019048826304</v>
+        <v>70.588980951173696</v>
       </c>
       <c r="U26" s="39">
-        <v>70.588980951173696</v>
+        <v>0</v>
       </c>
       <c r="V26" s="39">
         <v>0</v>
@@ -7657,20 +7589,17 @@
       <c r="Y26" s="39">
         <v>0</v>
       </c>
-      <c r="Z26" s="39">
-        <v>0</v>
-      </c>
-      <c r="AA26" s="40">
+      <c r="Z26" s="40">
         <v>98.527067464112989</v>
       </c>
+      <c r="AA26" s="41">
+        <v>0.71005758054169499</v>
+      </c>
       <c r="AB26" s="41">
-        <v>0.71005758054169499</v>
-      </c>
-      <c r="AC26" s="41">
         <v>0.76287495534531047</v>
       </c>
     </row>
-    <row r="27" spans="1:29">
+    <row r="27" spans="1:28">
       <c r="A27" s="2">
         <v>2004</v>
       </c>
@@ -7693,46 +7622,46 @@
         <v>0</v>
       </c>
       <c r="H27" s="39">
-        <v>0</v>
+        <v>4.1139645810936161E-2</v>
       </c>
       <c r="I27" s="39">
-        <v>4.1139645810936161E-2</v>
+        <v>71.637707202154786</v>
       </c>
       <c r="J27" s="39">
-        <v>71.637707202154786</v>
+        <v>1.1096061072968537</v>
       </c>
       <c r="K27" s="39">
-        <v>1.1096061072968537</v>
+        <v>24.642259730884618</v>
       </c>
       <c r="L27" s="39">
-        <v>24.642259730884618</v>
+        <v>2.6104269596637417</v>
       </c>
       <c r="M27" s="39">
-        <v>2.6104269596637417</v>
+        <v>13.42549648954626</v>
       </c>
       <c r="N27" s="39">
-        <v>13.42549648954626</v>
+        <v>81.741371347401028</v>
       </c>
       <c r="O27" s="39">
-        <v>81.741371347401028</v>
+        <v>1.288136645721671</v>
       </c>
       <c r="P27" s="39">
-        <v>1.288136645721671</v>
-      </c>
-      <c r="Q27" s="39">
         <v>3.5449955173310461</v>
       </c>
-      <c r="R27" s="42">
+      <c r="Q27" s="42">
         <v>69.975432645473276</v>
       </c>
-      <c r="S27" s="43">
+      <c r="R27" s="43">
         <v>30.02456735452672</v>
       </c>
+      <c r="S27" s="39">
+        <v>35.024198650153885</v>
+      </c>
       <c r="T27" s="39">
-        <v>35.024198650153885</v>
+        <v>64.975801349846122</v>
       </c>
       <c r="U27" s="39">
-        <v>64.975801349846122</v>
+        <v>0</v>
       </c>
       <c r="V27" s="39">
         <v>0</v>
@@ -7746,20 +7675,17 @@
       <c r="Y27" s="39">
         <v>0</v>
       </c>
-      <c r="Z27" s="39">
-        <v>0</v>
-      </c>
-      <c r="AA27" s="40">
+      <c r="Z27" s="40">
         <v>99.449272099946057</v>
       </c>
+      <c r="AA27" s="41">
+        <v>0.37297358136141179</v>
+      </c>
       <c r="AB27" s="41">
-        <v>0.37297358136141179</v>
-      </c>
-      <c r="AC27" s="41">
         <v>0.1777543186925355</v>
       </c>
     </row>
-    <row r="28" spans="1:29">
+    <row r="28" spans="1:28">
       <c r="A28" s="2">
         <v>2005</v>
       </c>
@@ -7782,46 +7708,46 @@
         <v>0</v>
       </c>
       <c r="H28" s="39">
-        <v>0</v>
+        <v>8.0956039148273568E-2</v>
       </c>
       <c r="I28" s="39">
-        <v>8.0956039148273568E-2</v>
+        <v>80.707486883399199</v>
       </c>
       <c r="J28" s="39">
-        <v>80.707486883399199</v>
+        <v>0.37412024900010676</v>
       </c>
       <c r="K28" s="39">
-        <v>0.37412024900010676</v>
+        <v>16.074079943227424</v>
       </c>
       <c r="L28" s="39">
-        <v>16.074079943227424</v>
+        <v>2.8443129243732796</v>
       </c>
       <c r="M28" s="39">
-        <v>2.8443129243732796</v>
+        <v>16.212394197346708</v>
       </c>
       <c r="N28" s="39">
-        <v>16.212394197346708</v>
+        <v>79.866749804499776</v>
       </c>
       <c r="O28" s="39">
-        <v>79.866749804499776</v>
+        <v>1.21279036519786</v>
       </c>
       <c r="P28" s="39">
-        <v>1.21279036519786</v>
-      </c>
-      <c r="Q28" s="39">
         <v>2.7080656329556532</v>
       </c>
-      <c r="R28" s="42">
+      <c r="Q28" s="42">
         <v>76.548757927663189</v>
       </c>
-      <c r="S28" s="43">
+      <c r="R28" s="43">
         <v>23.451242072336807</v>
       </c>
+      <c r="S28" s="39">
+        <v>36.508245458710697</v>
+      </c>
       <c r="T28" s="39">
-        <v>36.508245458710697</v>
+        <v>63.491754541289303</v>
       </c>
       <c r="U28" s="39">
-        <v>63.491754541289303</v>
+        <v>0</v>
       </c>
       <c r="V28" s="39">
         <v>0</v>
@@ -7835,20 +7761,17 @@
       <c r="Y28" s="39">
         <v>0</v>
       </c>
-      <c r="Z28" s="39">
-        <v>0</v>
-      </c>
-      <c r="AA28" s="40">
+      <c r="Z28" s="40">
         <v>99.630013676403209</v>
       </c>
+      <c r="AA28" s="41">
+        <v>0.26181527554335282</v>
+      </c>
       <c r="AB28" s="41">
-        <v>0.26181527554335282</v>
-      </c>
-      <c r="AC28" s="41">
         <v>0.10817104805343788</v>
       </c>
     </row>
-    <row r="29" spans="1:29">
+    <row r="29" spans="1:28">
       <c r="A29" s="2">
         <v>2005</v>
       </c>
@@ -7871,46 +7794,46 @@
         <v>0</v>
       </c>
       <c r="H29" s="39">
-        <v>0</v>
+        <v>0.27228396048377373</v>
       </c>
       <c r="I29" s="39">
-        <v>0.27228396048377373</v>
+        <v>77.047667920126301</v>
       </c>
       <c r="J29" s="39">
-        <v>77.047667920126301</v>
+        <v>0.83928516346852189</v>
       </c>
       <c r="K29" s="39">
-        <v>0.83928516346852189</v>
+        <v>20.608054109076228</v>
       </c>
       <c r="L29" s="39">
-        <v>20.608054109076228</v>
+        <v>1.5049928073289534</v>
       </c>
       <c r="M29" s="39">
-        <v>1.5049928073289534</v>
+        <v>14.401606222992431</v>
       </c>
       <c r="N29" s="39">
-        <v>14.401606222992431</v>
+        <v>80.871701255983368</v>
       </c>
       <c r="O29" s="39">
-        <v>80.871701255983368</v>
+        <v>1.6477245641633929</v>
       </c>
       <c r="P29" s="39">
-        <v>1.6477245641633929</v>
-      </c>
-      <c r="Q29" s="39">
         <v>3.0789679568607986</v>
       </c>
-      <c r="R29" s="42">
+      <c r="Q29" s="42">
         <v>74.495882090669724</v>
       </c>
-      <c r="S29" s="43">
+      <c r="R29" s="43">
         <v>25.504117909330283</v>
       </c>
+      <c r="S29" s="39">
+        <v>28.050856250332995</v>
+      </c>
       <c r="T29" s="39">
-        <v>28.050856250332995</v>
+        <v>71.949143749667016</v>
       </c>
       <c r="U29" s="39">
-        <v>71.949143749667016</v>
+        <v>0</v>
       </c>
       <c r="V29" s="39">
         <v>0</v>
@@ -7924,20 +7847,17 @@
       <c r="Y29" s="39">
         <v>0</v>
       </c>
-      <c r="Z29" s="39">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="40">
+      <c r="Z29" s="40">
         <v>99.454310414931584</v>
       </c>
+      <c r="AA29" s="41">
+        <v>0.45090896854573448</v>
+      </c>
       <c r="AB29" s="41">
-        <v>0.45090896854573448</v>
-      </c>
-      <c r="AC29" s="41">
         <v>9.4780616522673028E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:29">
+    <row r="30" spans="1:28">
       <c r="A30" s="2">
         <v>2006</v>
       </c>
@@ -7960,46 +7880,46 @@
         <v>0</v>
       </c>
       <c r="H30" s="39">
-        <v>0</v>
+        <v>0.20886288954620097</v>
       </c>
       <c r="I30" s="39">
-        <v>0.20886288954620097</v>
+        <v>81.340479218530149</v>
       </c>
       <c r="J30" s="39">
-        <v>81.340479218530149</v>
+        <v>0.54845627232384453</v>
       </c>
       <c r="K30" s="39">
-        <v>0.54845627232384453</v>
+        <v>15.712265937872063</v>
       </c>
       <c r="L30" s="39">
-        <v>15.712265937872063</v>
+        <v>2.3987985712739475</v>
       </c>
       <c r="M30" s="39">
-        <v>2.3987985712739475</v>
+        <v>17.323134267777899</v>
       </c>
       <c r="N30" s="39">
-        <v>17.323134267777899</v>
+        <v>78.05684462604178</v>
       </c>
       <c r="O30" s="39">
-        <v>78.05684462604178</v>
+        <v>1.2262893711440632</v>
       </c>
       <c r="P30" s="39">
-        <v>1.2262893711440632</v>
-      </c>
-      <c r="Q30" s="39">
         <v>3.3937317350362592</v>
       </c>
-      <c r="R30" s="42">
+      <c r="Q30" s="42">
         <v>71.635018670851821</v>
       </c>
-      <c r="S30" s="43">
+      <c r="R30" s="43">
         <v>28.364981329148176</v>
       </c>
+      <c r="S30" s="39">
+        <v>33.613621604069706</v>
+      </c>
       <c r="T30" s="39">
-        <v>33.613621604069706</v>
+        <v>66.386378395930294</v>
       </c>
       <c r="U30" s="39">
-        <v>66.386378395930294</v>
+        <v>0</v>
       </c>
       <c r="V30" s="39">
         <v>0</v>
@@ -8013,20 +7933,17 @@
       <c r="Y30" s="39">
         <v>0</v>
       </c>
-      <c r="Z30" s="39">
-        <v>0</v>
-      </c>
-      <c r="AA30" s="40">
+      <c r="Z30" s="40">
         <v>98.025692715661876</v>
       </c>
+      <c r="AA30" s="41">
+        <v>0.8537179348414331</v>
+      </c>
       <c r="AB30" s="41">
-        <v>0.8537179348414331</v>
-      </c>
-      <c r="AC30" s="41">
         <v>1.1205893494966988</v>
       </c>
     </row>
-    <row r="31" spans="1:29">
+    <row r="31" spans="1:28">
       <c r="A31" s="2">
         <v>2006</v>
       </c>
@@ -8049,46 +7966,46 @@
         <v>0</v>
       </c>
       <c r="H31" s="39">
-        <v>0</v>
+        <v>4.3064938070048013E-2</v>
       </c>
       <c r="I31" s="39">
-        <v>4.3064938070048013E-2</v>
+        <v>72.779745338381147</v>
       </c>
       <c r="J31" s="39">
-        <v>72.779745338381147</v>
+        <v>1.2144955296023243</v>
       </c>
       <c r="K31" s="39">
-        <v>1.2144955296023243</v>
+        <v>23.630438555332017</v>
       </c>
       <c r="L31" s="39">
-        <v>23.630438555332017</v>
+        <v>2.3753205766845138</v>
       </c>
       <c r="M31" s="39">
-        <v>2.3753205766845138</v>
+        <v>13.5143560506238</v>
       </c>
       <c r="N31" s="39">
-        <v>13.5143560506238</v>
+        <v>82.270743480803958</v>
       </c>
       <c r="O31" s="39">
-        <v>82.270743480803958</v>
+        <v>3.1077459040101814</v>
       </c>
       <c r="P31" s="39">
-        <v>3.1077459040101814</v>
-      </c>
-      <c r="Q31" s="39">
         <v>1.1071545645620553</v>
       </c>
-      <c r="R31" s="42">
+      <c r="Q31" s="42">
         <v>64.045918793667525</v>
       </c>
-      <c r="S31" s="43">
+      <c r="R31" s="43">
         <v>35.954081206332475</v>
       </c>
+      <c r="S31" s="39">
+        <v>26.974077478322911</v>
+      </c>
       <c r="T31" s="39">
-        <v>26.974077478322911</v>
+        <v>73.025922521677089</v>
       </c>
       <c r="U31" s="39">
-        <v>73.025922521677089</v>
+        <v>0</v>
       </c>
       <c r="V31" s="39">
         <v>0</v>
@@ -8102,20 +8019,17 @@
       <c r="Y31" s="39">
         <v>0</v>
       </c>
-      <c r="Z31" s="39">
-        <v>0</v>
-      </c>
-      <c r="AA31" s="40">
+      <c r="Z31" s="40">
         <v>99.218403512042102</v>
       </c>
+      <c r="AA31" s="41">
+        <v>0.56627179760764634</v>
+      </c>
       <c r="AB31" s="41">
-        <v>0.56627179760764634</v>
-      </c>
-      <c r="AC31" s="41">
         <v>0.21532469035024007</v>
       </c>
     </row>
-    <row r="32" spans="1:29">
+    <row r="32" spans="1:28">
       <c r="A32" s="2">
         <v>2007</v>
       </c>
@@ -8138,46 +8052,46 @@
         <v>0</v>
       </c>
       <c r="H32" s="39">
-        <v>0</v>
+        <v>9.3860633969544319E-2</v>
       </c>
       <c r="I32" s="39">
-        <v>9.3860633969544319E-2</v>
+        <v>75.318372464737678</v>
       </c>
       <c r="J32" s="39">
-        <v>75.318372464737678</v>
+        <v>1.2059896886980277</v>
       </c>
       <c r="K32" s="39">
-        <v>1.2059896886980277</v>
+        <v>20.809681567446088</v>
       </c>
       <c r="L32" s="39">
-        <v>20.809681567446088</v>
+        <v>2.6659562791182112</v>
       </c>
       <c r="M32" s="39">
-        <v>2.6659562791182112</v>
+        <v>12.074481404689644</v>
       </c>
       <c r="N32" s="39">
-        <v>12.074481404689644</v>
+        <v>83.758526398028792</v>
       </c>
       <c r="O32" s="39">
-        <v>83.758526398028792</v>
+        <v>1.0805613149433577</v>
       </c>
       <c r="P32" s="39">
-        <v>1.0805613149433577</v>
-      </c>
-      <c r="Q32" s="39">
         <v>3.0864308823382114</v>
       </c>
-      <c r="R32" s="42">
+      <c r="Q32" s="42">
         <v>62.056513152887547</v>
       </c>
-      <c r="S32" s="43">
+      <c r="R32" s="43">
         <v>37.943486847112453</v>
       </c>
+      <c r="S32" s="39">
+        <v>27.828122715702747</v>
+      </c>
       <c r="T32" s="39">
-        <v>27.828122715702747</v>
+        <v>72.171877284297253</v>
       </c>
       <c r="U32" s="39">
-        <v>72.171877284297253</v>
+        <v>0</v>
       </c>
       <c r="V32" s="39">
         <v>0</v>
@@ -8191,20 +8105,17 @@
       <c r="Y32" s="39">
         <v>0</v>
       </c>
-      <c r="Z32" s="39">
-        <v>0</v>
-      </c>
-      <c r="AA32" s="40">
+      <c r="Z32" s="40">
         <v>98.493633845469788</v>
       </c>
+      <c r="AA32" s="41">
+        <v>1.4230463406378373</v>
+      </c>
       <c r="AB32" s="41">
-        <v>1.4230463406378373</v>
-      </c>
-      <c r="AC32" s="41">
         <v>8.3319813892377234E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:29">
+    <row r="33" spans="1:28">
       <c r="A33" s="2">
         <v>2007</v>
       </c>
@@ -8227,46 +8138,46 @@
         <v>0</v>
       </c>
       <c r="H33" s="39">
-        <v>0</v>
+        <v>2.2910590511378927E-2</v>
       </c>
       <c r="I33" s="39">
-        <v>2.2910590511378927E-2</v>
+        <v>69.992327635420864</v>
       </c>
       <c r="J33" s="39">
-        <v>69.992327635420864</v>
+        <v>0.58906306247341034</v>
       </c>
       <c r="K33" s="39">
-        <v>0.58906306247341034</v>
+        <v>27.788140924247216</v>
       </c>
       <c r="L33" s="39">
-        <v>27.788140924247216</v>
+        <v>1.6304683778585012</v>
       </c>
       <c r="M33" s="39">
-        <v>1.6304683778585012</v>
+        <v>11.220878421387651</v>
       </c>
       <c r="N33" s="39">
-        <v>11.220878421387651</v>
+        <v>85.892879876329914</v>
       </c>
       <c r="O33" s="39">
-        <v>85.892879876329914</v>
+        <v>0.52268800581976904</v>
       </c>
       <c r="P33" s="39">
-        <v>0.52268800581976904</v>
-      </c>
-      <c r="Q33" s="39">
         <v>2.3635536964626715</v>
       </c>
-      <c r="R33" s="42">
+      <c r="Q33" s="42">
         <v>64.045918793667525</v>
       </c>
-      <c r="S33" s="43">
+      <c r="R33" s="43">
         <v>35.954081206332475</v>
       </c>
+      <c r="S33" s="39">
+        <v>27.863010410946949</v>
+      </c>
       <c r="T33" s="39">
-        <v>27.863010410946949</v>
+        <v>72.136989589053044</v>
       </c>
       <c r="U33" s="39">
-        <v>72.136989589053044</v>
+        <v>0</v>
       </c>
       <c r="V33" s="39">
         <v>0</v>
@@ -8280,20 +8191,17 @@
       <c r="Y33" s="39">
         <v>0</v>
       </c>
-      <c r="Z33" s="39">
-        <v>0</v>
-      </c>
-      <c r="AA33" s="40">
+      <c r="Z33" s="40">
         <v>99.133645788950432</v>
       </c>
+      <c r="AA33" s="41">
+        <v>0.76984985378679449</v>
+      </c>
       <c r="AB33" s="41">
-        <v>0.76984985378679449</v>
-      </c>
-      <c r="AC33" s="41">
         <v>9.6504357262772261E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:29">
+    <row r="34" spans="1:28">
       <c r="A34" s="2">
         <v>2008</v>
       </c>
@@ -8316,46 +8224,46 @@
         <v>0</v>
       </c>
       <c r="H34" s="39">
-        <v>0</v>
+        <v>4.9254842054355215E-2</v>
       </c>
       <c r="I34" s="39">
-        <v>4.9254842054355215E-2</v>
+        <v>75.767153087975217</v>
       </c>
       <c r="J34" s="39">
-        <v>75.767153087975217</v>
+        <v>0.58035053029262018</v>
       </c>
       <c r="K34" s="39">
-        <v>0.58035053029262018</v>
+        <v>22.387039551995088</v>
       </c>
       <c r="L34" s="39">
-        <v>22.387039551995088</v>
+        <v>1.2654568297370754</v>
       </c>
       <c r="M34" s="39">
-        <v>1.2654568297370754</v>
+        <v>14.22396716338003</v>
       </c>
       <c r="N34" s="39">
-        <v>14.22396716338003</v>
+        <v>81.163023110555898</v>
       </c>
       <c r="O34" s="39">
-        <v>81.163023110555898</v>
+        <v>0.99027393593289914</v>
       </c>
       <c r="P34" s="39">
-        <v>0.99027393593289914</v>
-      </c>
-      <c r="Q34" s="39">
         <v>3.6227357901311681</v>
       </c>
-      <c r="R34" s="42">
+      <c r="Q34" s="42">
         <v>67.014424887258158</v>
       </c>
-      <c r="S34" s="43">
+      <c r="R34" s="43">
         <v>32.985575112741834</v>
       </c>
+      <c r="S34" s="39">
+        <v>34.044732676483129</v>
+      </c>
       <c r="T34" s="39">
-        <v>34.044732676483129</v>
+        <v>65.955267323516864</v>
       </c>
       <c r="U34" s="39">
-        <v>65.955267323516864</v>
+        <v>0</v>
       </c>
       <c r="V34" s="39">
         <v>0</v>
@@ -8369,20 +8277,17 @@
       <c r="Y34" s="39">
         <v>0</v>
       </c>
-      <c r="Z34" s="39">
-        <v>0</v>
-      </c>
-      <c r="AA34" s="40">
+      <c r="Z34" s="40">
         <v>98.802179348301337</v>
       </c>
+      <c r="AA34" s="41">
+        <v>1.1712301753722221</v>
+      </c>
       <c r="AB34" s="41">
-        <v>1.1712301753722221</v>
-      </c>
-      <c r="AC34" s="41">
         <v>2.659047632644539E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:29">
+    <row r="35" spans="1:28">
       <c r="A35" s="2">
         <v>2008</v>
       </c>
@@ -8405,46 +8310,46 @@
         <v>0</v>
       </c>
       <c r="H35" s="39">
-        <v>0</v>
+        <v>0.14529807663287875</v>
       </c>
       <c r="I35" s="39">
-        <v>0.14529807663287875</v>
+        <v>74.306706881943441</v>
       </c>
       <c r="J35" s="39">
-        <v>74.306706881943441</v>
+        <v>0.86840851419787568</v>
       </c>
       <c r="K35" s="39">
-        <v>0.86840851419787568</v>
+        <v>24.155899594038424</v>
       </c>
       <c r="L35" s="39">
-        <v>24.155899594038424</v>
+        <v>0.6689850098202601</v>
       </c>
       <c r="M35" s="39">
-        <v>0.6689850098202601</v>
+        <v>13.877935567882682</v>
       </c>
       <c r="N35" s="39">
-        <v>13.877935567882682</v>
+        <v>83.052236022568266</v>
       </c>
       <c r="O35" s="39">
-        <v>83.052236022568266</v>
+        <v>0.67911787977242</v>
       </c>
       <c r="P35" s="39">
-        <v>0.67911787977242</v>
-      </c>
-      <c r="Q35" s="39">
         <v>2.3907105297766238</v>
       </c>
-      <c r="R35" s="42">
+      <c r="Q35" s="42">
         <v>75.190422497558401</v>
       </c>
-      <c r="S35" s="43">
+      <c r="R35" s="43">
         <v>24.809577502441591</v>
       </c>
+      <c r="S35" s="39">
+        <v>33.442782701681836</v>
+      </c>
       <c r="T35" s="39">
-        <v>33.442782701681836</v>
+        <v>66.557217298318164</v>
       </c>
       <c r="U35" s="39">
-        <v>66.557217298318164</v>
+        <v>0</v>
       </c>
       <c r="V35" s="39">
         <v>0</v>
@@ -8458,20 +8363,17 @@
       <c r="Y35" s="39">
         <v>0</v>
       </c>
-      <c r="Z35" s="39">
-        <v>0</v>
-      </c>
-      <c r="AA35" s="40">
+      <c r="Z35" s="40">
         <v>98.898751069880149</v>
       </c>
+      <c r="AA35" s="41">
+        <v>1.0423920472062385</v>
+      </c>
       <c r="AB35" s="41">
-        <v>1.0423920472062385</v>
-      </c>
-      <c r="AC35" s="41">
         <v>5.8856882913609736E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:29">
+    <row r="36" spans="1:28">
       <c r="A36" s="2">
         <v>2009</v>
       </c>
@@ -8494,46 +8396,46 @@
         <v>0</v>
       </c>
       <c r="H36" s="39">
-        <v>0</v>
+        <v>9.2860645753246956E-2</v>
       </c>
       <c r="I36" s="39">
-        <v>9.2860645753246956E-2</v>
+        <v>68.744878426905856</v>
       </c>
       <c r="J36" s="39">
-        <v>68.744878426905856</v>
+        <v>0.511920016452312</v>
       </c>
       <c r="K36" s="39">
-        <v>0.511920016452312</v>
+        <v>29.904766424627844</v>
       </c>
       <c r="L36" s="39">
-        <v>29.904766424627844</v>
+        <v>0.83843513201398456</v>
       </c>
       <c r="M36" s="39">
-        <v>0.83843513201398456</v>
+        <v>14.837565571747675</v>
       </c>
       <c r="N36" s="39">
-        <v>14.837565571747675</v>
+        <v>81.477919168781199</v>
       </c>
       <c r="O36" s="39">
-        <v>81.477919168781199</v>
+        <v>0.92101016876222053</v>
       </c>
       <c r="P36" s="39">
-        <v>0.92101016876222053</v>
-      </c>
-      <c r="Q36" s="39">
         <v>2.7635050907089025</v>
       </c>
-      <c r="R36" s="42">
+      <c r="Q36" s="42">
         <v>72.064132377833673</v>
       </c>
-      <c r="S36" s="43">
+      <c r="R36" s="43">
         <v>27.935867622166327</v>
       </c>
+      <c r="S36" s="39">
+        <v>39.032477496717448</v>
+      </c>
       <c r="T36" s="39">
-        <v>39.032477496717448</v>
+        <v>60.967522503282559</v>
       </c>
       <c r="U36" s="39">
-        <v>60.967522503282559</v>
+        <v>0</v>
       </c>
       <c r="V36" s="39">
         <v>0</v>
@@ -8547,20 +8449,17 @@
       <c r="Y36" s="39">
         <v>0</v>
       </c>
-      <c r="Z36" s="39">
-        <v>0</v>
-      </c>
-      <c r="AA36" s="40">
+      <c r="Z36" s="40">
         <v>98.492240520146169</v>
       </c>
+      <c r="AA36" s="41">
+        <v>1.042823469855884</v>
+      </c>
       <c r="AB36" s="41">
-        <v>1.042823469855884</v>
-      </c>
-      <c r="AC36" s="41">
         <v>0.46493600999794343</v>
       </c>
     </row>
-    <row r="37" spans="1:29">
+    <row r="37" spans="1:28">
       <c r="A37" s="2">
         <v>2009</v>
       </c>
@@ -8583,46 +8482,46 @@
         <v>0</v>
       </c>
       <c r="H37" s="39">
-        <v>0</v>
+        <v>6.2316131182702197E-2</v>
       </c>
       <c r="I37" s="39">
-        <v>6.2316131182702197E-2</v>
+        <v>67.05389620741127</v>
       </c>
       <c r="J37" s="39">
-        <v>67.05389620741127</v>
+        <v>0.80199411619784644</v>
       </c>
       <c r="K37" s="39">
-        <v>0.80199411619784644</v>
+        <v>31.818616581887742</v>
       </c>
       <c r="L37" s="39">
-        <v>31.818616581887742</v>
+        <v>0.32549309450313751</v>
       </c>
       <c r="M37" s="39">
-        <v>0.32549309450313751</v>
+        <v>14.224309088010667</v>
       </c>
       <c r="N37" s="39">
-        <v>14.224309088010667</v>
+        <v>81.519064388504844</v>
       </c>
       <c r="O37" s="39">
-        <v>81.519064388504844</v>
+        <v>1.0445922641044592</v>
       </c>
       <c r="P37" s="39">
-        <v>1.0445922641044592</v>
-      </c>
-      <c r="Q37" s="39">
         <v>3.2120342593800268</v>
       </c>
-      <c r="R37" s="42">
+      <c r="Q37" s="42">
         <v>68.615277596626228</v>
       </c>
-      <c r="S37" s="43">
+      <c r="R37" s="43">
         <v>31.384722403373765</v>
       </c>
+      <c r="S37" s="39">
+        <v>31.045606712751621</v>
+      </c>
       <c r="T37" s="39">
-        <v>31.045606712751621</v>
+        <v>68.954393287248379</v>
       </c>
       <c r="U37" s="39">
-        <v>68.954393287248379</v>
+        <v>0</v>
       </c>
       <c r="V37" s="39">
         <v>0</v>
@@ -8636,20 +8535,17 @@
       <c r="Y37" s="39">
         <v>0</v>
       </c>
-      <c r="Z37" s="39">
-        <v>0</v>
-      </c>
-      <c r="AA37" s="40">
+      <c r="Z37" s="40">
         <v>99.245829891453994</v>
       </c>
+      <c r="AA37" s="41">
+        <v>0.69098444995145136</v>
+      </c>
       <c r="AB37" s="41">
-        <v>0.69098444995145136</v>
-      </c>
-      <c r="AC37" s="41">
         <v>6.3185658594553856E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:29">
+    <row r="38" spans="1:28">
       <c r="A38" s="2">
         <v>2010</v>
       </c>
@@ -8672,46 +8568,46 @@
         <v>0</v>
       </c>
       <c r="H38" s="39">
-        <v>0</v>
+        <v>0.342623195248627</v>
       </c>
       <c r="I38" s="39">
-        <v>0.342623195248627</v>
+        <v>67.774471310355111</v>
       </c>
       <c r="J38" s="39">
-        <v>67.774471310355111</v>
+        <v>0.98422628662309575</v>
       </c>
       <c r="K38" s="39">
-        <v>0.98422628662309575</v>
+        <v>31.005069456524442</v>
       </c>
       <c r="L38" s="39">
-        <v>31.005069456524442</v>
+        <v>0.23623294649735344</v>
       </c>
       <c r="M38" s="39">
-        <v>0.23623294649735344</v>
+        <v>14.459466805414262</v>
       </c>
       <c r="N38" s="39">
-        <v>14.459466805414262</v>
+        <v>82.670477048403754</v>
       </c>
       <c r="O38" s="39">
-        <v>82.670477048403754</v>
+        <v>0.86323784081819666</v>
       </c>
       <c r="P38" s="39">
-        <v>0.86323784081819666</v>
-      </c>
-      <c r="Q38" s="39">
         <v>2.0068183053637854</v>
       </c>
-      <c r="R38" s="42">
+      <c r="Q38" s="42">
         <v>76.757380532292942</v>
       </c>
-      <c r="S38" s="43">
+      <c r="R38" s="43">
         <v>23.242619467707065</v>
       </c>
+      <c r="S38" s="39">
+        <v>41.515183519296237</v>
+      </c>
       <c r="T38" s="39">
-        <v>41.515183519296237</v>
+        <v>58.484816480703763</v>
       </c>
       <c r="U38" s="39">
-        <v>58.484816480703763</v>
+        <v>0</v>
       </c>
       <c r="V38" s="39">
         <v>0</v>
@@ -8725,109 +8621,103 @@
       <c r="Y38" s="39">
         <v>0</v>
       </c>
-      <c r="Z38" s="39">
-        <v>0</v>
-      </c>
-      <c r="AA38" s="40">
+      <c r="Z38" s="40">
         <v>83.039942679071032</v>
       </c>
+      <c r="AA38" s="41">
+        <v>3.5177308190978778</v>
+      </c>
       <c r="AB38" s="41">
-        <v>3.5177308190978778</v>
-      </c>
-      <c r="AC38" s="41">
         <v>13.442326501831085</v>
       </c>
     </row>
-    <row r="39" spans="1:29" s="38" customFormat="1">
+    <row r="39" spans="1:28" s="38" customFormat="1">
       <c r="A39" s="37">
         <v>2010</v>
       </c>
       <c r="B39" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="C39" s="59">
+      <c r="C39" s="44">
         <v>94.041215088995315</v>
       </c>
-      <c r="D39" s="59">
+      <c r="D39" s="44">
         <v>1.7931084146473195</v>
       </c>
-      <c r="E39" s="59">
+      <c r="E39" s="44">
         <v>3.6915949543321456</v>
       </c>
-      <c r="F39" s="59">
-        <v>0</v>
-      </c>
-      <c r="G39" s="59">
-        <v>0</v>
-      </c>
-      <c r="H39" s="59">
-        <v>0</v>
-      </c>
-      <c r="I39" s="59">
+      <c r="F39" s="44">
+        <v>0</v>
+      </c>
+      <c r="G39" s="44">
+        <v>0</v>
+      </c>
+      <c r="H39" s="44">
         <v>0.47408154202522834</v>
       </c>
-      <c r="J39" s="59">
+      <c r="I39" s="44">
         <v>57.906637893579585</v>
       </c>
-      <c r="K39" s="59">
+      <c r="J39" s="44">
         <v>2.3226506446339714</v>
       </c>
-      <c r="L39" s="59">
+      <c r="K39" s="44">
         <v>37.882537632653452</v>
       </c>
-      <c r="M39" s="59">
+      <c r="L39" s="44">
         <v>1.8881738291329906</v>
       </c>
-      <c r="N39" s="59">
+      <c r="M39" s="44">
         <v>13.006188279235896</v>
       </c>
-      <c r="O39" s="59">
+      <c r="N39" s="44">
         <v>83.709558947080382</v>
       </c>
-      <c r="P39" s="59">
+      <c r="O39" s="44">
         <v>1.2993466060480947</v>
       </c>
-      <c r="Q39" s="59">
+      <c r="P39" s="44">
         <v>1.9849061676356357</v>
       </c>
-      <c r="R39" s="60">
+      <c r="Q39" s="45">
         <v>73.848096343433525</v>
       </c>
-      <c r="S39" s="61">
+      <c r="R39" s="46">
         <v>26.151903656566482</v>
       </c>
-      <c r="T39" s="59">
-        <v>0</v>
-      </c>
-      <c r="U39" s="59">
-        <v>0</v>
-      </c>
-      <c r="V39" s="59">
-        <v>0</v>
-      </c>
-      <c r="W39" s="59">
-        <v>0</v>
-      </c>
-      <c r="X39" s="59">
-        <v>0</v>
-      </c>
-      <c r="Y39" s="59">
-        <v>0</v>
-      </c>
-      <c r="Z39" s="59">
-        <v>0</v>
-      </c>
-      <c r="AA39" s="62">
+      <c r="S39" s="44">
+        <v>0</v>
+      </c>
+      <c r="T39" s="44">
+        <v>0</v>
+      </c>
+      <c r="U39" s="44">
+        <v>0</v>
+      </c>
+      <c r="V39" s="44">
+        <v>0</v>
+      </c>
+      <c r="W39" s="44">
+        <v>0</v>
+      </c>
+      <c r="X39" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y39" s="44">
+        <v>0</v>
+      </c>
+      <c r="Z39" s="47">
         <v>39.136746224949022</v>
       </c>
-      <c r="AB39" s="63">
+      <c r="AA39" s="48">
         <v>58.435723076093893</v>
       </c>
-      <c r="AC39" s="63">
+      <c r="AB39" s="48">
         <v>2.4275306989570886</v>
       </c>
     </row>
-    <row r="40" spans="1:29" s="38" customFormat="1">
+    <row r="40" spans="1:28" s="38" customFormat="1">
       <c r="A40" s="37">
         <v>2011</v>
       </c>
@@ -8853,70 +8743,67 @@
         <v>0.17685119842194316</v>
       </c>
       <c r="I40" s="39">
-        <v>0</v>
+        <v>58.923505519214437</v>
       </c>
       <c r="J40" s="39">
-        <v>58.923505519214437</v>
+        <v>3.8515921214977684</v>
       </c>
       <c r="K40" s="39">
-        <v>3.8515921214977684</v>
+        <v>33.931836125712607</v>
       </c>
       <c r="L40" s="39">
-        <v>33.931836125712607</v>
+        <v>3.2930662335751961</v>
       </c>
       <c r="M40" s="39">
-        <v>3.2930662335751961</v>
+        <v>14.938662021085333</v>
       </c>
       <c r="N40" s="39">
-        <v>14.938662021085333</v>
+        <v>80.744151187355101</v>
       </c>
       <c r="O40" s="39">
-        <v>80.744151187355101</v>
+        <v>1.0401067568321369</v>
       </c>
       <c r="P40" s="39">
-        <v>1.0401067568321369</v>
-      </c>
-      <c r="Q40" s="39">
         <v>3.2770800347274367</v>
       </c>
-      <c r="R40" s="42">
+      <c r="Q40" s="42">
         <v>71.579140081154648</v>
       </c>
-      <c r="S40" s="43">
+      <c r="R40" s="43">
         <v>28.420859918845352</v>
       </c>
-      <c r="T40" s="59">
-        <v>0</v>
-      </c>
-      <c r="U40" s="59">
-        <v>0</v>
+      <c r="S40" s="44">
+        <v>0</v>
+      </c>
+      <c r="T40" s="44">
+        <v>0</v>
+      </c>
+      <c r="U40" s="39">
+        <v>4.3826462511583619</v>
       </c>
       <c r="V40" s="39">
-        <v>4.3826462511583619</v>
+        <v>16.747433183419343</v>
       </c>
       <c r="W40" s="39">
-        <v>16.747433183419343</v>
+        <v>30.867120659508203</v>
       </c>
       <c r="X40" s="39">
-        <v>30.867120659508203</v>
+        <v>46.088208371945392</v>
       </c>
       <c r="Y40" s="39">
-        <v>46.088208371945392</v>
-      </c>
-      <c r="Z40" s="39">
         <v>1.9145915339686965</v>
       </c>
-      <c r="AA40" s="40">
+      <c r="Z40" s="40">
+        <v>0</v>
+      </c>
+      <c r="AA40" s="41">
         <v>0</v>
       </c>
       <c r="AB40" s="41">
         <v>0</v>
       </c>
-      <c r="AC40" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:29" s="38" customFormat="1">
+    </row>
+    <row r="41" spans="1:28" s="38" customFormat="1">
       <c r="A41" s="37">
         <v>2011</v>
       </c>
@@ -8942,70 +8829,67 @@
         <v>9.9473567867172083E-2</v>
       </c>
       <c r="I41" s="39">
-        <v>0</v>
+        <v>56.133260060346522</v>
       </c>
       <c r="J41" s="39">
-        <v>56.133260060346522</v>
+        <v>2.7782213328079801</v>
       </c>
       <c r="K41" s="39">
-        <v>2.7782213328079801</v>
+        <v>38.571591510011096</v>
       </c>
       <c r="L41" s="39">
-        <v>38.571591510011096</v>
+        <v>2.5169270968343995</v>
       </c>
       <c r="M41" s="39">
-        <v>2.5169270968343995</v>
+        <v>11.231442974679924</v>
       </c>
       <c r="N41" s="39">
-        <v>11.231442974679924</v>
+        <v>84.660683209007047</v>
       </c>
       <c r="O41" s="39">
-        <v>84.660683209007047</v>
+        <v>1.3462779734135122</v>
       </c>
       <c r="P41" s="39">
-        <v>1.3462779734135122</v>
-      </c>
-      <c r="Q41" s="39">
         <v>2.7615958428995122</v>
       </c>
-      <c r="R41" s="42">
+      <c r="Q41" s="42">
         <v>69.172460843348887</v>
       </c>
-      <c r="S41" s="43">
+      <c r="R41" s="43">
         <v>30.827539156651117</v>
       </c>
-      <c r="T41" s="59">
-        <v>0</v>
-      </c>
-      <c r="U41" s="59">
-        <v>0</v>
+      <c r="S41" s="44">
+        <v>0</v>
+      </c>
+      <c r="T41" s="44">
+        <v>0</v>
+      </c>
+      <c r="U41" s="39">
+        <v>3.2645189386476989</v>
       </c>
       <c r="V41" s="39">
-        <v>3.2645189386476989</v>
+        <v>15.918003380234957</v>
       </c>
       <c r="W41" s="39">
-        <v>15.918003380234957</v>
+        <v>26.7652395715604</v>
       </c>
       <c r="X41" s="39">
-        <v>26.7652395715604</v>
+        <v>53.546032371452569</v>
       </c>
       <c r="Y41" s="39">
-        <v>53.546032371452569</v>
-      </c>
-      <c r="Z41" s="39">
         <v>0.50620573810437253</v>
       </c>
-      <c r="AA41" s="40">
+      <c r="Z41" s="40">
+        <v>0</v>
+      </c>
+      <c r="AA41" s="41">
         <v>0</v>
       </c>
       <c r="AB41" s="41">
         <v>0</v>
       </c>
-      <c r="AC41" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:29">
+    </row>
+    <row r="42" spans="1:28">
       <c r="A42" s="2">
         <v>2012</v>
       </c>
@@ -9031,70 +8915,67 @@
         <v>0.244845636149984</v>
       </c>
       <c r="I42" s="39">
-        <v>0</v>
+        <v>58.262578784317917</v>
       </c>
       <c r="J42" s="39">
-        <v>58.262578784317917</v>
+        <v>5.40796923405619</v>
       </c>
       <c r="K42" s="39">
-        <v>5.40796923405619</v>
+        <v>33.033935120891641</v>
       </c>
       <c r="L42" s="39">
-        <v>33.033935120891641</v>
+        <v>3.2955168607342524</v>
       </c>
       <c r="M42" s="39">
-        <v>3.2955168607342524</v>
+        <v>16.13407311913733</v>
       </c>
       <c r="N42" s="39">
-        <v>16.13407311913733</v>
+        <v>79.946581577054303</v>
       </c>
       <c r="O42" s="39">
-        <v>79.946581577054303</v>
+        <v>0.94814139500430905</v>
       </c>
       <c r="P42" s="39">
-        <v>0.94814139500430905</v>
-      </c>
-      <c r="Q42" s="39">
         <v>2.9712039088040685</v>
       </c>
-      <c r="R42" s="42">
+      <c r="Q42" s="42">
         <v>29.943809422070295</v>
       </c>
-      <c r="S42" s="43">
+      <c r="R42" s="43">
         <v>70.056190577929712</v>
       </c>
-      <c r="T42" s="59">
-        <v>0</v>
-      </c>
-      <c r="U42" s="59">
-        <v>0</v>
+      <c r="S42" s="44">
+        <v>0</v>
+      </c>
+      <c r="T42" s="44">
+        <v>0</v>
+      </c>
+      <c r="U42" s="39">
+        <v>2.4635544635544635</v>
       </c>
       <c r="V42" s="39">
-        <v>2.4635544635544635</v>
+        <v>16.659616137877006</v>
       </c>
       <c r="W42" s="39">
-        <v>16.659616137877006</v>
+        <v>29.582736887084714</v>
       </c>
       <c r="X42" s="39">
-        <v>29.582736887084714</v>
+        <v>46.528932094149482</v>
       </c>
       <c r="Y42" s="39">
-        <v>46.528932094149482</v>
-      </c>
-      <c r="Z42" s="39">
         <v>4.7651604173343305</v>
       </c>
-      <c r="AA42" s="40">
+      <c r="Z42" s="40">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="41">
         <v>0</v>
       </c>
       <c r="AB42" s="41">
         <v>0</v>
       </c>
-      <c r="AC42" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:29">
+    </row>
+    <row r="43" spans="1:28">
       <c r="A43" s="2">
         <v>2012</v>
       </c>
@@ -9120,70 +9001,67 @@
         <v>5.9526748632530685E-2</v>
       </c>
       <c r="I43" s="39">
-        <v>0</v>
+        <v>53.436915362290215</v>
       </c>
       <c r="J43" s="39">
-        <v>53.436915362290215</v>
+        <v>2.5569070230590714</v>
       </c>
       <c r="K43" s="39">
-        <v>2.5569070230590714</v>
+        <v>41.563386386205153</v>
       </c>
       <c r="L43" s="39">
-        <v>41.563386386205153</v>
+        <v>2.4427912284455564</v>
       </c>
       <c r="M43" s="39">
-        <v>2.4427912284455564</v>
+        <v>12.716504545429608</v>
       </c>
       <c r="N43" s="39">
-        <v>12.716504545429608</v>
+        <v>85.212952142688636</v>
       </c>
       <c r="O43" s="39">
-        <v>85.212952142688636</v>
+        <v>1.2443010681896736</v>
       </c>
       <c r="P43" s="39">
-        <v>1.2443010681896736</v>
-      </c>
-      <c r="Q43" s="39">
         <v>0.82624224369208488</v>
       </c>
-      <c r="R43" s="42">
+      <c r="Q43" s="42">
         <v>33.962616104591511</v>
       </c>
-      <c r="S43" s="43">
+      <c r="R43" s="43">
         <v>66.037383895408482</v>
       </c>
-      <c r="T43" s="59">
-        <v>0</v>
-      </c>
-      <c r="U43" s="59">
-        <v>0</v>
+      <c r="S43" s="44">
+        <v>0</v>
+      </c>
+      <c r="T43" s="44">
+        <v>0</v>
+      </c>
+      <c r="U43" s="39">
+        <v>3.1370870846157648</v>
       </c>
       <c r="V43" s="39">
-        <v>3.1370870846157648</v>
+        <v>20.752615610821248</v>
       </c>
       <c r="W43" s="39">
-        <v>20.752615610821248</v>
+        <v>21.282595695420557</v>
       </c>
       <c r="X43" s="39">
-        <v>21.282595695420557</v>
+        <v>52.87621179452573</v>
       </c>
       <c r="Y43" s="39">
-        <v>52.87621179452573</v>
-      </c>
-      <c r="Z43" s="39">
         <v>1.951489814616697</v>
       </c>
-      <c r="AA43" s="40">
+      <c r="Z43" s="40">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="41">
         <v>0</v>
       </c>
       <c r="AB43" s="41">
         <v>0</v>
       </c>
-      <c r="AC43" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:29">
+    </row>
+    <row r="44" spans="1:28">
       <c r="A44" s="2">
         <v>2013</v>
       </c>
@@ -9209,70 +9087,67 @@
         <v>0</v>
       </c>
       <c r="I44" s="39">
-        <v>0</v>
+        <v>60.21253535308189</v>
       </c>
       <c r="J44" s="39">
-        <v>60.21253535308189</v>
+        <v>3.5634623894514745</v>
       </c>
       <c r="K44" s="39">
-        <v>3.5634623894514745</v>
+        <v>34.35043321554317</v>
       </c>
       <c r="L44" s="39">
-        <v>34.35043321554317</v>
+        <v>1.8735690419234643</v>
       </c>
       <c r="M44" s="39">
-        <v>1.8735690419234643</v>
+        <v>9.4754110556295927</v>
       </c>
       <c r="N44" s="39">
-        <v>9.4754110556295927</v>
+        <v>87.12570818032448</v>
       </c>
       <c r="O44" s="39">
-        <v>87.12570818032448</v>
+        <v>1.4660631394786561</v>
       </c>
       <c r="P44" s="39">
-        <v>1.4660631394786561</v>
-      </c>
-      <c r="Q44" s="39">
         <v>1.9328176245672675</v>
       </c>
-      <c r="R44" s="42">
+      <c r="Q44" s="42">
         <v>75.445048003232287</v>
       </c>
-      <c r="S44" s="43">
+      <c r="R44" s="43">
         <v>24.55495199676772</v>
       </c>
-      <c r="T44" s="59">
-        <v>0</v>
-      </c>
-      <c r="U44" s="59">
-        <v>0</v>
+      <c r="S44" s="44">
+        <v>0</v>
+      </c>
+      <c r="T44" s="44">
+        <v>0</v>
+      </c>
+      <c r="U44" s="39">
+        <v>3.8266624766717756</v>
       </c>
       <c r="V44" s="39">
-        <v>3.8266624766717756</v>
+        <v>16.232724287647425</v>
       </c>
       <c r="W44" s="39">
-        <v>16.232724287647425</v>
+        <v>26.241766980702508</v>
       </c>
       <c r="X44" s="39">
-        <v>26.241766980702508</v>
+        <v>51.760759842746928</v>
       </c>
       <c r="Y44" s="39">
-        <v>51.760759842746928</v>
-      </c>
-      <c r="Z44" s="39">
         <v>1.9380864122313646</v>
       </c>
-      <c r="AA44" s="40">
+      <c r="Z44" s="40">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="41">
         <v>0</v>
       </c>
       <c r="AB44" s="41">
         <v>0</v>
       </c>
-      <c r="AC44" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:29">
+    </row>
+    <row r="45" spans="1:28">
       <c r="A45" s="2">
         <v>2013</v>
       </c>
@@ -9298,70 +9173,67 @@
         <v>0</v>
       </c>
       <c r="I45" s="39">
-        <v>0</v>
+        <v>59.752062607654381</v>
       </c>
       <c r="J45" s="39">
-        <v>59.752062607654381</v>
+        <v>2.5084168690364219</v>
       </c>
       <c r="K45" s="39">
-        <v>2.5084168690364219</v>
+        <v>35.379892898552988</v>
       </c>
       <c r="L45" s="39">
-        <v>35.379892898552988</v>
+        <v>2.3596276247562069</v>
       </c>
       <c r="M45" s="39">
-        <v>2.3596276247562069</v>
+        <v>10.059359312620501</v>
       </c>
       <c r="N45" s="39">
-        <v>10.059359312620501</v>
+        <v>87.377042221740652</v>
       </c>
       <c r="O45" s="39">
-        <v>87.377042221740652</v>
+        <v>1.0908977174478847</v>
       </c>
       <c r="P45" s="39">
-        <v>1.0908977174478847</v>
-      </c>
-      <c r="Q45" s="39">
         <v>1.4727007481909595</v>
       </c>
-      <c r="R45" s="42">
+      <c r="Q45" s="42">
         <v>71.339751079615652</v>
       </c>
-      <c r="S45" s="43">
+      <c r="R45" s="43">
         <v>28.660248920384351</v>
       </c>
-      <c r="T45" s="59">
-        <v>0</v>
-      </c>
-      <c r="U45" s="59">
-        <v>0</v>
+      <c r="S45" s="44">
+        <v>0</v>
+      </c>
+      <c r="T45" s="44">
+        <v>0</v>
+      </c>
+      <c r="U45" s="39">
+        <v>5.6021607951511685</v>
       </c>
       <c r="V45" s="39">
-        <v>5.6021607951511685</v>
+        <v>17.010453226336143</v>
       </c>
       <c r="W45" s="39">
-        <v>17.010453226336143</v>
+        <v>21.874699796475973</v>
       </c>
       <c r="X45" s="39">
-        <v>21.874699796475973</v>
+        <v>53.688789199598766</v>
       </c>
       <c r="Y45" s="39">
-        <v>53.688789199598766</v>
-      </c>
-      <c r="Z45" s="39">
         <v>1.8238969824379541</v>
       </c>
-      <c r="AA45" s="40">
+      <c r="Z45" s="40">
+        <v>0</v>
+      </c>
+      <c r="AA45" s="41">
         <v>0</v>
       </c>
       <c r="AB45" s="41">
         <v>0</v>
       </c>
-      <c r="AC45" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:29">
+    </row>
+    <row r="46" spans="1:28">
       <c r="A46" s="2">
         <v>2014</v>
       </c>
@@ -9387,70 +9259,67 @@
         <v>8.598333458725696E-2</v>
       </c>
       <c r="I46" s="39">
-        <v>0</v>
+        <v>56.890566246320759</v>
       </c>
       <c r="J46" s="39">
-        <v>56.890566246320759</v>
+        <v>1.8627675271653599</v>
       </c>
       <c r="K46" s="39">
-        <v>1.8627675271653599</v>
+        <v>39.591640577378087</v>
       </c>
       <c r="L46" s="39">
-        <v>39.591640577378087</v>
+        <v>1.6550256491357909</v>
       </c>
       <c r="M46" s="39">
-        <v>1.6550256491357909</v>
+        <v>12.905330813202742</v>
       </c>
       <c r="N46" s="39">
-        <v>12.905330813202742</v>
+        <v>81.652231190761711</v>
       </c>
       <c r="O46" s="39">
-        <v>81.652231190761711</v>
+        <v>1.4993343968652932</v>
       </c>
       <c r="P46" s="39">
-        <v>1.4993343968652932</v>
-      </c>
-      <c r="Q46" s="39">
         <v>3.9431035991702603</v>
       </c>
-      <c r="R46" s="42">
+      <c r="Q46" s="42">
         <v>70.056610813325577</v>
       </c>
-      <c r="S46" s="43">
+      <c r="R46" s="43">
         <v>29.943389186674423</v>
       </c>
-      <c r="T46" s="59">
-        <v>0</v>
-      </c>
-      <c r="U46" s="59">
-        <v>0</v>
+      <c r="S46" s="44">
+        <v>0</v>
+      </c>
+      <c r="T46" s="44">
+        <v>0</v>
+      </c>
+      <c r="U46" s="39">
+        <v>9.3922974286376704</v>
       </c>
       <c r="V46" s="39">
-        <v>9.3922974286376704</v>
+        <v>17.008424831372864</v>
       </c>
       <c r="W46" s="39">
-        <v>17.008424831372864</v>
+        <v>28.271934578965713</v>
       </c>
       <c r="X46" s="39">
-        <v>28.271934578965713</v>
+        <v>44.056939392497036</v>
       </c>
       <c r="Y46" s="39">
-        <v>44.056939392497036</v>
-      </c>
-      <c r="Z46" s="39">
         <v>1.2704037685267215</v>
       </c>
-      <c r="AA46" s="40">
+      <c r="Z46" s="40">
+        <v>0</v>
+      </c>
+      <c r="AA46" s="41">
         <v>0</v>
       </c>
       <c r="AB46" s="41">
         <v>0</v>
       </c>
-      <c r="AC46" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:29">
+    </row>
+    <row r="47" spans="1:28">
       <c r="A47" s="2">
         <v>2014</v>
       </c>
@@ -9476,70 +9345,67 @@
         <v>0.14314059409736754</v>
       </c>
       <c r="I47" s="39">
-        <v>0</v>
+        <v>61.060326731186443</v>
       </c>
       <c r="J47" s="39">
-        <v>61.060326731186443</v>
+        <v>0.93584553596247677</v>
       </c>
       <c r="K47" s="39">
-        <v>0.93584553596247677</v>
+        <v>37.23380801906837</v>
       </c>
       <c r="L47" s="39">
-        <v>37.23380801906837</v>
+        <v>0.77001971378271383</v>
       </c>
       <c r="M47" s="39">
-        <v>0.77001971378271383</v>
+        <v>8.8628949546135676</v>
       </c>
       <c r="N47" s="39">
-        <v>8.8628949546135676</v>
+        <v>88.762824342847281</v>
       </c>
       <c r="O47" s="39">
-        <v>88.762824342847281</v>
+        <v>0.74605644468159205</v>
       </c>
       <c r="P47" s="39">
-        <v>0.74605644468159205</v>
-      </c>
-      <c r="Q47" s="39">
         <v>1.6282242578575559</v>
       </c>
-      <c r="R47" s="42">
+      <c r="Q47" s="42">
         <v>68.789918812444284</v>
       </c>
-      <c r="S47" s="43">
+      <c r="R47" s="43">
         <v>31.210081187555716</v>
       </c>
-      <c r="T47" s="59">
-        <v>0</v>
-      </c>
-      <c r="U47" s="59">
-        <v>0</v>
+      <c r="S47" s="44">
+        <v>0</v>
+      </c>
+      <c r="T47" s="44">
+        <v>0</v>
+      </c>
+      <c r="U47" s="39">
+        <v>11.02725741982689</v>
       </c>
       <c r="V47" s="39">
-        <v>11.02725741982689</v>
+        <v>29.325290195188813</v>
       </c>
       <c r="W47" s="39">
-        <v>29.325290195188813</v>
+        <v>19.16454458605849</v>
       </c>
       <c r="X47" s="39">
-        <v>19.16454458605849</v>
+        <v>40.120902680371529</v>
       </c>
       <c r="Y47" s="39">
-        <v>40.120902680371529</v>
-      </c>
-      <c r="Z47" s="39">
         <v>0.36200511855427997</v>
       </c>
-      <c r="AA47" s="40">
+      <c r="Z47" s="40">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="41">
         <v>0</v>
       </c>
       <c r="AB47" s="41">
         <v>0</v>
       </c>
-      <c r="AC47" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:29">
+    </row>
+    <row r="48" spans="1:28">
       <c r="A48" s="2">
         <v>2015</v>
       </c>
@@ -9565,70 +9431,67 @@
         <v>0.29690950084516959</v>
       </c>
       <c r="I48" s="39">
-        <v>0</v>
+        <v>63.692135651660699</v>
       </c>
       <c r="J48" s="39">
-        <v>63.692135651660699</v>
+        <v>0.83002642934615189</v>
       </c>
       <c r="K48" s="39">
-        <v>0.83002642934615189</v>
+        <v>35.338702036949314</v>
       </c>
       <c r="L48" s="39">
-        <v>35.338702036949314</v>
+        <v>0.13913588204383492</v>
       </c>
       <c r="M48" s="39">
-        <v>0.13913588204383492</v>
+        <v>12.912715854760259</v>
       </c>
       <c r="N48" s="39">
-        <v>12.912715854760259</v>
+        <v>83.706476354665767</v>
       </c>
       <c r="O48" s="39">
-        <v>83.706476354665767</v>
+        <v>0.93421655496967482</v>
       </c>
       <c r="P48" s="39">
-        <v>0.93421655496967482</v>
-      </c>
-      <c r="Q48" s="39">
         <v>2.44659123560429</v>
       </c>
-      <c r="R48" s="42">
+      <c r="Q48" s="42">
         <v>71.872807800928257</v>
       </c>
-      <c r="S48" s="43">
+      <c r="R48" s="43">
         <v>28.127192199071736</v>
       </c>
-      <c r="T48" s="59">
-        <v>0</v>
-      </c>
-      <c r="U48" s="59">
-        <v>0</v>
+      <c r="S48" s="44">
+        <v>0</v>
+      </c>
+      <c r="T48" s="44">
+        <v>0</v>
+      </c>
+      <c r="U48" s="39">
+        <v>11.800146513319511</v>
       </c>
       <c r="V48" s="39">
-        <v>11.800146513319511</v>
+        <v>16.400172916779919</v>
       </c>
       <c r="W48" s="39">
-        <v>16.400172916779919</v>
+        <v>22.934899938650783</v>
       </c>
       <c r="X48" s="39">
-        <v>22.934899938650783</v>
+        <v>48.266172766642597</v>
       </c>
       <c r="Y48" s="39">
-        <v>48.266172766642597</v>
-      </c>
-      <c r="Z48" s="39">
         <v>0.59860786460719673</v>
       </c>
-      <c r="AA48" s="40">
+      <c r="Z48" s="40">
+        <v>0</v>
+      </c>
+      <c r="AA48" s="41">
         <v>0</v>
       </c>
       <c r="AB48" s="41">
         <v>0</v>
       </c>
-      <c r="AC48" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:29">
+    </row>
+    <row r="49" spans="1:28">
       <c r="A49" s="11">
         <v>2015</v>
       </c>
@@ -9654,70 +9517,67 @@
         <v>0</v>
       </c>
       <c r="I49" s="39">
-        <v>0</v>
+        <v>60.838385393478156</v>
       </c>
       <c r="J49" s="39">
-        <v>60.838385393478156</v>
+        <v>0.14376006424472915</v>
       </c>
       <c r="K49" s="39">
-        <v>0.14376006424472915</v>
+        <v>38.741360873129146</v>
       </c>
       <c r="L49" s="39">
-        <v>38.741360873129146</v>
+        <v>0.2764936691479668</v>
       </c>
       <c r="M49" s="39">
-        <v>0.2764936691479668</v>
+        <v>9.968335337513679</v>
       </c>
       <c r="N49" s="39">
-        <v>9.968335337513679</v>
+        <v>88.032754825636303</v>
       </c>
       <c r="O49" s="39">
-        <v>88.032754825636303</v>
+        <v>0.96554335478985232</v>
       </c>
       <c r="P49" s="39">
-        <v>0.96554335478985232</v>
-      </c>
-      <c r="Q49" s="39">
         <v>1.0333664820601587</v>
       </c>
-      <c r="R49" s="42">
+      <c r="Q49" s="42">
         <v>68.741652138092874</v>
       </c>
-      <c r="S49" s="43">
+      <c r="R49" s="43">
         <v>31.258347861907122</v>
       </c>
-      <c r="T49" s="59">
-        <v>0</v>
-      </c>
-      <c r="U49" s="59">
-        <v>0</v>
+      <c r="S49" s="44">
+        <v>0</v>
+      </c>
+      <c r="T49" s="44">
+        <v>0</v>
+      </c>
+      <c r="U49" s="39">
+        <v>5.7447853169170848</v>
       </c>
       <c r="V49" s="39">
-        <v>5.7447853169170848</v>
+        <v>22.245985744660491</v>
       </c>
       <c r="W49" s="39">
-        <v>22.245985744660491</v>
+        <v>18.564604649421007</v>
       </c>
       <c r="X49" s="39">
-        <v>18.564604649421007</v>
+        <v>53.018545256333972</v>
       </c>
       <c r="Y49" s="39">
-        <v>53.018545256333972</v>
-      </c>
-      <c r="Z49" s="39">
         <v>0.42607903266744612</v>
       </c>
-      <c r="AA49" s="40">
+      <c r="Z49" s="40">
+        <v>0</v>
+      </c>
+      <c r="AA49" s="41">
         <v>0</v>
       </c>
       <c r="AB49" s="41">
         <v>0</v>
       </c>
-      <c r="AC49" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:29">
+    </row>
+    <row r="50" spans="1:28">
       <c r="A50" s="2">
         <v>2016</v>
       </c>
@@ -9743,70 +9603,67 @@
         <v>0</v>
       </c>
       <c r="I50" s="39">
-        <v>0</v>
+        <v>68.274945271525979</v>
       </c>
       <c r="J50" s="39">
-        <v>68.274945271525979</v>
+        <v>0.15304131586431308</v>
       </c>
       <c r="K50" s="39">
-        <v>0.15304131586431308</v>
+        <v>31.230745828400607</v>
       </c>
       <c r="L50" s="39">
-        <v>31.230745828400607</v>
+        <v>0.34126758420909914</v>
       </c>
       <c r="M50" s="39">
-        <v>0.34126758420909914</v>
+        <v>17.320255818413898</v>
       </c>
       <c r="N50" s="39">
-        <v>17.320255818413898</v>
+        <v>79.461114675167494</v>
       </c>
       <c r="O50" s="39">
-        <v>79.461114675167494</v>
+        <v>1.2817375546458025</v>
       </c>
       <c r="P50" s="39">
-        <v>1.2817375546458025</v>
-      </c>
-      <c r="Q50" s="39">
         <v>1.9368919517728056</v>
       </c>
-      <c r="R50" s="42">
+      <c r="Q50" s="42">
         <v>69.451260242987814</v>
       </c>
-      <c r="S50" s="43">
+      <c r="R50" s="43">
         <v>30.548739757012189</v>
       </c>
-      <c r="T50" s="59">
-        <v>0</v>
-      </c>
-      <c r="U50" s="59">
-        <v>0</v>
+      <c r="S50" s="44">
+        <v>0</v>
+      </c>
+      <c r="T50" s="44">
+        <v>0</v>
+      </c>
+      <c r="U50" s="39">
+        <v>13.424249839617463</v>
       </c>
       <c r="V50" s="39">
-        <v>13.424249839617463</v>
+        <v>17.542741119437043</v>
       </c>
       <c r="W50" s="39">
-        <v>17.542741119437043</v>
+        <v>27.854313132849651</v>
       </c>
       <c r="X50" s="39">
-        <v>27.854313132849651</v>
+        <v>40.050793314859028</v>
       </c>
       <c r="Y50" s="39">
-        <v>40.050793314859028</v>
-      </c>
-      <c r="Z50" s="39">
         <v>1.1279025932368172</v>
       </c>
-      <c r="AA50" s="40">
+      <c r="Z50" s="40">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="41">
         <v>0</v>
       </c>
       <c r="AB50" s="41">
         <v>0</v>
       </c>
-      <c r="AC50" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:29">
+    </row>
+    <row r="51" spans="1:28">
       <c r="A51" s="2">
         <v>2016</v>
       </c>
@@ -9832,70 +9689,67 @@
         <v>0</v>
       </c>
       <c r="I51" s="39">
-        <v>0</v>
+        <v>55.257475643494466</v>
       </c>
       <c r="J51" s="39">
-        <v>55.257475643494466</v>
+        <v>0.12119859440773595</v>
       </c>
       <c r="K51" s="39">
-        <v>0.12119859440773595</v>
+        <v>44.536979845218752</v>
       </c>
       <c r="L51" s="39">
-        <v>44.536979845218752</v>
+        <v>8.4345916879045357E-2</v>
       </c>
       <c r="M51" s="39">
-        <v>8.4345916879045357E-2</v>
+        <v>9.7607690271412189</v>
       </c>
       <c r="N51" s="39">
-        <v>9.7607690271412189</v>
+        <v>86.86643240128933</v>
       </c>
       <c r="O51" s="39">
-        <v>86.86643240128933</v>
+        <v>1.4307662761666986</v>
       </c>
       <c r="P51" s="39">
-        <v>1.4307662761666986</v>
-      </c>
-      <c r="Q51" s="39">
         <v>1.9420322954027582</v>
       </c>
-      <c r="R51" s="42">
+      <c r="Q51" s="42">
         <v>60.574123191753301</v>
       </c>
-      <c r="S51" s="43">
+      <c r="R51" s="43">
         <v>39.425876808246699</v>
       </c>
-      <c r="T51" s="59">
-        <v>0</v>
-      </c>
-      <c r="U51" s="59">
-        <v>0</v>
+      <c r="S51" s="44">
+        <v>0</v>
+      </c>
+      <c r="T51" s="44">
+        <v>0</v>
+      </c>
+      <c r="U51" s="39">
+        <v>9.4698404953830355</v>
       </c>
       <c r="V51" s="39">
-        <v>9.4698404953830355</v>
+        <v>16.021831318547278</v>
       </c>
       <c r="W51" s="39">
-        <v>16.021831318547278</v>
+        <v>23.587011247852423</v>
       </c>
       <c r="X51" s="39">
-        <v>23.587011247852423</v>
+        <v>49.45084319964289</v>
       </c>
       <c r="Y51" s="39">
-        <v>49.45084319964289</v>
-      </c>
-      <c r="Z51" s="39">
         <v>1.4704737385743725</v>
       </c>
-      <c r="AA51" s="40">
+      <c r="Z51" s="40">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="41">
         <v>0</v>
       </c>
       <c r="AB51" s="41">
         <v>0</v>
       </c>
-      <c r="AC51" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:29">
+    </row>
+    <row r="52" spans="1:28">
       <c r="A52" s="2">
         <v>2017</v>
       </c>
@@ -9921,70 +9775,67 @@
         <v>0</v>
       </c>
       <c r="I52" s="39">
-        <v>0</v>
+        <v>56.927395513089898</v>
       </c>
       <c r="J52" s="39">
-        <v>56.927395513089898</v>
+        <v>0.54464423948864271</v>
       </c>
       <c r="K52" s="39">
-        <v>0.54464423948864271</v>
+        <v>42.329824018165866</v>
       </c>
       <c r="L52" s="39">
-        <v>42.329824018165866</v>
+        <v>0.1981362292555976</v>
       </c>
       <c r="M52" s="39">
-        <v>0.1981362292555976</v>
+        <v>14.320918025051792</v>
       </c>
       <c r="N52" s="39">
-        <v>14.320918025051792</v>
+        <v>77.596229697948232</v>
       </c>
       <c r="O52" s="39">
-        <v>77.596229697948232</v>
+        <v>1.7013911927985312</v>
       </c>
       <c r="P52" s="39">
-        <v>1.7013911927985312</v>
-      </c>
-      <c r="Q52" s="39">
         <v>6.3814610842014465</v>
       </c>
-      <c r="R52" s="42">
+      <c r="Q52" s="42">
         <v>58.392866358495709</v>
       </c>
-      <c r="S52" s="43">
+      <c r="R52" s="43">
         <v>41.607133641504284</v>
       </c>
-      <c r="T52" s="59">
-        <v>0</v>
-      </c>
-      <c r="U52" s="59">
-        <v>0</v>
+      <c r="S52" s="44">
+        <v>0</v>
+      </c>
+      <c r="T52" s="44">
+        <v>0</v>
+      </c>
+      <c r="U52" s="39">
+        <v>4.3020443972603752</v>
       </c>
       <c r="V52" s="39">
-        <v>4.3020443972603752</v>
+        <v>22.732031347916159</v>
       </c>
       <c r="W52" s="39">
-        <v>22.732031347916159</v>
+        <v>30.607716069861912</v>
       </c>
       <c r="X52" s="39">
-        <v>30.607716069861912</v>
+        <v>41.456918732812838</v>
       </c>
       <c r="Y52" s="39">
-        <v>41.456918732812838</v>
-      </c>
-      <c r="Z52" s="39">
         <v>0.90128945214871825</v>
       </c>
-      <c r="AA52" s="40">
+      <c r="Z52" s="40">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="41">
         <v>0</v>
       </c>
       <c r="AB52" s="41">
         <v>0</v>
       </c>
-      <c r="AC52" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:29">
+    </row>
+    <row r="53" spans="1:28">
       <c r="A53" s="2">
         <v>2017</v>
       </c>
@@ -10010,70 +9861,67 @@
         <v>0</v>
       </c>
       <c r="I53" s="39">
-        <v>0</v>
+        <v>53.020395547580911</v>
       </c>
       <c r="J53" s="39">
-        <v>53.020395547580911</v>
+        <v>0.8525908888380439</v>
       </c>
       <c r="K53" s="39">
-        <v>0.8525908888380439</v>
+        <v>45.833985621560437</v>
       </c>
       <c r="L53" s="39">
-        <v>45.833985621560437</v>
+        <v>0.29302794202060833</v>
       </c>
       <c r="M53" s="39">
-        <v>0.29302794202060833</v>
+        <v>7.8395009694006577</v>
       </c>
       <c r="N53" s="39">
-        <v>7.8395009694006577</v>
+        <v>88.528558182102813</v>
       </c>
       <c r="O53" s="39">
-        <v>88.528558182102813</v>
+        <v>1.2648370483656668</v>
       </c>
       <c r="P53" s="39">
-        <v>1.2648370483656668</v>
-      </c>
-      <c r="Q53" s="39">
         <v>2.3671038001308591</v>
       </c>
-      <c r="R53" s="42">
+      <c r="Q53" s="42">
         <v>61.445952401022787</v>
       </c>
-      <c r="S53" s="43">
+      <c r="R53" s="43">
         <v>38.554047598977213</v>
       </c>
-      <c r="T53" s="59">
-        <v>0</v>
-      </c>
-      <c r="U53" s="59">
-        <v>0</v>
+      <c r="S53" s="44">
+        <v>0</v>
+      </c>
+      <c r="T53" s="44">
+        <v>0</v>
+      </c>
+      <c r="U53" s="39">
+        <v>5.5097281262669444</v>
       </c>
       <c r="V53" s="39">
-        <v>5.5097281262669444</v>
+        <v>28.964808548387744</v>
       </c>
       <c r="W53" s="39">
-        <v>28.964808548387744</v>
+        <v>17.205155686147002</v>
       </c>
       <c r="X53" s="39">
-        <v>17.205155686147002</v>
+        <v>47.391449203806957</v>
       </c>
       <c r="Y53" s="39">
-        <v>47.391449203806957</v>
-      </c>
-      <c r="Z53" s="39">
         <v>0.92885843539135293</v>
       </c>
-      <c r="AA53" s="40">
+      <c r="Z53" s="40">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="41">
         <v>0</v>
       </c>
       <c r="AB53" s="41">
         <v>0</v>
       </c>
-      <c r="AC53" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:29">
+    </row>
+    <row r="54" spans="1:28">
       <c r="A54" s="2">
         <v>2018</v>
       </c>
@@ -10099,70 +9947,67 @@
         <v>0</v>
       </c>
       <c r="I54" s="39">
-        <v>0</v>
+        <v>62.503391082913282</v>
       </c>
       <c r="J54" s="39">
-        <v>62.503391082913282</v>
+        <v>0.4397541333741013</v>
       </c>
       <c r="K54" s="39">
-        <v>0.4397541333741013</v>
+        <v>35.836964227634965</v>
       </c>
       <c r="L54" s="39">
-        <v>35.836964227634965</v>
+        <v>1.219890556077645</v>
       </c>
       <c r="M54" s="39">
-        <v>1.219890556077645</v>
+        <v>15.385699147620397</v>
       </c>
       <c r="N54" s="39">
-        <v>15.385699147620397</v>
+        <v>80.482050866993106</v>
       </c>
       <c r="O54" s="39">
-        <v>80.482050866993106</v>
+        <v>1.4814348514893037</v>
       </c>
       <c r="P54" s="39">
-        <v>1.4814348514893037</v>
-      </c>
-      <c r="Q54" s="39">
         <v>2.6508151338971899</v>
       </c>
-      <c r="R54" s="42">
+      <c r="Q54" s="42">
         <v>73.721917711719726</v>
       </c>
-      <c r="S54" s="43">
+      <c r="R54" s="43">
         <v>26.27808228828027</v>
       </c>
-      <c r="T54" s="59">
-        <v>0</v>
-      </c>
-      <c r="U54" s="59">
-        <v>0</v>
+      <c r="S54" s="44">
+        <v>0</v>
+      </c>
+      <c r="T54" s="44">
+        <v>0</v>
+      </c>
+      <c r="U54" s="39">
+        <v>7.132889982029134</v>
       </c>
       <c r="V54" s="39">
-        <v>7.132889982029134</v>
+        <v>25.775977193936967</v>
       </c>
       <c r="W54" s="39">
-        <v>25.775977193936967</v>
+        <v>21.235298437778688</v>
       </c>
       <c r="X54" s="39">
-        <v>21.235298437778688</v>
+        <v>45.134301871578003</v>
       </c>
       <c r="Y54" s="39">
-        <v>45.134301871578003</v>
-      </c>
-      <c r="Z54" s="39">
         <v>0.72153251467720636</v>
       </c>
-      <c r="AA54" s="40">
+      <c r="Z54" s="40">
+        <v>0</v>
+      </c>
+      <c r="AA54" s="41">
         <v>0</v>
       </c>
       <c r="AB54" s="41">
         <v>0</v>
       </c>
-      <c r="AC54" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:29">
+    </row>
+    <row r="55" spans="1:28">
       <c r="A55" s="2">
         <v>2018</v>
       </c>
@@ -10188,70 +10033,67 @@
         <v>0</v>
       </c>
       <c r="I55" s="39">
-        <v>0</v>
+        <v>64.098640047302695</v>
       </c>
       <c r="J55" s="39">
-        <v>64.098640047302695</v>
+        <v>0.53911168307189317</v>
       </c>
       <c r="K55" s="39">
-        <v>0.53911168307189317</v>
+        <v>35.035838218336217</v>
       </c>
       <c r="L55" s="39">
-        <v>35.035838218336217</v>
+        <v>0.32641005128918593</v>
       </c>
       <c r="M55" s="39">
-        <v>0.32641005128918593</v>
+        <v>12.815607751436071</v>
       </c>
       <c r="N55" s="39">
-        <v>12.815607751436071</v>
+        <v>83.54920096424739</v>
       </c>
       <c r="O55" s="39">
-        <v>83.54920096424739</v>
+        <v>0.85990320069134707</v>
       </c>
       <c r="P55" s="39">
-        <v>0.85990320069134707</v>
-      </c>
-      <c r="Q55" s="39">
         <v>2.7752880836251848</v>
       </c>
-      <c r="R55" s="42">
+      <c r="Q55" s="42">
         <v>69.686673105684619</v>
       </c>
-      <c r="S55" s="43">
+      <c r="R55" s="43">
         <v>30.313326894315384</v>
       </c>
-      <c r="T55" s="59">
-        <v>0</v>
-      </c>
-      <c r="U55" s="59">
-        <v>0</v>
+      <c r="S55" s="44">
+        <v>0</v>
+      </c>
+      <c r="T55" s="44">
+        <v>0</v>
+      </c>
+      <c r="U55" s="39">
+        <v>2.4852647265780723</v>
       </c>
       <c r="V55" s="39">
-        <v>2.4852647265780723</v>
+        <v>21.025355639803834</v>
       </c>
       <c r="W55" s="39">
-        <v>21.025355639803834</v>
+        <v>31.269547815059273</v>
       </c>
       <c r="X55" s="39">
-        <v>31.269547815059273</v>
+        <v>44.891548922713056</v>
       </c>
       <c r="Y55" s="39">
-        <v>44.891548922713056</v>
-      </c>
-      <c r="Z55" s="39">
         <v>0.3282828958457632</v>
       </c>
-      <c r="AA55" s="40">
+      <c r="Z55" s="40">
+        <v>0</v>
+      </c>
+      <c r="AA55" s="41">
         <v>0</v>
       </c>
       <c r="AB55" s="41">
         <v>0</v>
       </c>
-      <c r="AC55" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:29">
+    </row>
+    <row r="56" spans="1:28">
       <c r="A56" s="2">
         <v>2019</v>
       </c>
@@ -10277,70 +10119,67 @@
         <v>0</v>
       </c>
       <c r="I56" s="39">
-        <v>0</v>
+        <v>66.751467527241658</v>
       </c>
       <c r="J56" s="39">
-        <v>66.751467527241658</v>
+        <v>0.16657152749833898</v>
       </c>
       <c r="K56" s="39">
-        <v>0.16657152749833898</v>
+        <v>32.8569690666246</v>
       </c>
       <c r="L56" s="39">
-        <v>32.8569690666246</v>
+        <v>0.22499187863539685</v>
       </c>
       <c r="M56" s="39">
-        <v>0.22499187863539685</v>
+        <v>12.449416932811248</v>
       </c>
       <c r="N56" s="39">
-        <v>12.449416932811248</v>
+        <v>84.307384626490759</v>
       </c>
       <c r="O56" s="39">
-        <v>84.307384626490759</v>
+        <v>1.5949959025543197</v>
       </c>
       <c r="P56" s="39">
-        <v>1.5949959025543197</v>
-      </c>
-      <c r="Q56" s="39">
         <v>1.6482025381436765</v>
       </c>
-      <c r="R56" s="42">
+      <c r="Q56" s="42">
         <v>74.244779934414126</v>
       </c>
-      <c r="S56" s="43">
+      <c r="R56" s="43">
         <v>25.755220065585867</v>
       </c>
-      <c r="T56" s="59">
-        <v>0</v>
-      </c>
-      <c r="U56" s="59">
-        <v>0</v>
+      <c r="S56" s="44">
+        <v>0</v>
+      </c>
+      <c r="T56" s="44">
+        <v>0</v>
+      </c>
+      <c r="U56" s="39">
+        <v>5.1409909000610936</v>
       </c>
       <c r="V56" s="39">
-        <v>5.1409909000610936</v>
+        <v>18.840362714180102</v>
       </c>
       <c r="W56" s="39">
-        <v>18.840362714180102</v>
+        <v>32.897074570837681</v>
       </c>
       <c r="X56" s="39">
-        <v>32.897074570837681</v>
+        <v>42.085245586055045</v>
       </c>
       <c r="Y56" s="39">
-        <v>42.085245586055045</v>
-      </c>
-      <c r="Z56" s="39">
         <v>1.0363262288660702</v>
       </c>
-      <c r="AA56" s="40">
+      <c r="Z56" s="40">
+        <v>0</v>
+      </c>
+      <c r="AA56" s="41">
         <v>0</v>
       </c>
       <c r="AB56" s="41">
         <v>0</v>
       </c>
-      <c r="AC56" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:29">
+    </row>
+    <row r="57" spans="1:28">
       <c r="A57" s="2">
         <v>2019</v>
       </c>
@@ -10366,70 +10205,67 @@
         <v>4.4455769220343395E-2</v>
       </c>
       <c r="I57" s="39">
-        <v>0</v>
+        <v>65.263779933099485</v>
       </c>
       <c r="J57" s="39">
-        <v>65.263779933099485</v>
+        <v>0.20032203325508394</v>
       </c>
       <c r="K57" s="39">
-        <v>0.20032203325508394</v>
+        <v>34.380302841374224</v>
       </c>
       <c r="L57" s="39">
-        <v>34.380302841374224</v>
+        <v>0.15559519227120189</v>
       </c>
       <c r="M57" s="39">
-        <v>0.15559519227120189</v>
+        <v>8.6696882132575777</v>
       </c>
       <c r="N57" s="39">
-        <v>8.6696882132575777</v>
+        <v>89.408141911489651</v>
       </c>
       <c r="O57" s="39">
-        <v>89.408141911489651</v>
+        <v>0.69963622169333106</v>
       </c>
       <c r="P57" s="39">
-        <v>0.69963622169333106</v>
-      </c>
-      <c r="Q57" s="39">
         <v>1.2225336535594433</v>
       </c>
-      <c r="R57" s="42">
+      <c r="Q57" s="42">
         <v>59.425275204861926</v>
       </c>
-      <c r="S57" s="43">
+      <c r="R57" s="43">
         <v>40.574724795138067</v>
       </c>
-      <c r="T57" s="59">
-        <v>0</v>
-      </c>
-      <c r="U57" s="59">
-        <v>0</v>
+      <c r="S57" s="44">
+        <v>0</v>
+      </c>
+      <c r="T57" s="44">
+        <v>0</v>
+      </c>
+      <c r="U57" s="39">
+        <v>3.9909895745799742</v>
       </c>
       <c r="V57" s="39">
-        <v>3.9909895745799742</v>
+        <v>23.60465809718465</v>
       </c>
       <c r="W57" s="39">
-        <v>23.60465809718465</v>
+        <v>33.68473269613397</v>
       </c>
       <c r="X57" s="39">
-        <v>33.68473269613397</v>
+        <v>36.477585075872987</v>
       </c>
       <c r="Y57" s="39">
-        <v>36.477585075872987</v>
-      </c>
-      <c r="Z57" s="39">
         <v>2.2420345562284156</v>
       </c>
-      <c r="AA57" s="40">
+      <c r="Z57" s="40">
+        <v>0</v>
+      </c>
+      <c r="AA57" s="41">
         <v>0</v>
       </c>
       <c r="AB57" s="41">
         <v>0</v>
       </c>
-      <c r="AC57" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:29">
+    </row>
+    <row r="58" spans="1:28">
       <c r="A58" s="2">
         <v>2020</v>
       </c>
@@ -10455,70 +10291,67 @@
         <v>2.339653943912114E-2</v>
       </c>
       <c r="I58" s="39">
-        <v>0</v>
+        <v>69.718895896034283</v>
       </c>
       <c r="J58" s="39">
-        <v>69.718895896034283</v>
+        <v>0.13133966457870277</v>
       </c>
       <c r="K58" s="39">
-        <v>0.13133966457870277</v>
+        <v>29.966314300602992</v>
       </c>
       <c r="L58" s="39">
-        <v>29.966314300602992</v>
+        <v>0.18345013878401803</v>
       </c>
       <c r="M58" s="39">
-        <v>0.18345013878401803</v>
+        <v>13.145000053173952</v>
       </c>
       <c r="N58" s="39">
-        <v>13.145000053173952</v>
+        <v>83.046814348459549</v>
       </c>
       <c r="O58" s="39">
-        <v>83.046814348459549</v>
+        <v>1.3087439248758388</v>
       </c>
       <c r="P58" s="39">
-        <v>1.3087439248758388</v>
-      </c>
-      <c r="Q58" s="39">
         <v>2.4994416734906575</v>
       </c>
-      <c r="R58" s="42">
+      <c r="Q58" s="42">
         <v>71.317304931352425</v>
       </c>
-      <c r="S58" s="43">
+      <c r="R58" s="43">
         <v>28.682695068647572</v>
       </c>
-      <c r="T58" s="59">
-        <v>0</v>
-      </c>
-      <c r="U58" s="59">
-        <v>0</v>
+      <c r="S58" s="44">
+        <v>0</v>
+      </c>
+      <c r="T58" s="44">
+        <v>0</v>
+      </c>
+      <c r="U58" s="39">
+        <v>2.8087811466431285</v>
       </c>
       <c r="V58" s="39">
-        <v>2.8087811466431285</v>
+        <v>18.776387574310601</v>
       </c>
       <c r="W58" s="39">
-        <v>18.776387574310601</v>
+        <v>25.644468313641244</v>
       </c>
       <c r="X58" s="39">
-        <v>25.644468313641244</v>
+        <v>52.343774925290596</v>
       </c>
       <c r="Y58" s="39">
-        <v>52.343774925290596</v>
-      </c>
-      <c r="Z58" s="39">
         <v>0.4265880401144303</v>
       </c>
-      <c r="AA58" s="40">
+      <c r="Z58" s="40">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="41">
         <v>0</v>
       </c>
       <c r="AB58" s="41">
         <v>0</v>
       </c>
-      <c r="AC58" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:29">
+    </row>
+    <row r="59" spans="1:28">
       <c r="A59" s="2">
         <v>2020</v>
       </c>
@@ -10544,70 +10377,67 @@
         <v>0.10346203250286055</v>
       </c>
       <c r="I59" s="39">
-        <v>0</v>
+        <v>54.859646738534785</v>
       </c>
       <c r="J59" s="39">
-        <v>54.859646738534785</v>
+        <v>0.42787688018132164</v>
       </c>
       <c r="K59" s="39">
-        <v>0.42787688018132164</v>
+        <v>44.28547629798819</v>
       </c>
       <c r="L59" s="39">
-        <v>44.28547629798819</v>
+        <v>0.42700008329570416</v>
       </c>
       <c r="M59" s="39">
-        <v>0.42700008329570416</v>
+        <v>7.1127955353502585</v>
       </c>
       <c r="N59" s="39">
-        <v>7.1127955353502585</v>
+        <v>90.569830295962788</v>
       </c>
       <c r="O59" s="39">
-        <v>90.569830295962788</v>
+        <v>1.0795561654165005</v>
       </c>
       <c r="P59" s="39">
-        <v>1.0795561654165005</v>
-      </c>
-      <c r="Q59" s="39">
         <v>1.2378180032704524</v>
       </c>
-      <c r="R59" s="42">
+      <c r="Q59" s="42">
         <v>70.768468630399425</v>
       </c>
-      <c r="S59" s="43">
+      <c r="R59" s="43">
         <v>29.231531369600578</v>
       </c>
-      <c r="T59" s="59">
-        <v>0</v>
-      </c>
-      <c r="U59" s="59">
-        <v>0</v>
+      <c r="S59" s="44">
+        <v>0</v>
+      </c>
+      <c r="T59" s="44">
+        <v>0</v>
+      </c>
+      <c r="U59" s="39">
+        <v>2.1325892250430729</v>
       </c>
       <c r="V59" s="39">
-        <v>2.1325892250430729</v>
+        <v>25.760073300219638</v>
       </c>
       <c r="W59" s="39">
-        <v>25.760073300219638</v>
+        <v>15.490151378982302</v>
       </c>
       <c r="X59" s="39">
-        <v>15.490151378982302</v>
+        <v>56.216051520584998</v>
       </c>
       <c r="Y59" s="39">
-        <v>56.216051520584998</v>
-      </c>
-      <c r="Z59" s="39">
         <v>0.40113457516998902</v>
       </c>
-      <c r="AA59" s="40">
+      <c r="Z59" s="40">
+        <v>0</v>
+      </c>
+      <c r="AA59" s="41">
         <v>0</v>
       </c>
       <c r="AB59" s="41">
         <v>0</v>
       </c>
-      <c r="AC59" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:29">
+    </row>
+    <row r="60" spans="1:28">
       <c r="A60" s="2">
         <v>2021</v>
       </c>
@@ -10633,70 +10463,67 @@
         <v>0.38260801828001662</v>
       </c>
       <c r="I60" s="39">
-        <v>0</v>
+        <v>65.883361030328217</v>
       </c>
       <c r="J60" s="39">
-        <v>65.883361030328217</v>
+        <v>0.25641358537598669</v>
       </c>
       <c r="K60" s="39">
-        <v>0.25641358537598669</v>
+        <v>33.801282717075196</v>
       </c>
       <c r="L60" s="39">
-        <v>33.801282717075196</v>
+        <v>5.8942667220606565E-2</v>
       </c>
       <c r="M60" s="39">
-        <v>5.8942667220606565E-2</v>
+        <v>12.573483589530534</v>
       </c>
       <c r="N60" s="39">
-        <v>12.573483589530534</v>
+        <v>85.17371208973826</v>
       </c>
       <c r="O60" s="39">
-        <v>85.17371208973826</v>
+        <v>0.70276796842542588</v>
       </c>
       <c r="P60" s="39">
-        <v>0.70276796842542588</v>
-      </c>
-      <c r="Q60" s="39">
         <v>1.5500363523057747</v>
       </c>
-      <c r="R60" s="42">
+      <c r="Q60" s="42">
         <v>70.752233070211872</v>
       </c>
-      <c r="S60" s="43">
+      <c r="R60" s="43">
         <v>29.247766929788117</v>
       </c>
-      <c r="T60" s="59">
-        <v>0</v>
-      </c>
-      <c r="U60" s="59">
-        <v>0</v>
+      <c r="S60" s="44">
+        <v>0</v>
+      </c>
+      <c r="T60" s="44">
+        <v>0</v>
+      </c>
+      <c r="U60" s="39">
+        <v>4.2412754466140425</v>
       </c>
       <c r="V60" s="39">
-        <v>4.2412754466140425</v>
+        <v>22.354850436227668</v>
       </c>
       <c r="W60" s="39">
-        <v>22.354850436227668</v>
+        <v>21.521084337349397</v>
       </c>
       <c r="X60" s="39">
-        <v>21.521084337349397</v>
+        <v>51.562370170336514</v>
       </c>
       <c r="Y60" s="39">
-        <v>51.562370170336514</v>
-      </c>
-      <c r="Z60" s="39">
         <v>0.32041960947237225</v>
       </c>
-      <c r="AA60" s="40">
+      <c r="Z60" s="40">
+        <v>0</v>
+      </c>
+      <c r="AA60" s="41">
         <v>0</v>
       </c>
       <c r="AB60" s="41">
         <v>0</v>
       </c>
-      <c r="AC60" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:29">
+    </row>
+    <row r="61" spans="1:28">
       <c r="A61" s="2">
         <v>2021</v>
       </c>
@@ -10722,70 +10549,67 @@
         <v>0.47041978834100745</v>
       </c>
       <c r="I61" s="39">
-        <v>0</v>
+        <v>67.0805855619612</v>
       </c>
       <c r="J61" s="39">
-        <v>67.0805855619612</v>
+        <v>0.94781909876422565</v>
       </c>
       <c r="K61" s="39">
-        <v>0.94781909876422565</v>
+        <v>31.534079012178267</v>
       </c>
       <c r="L61" s="39">
-        <v>31.534079012178267</v>
+        <v>0.43751632709629945</v>
       </c>
       <c r="M61" s="39">
-        <v>0.43751632709629945</v>
+        <v>13.729689631242673</v>
       </c>
       <c r="N61" s="39">
-        <v>13.729689631242673</v>
+        <v>83.252969282187493</v>
       </c>
       <c r="O61" s="39">
-        <v>83.252969282187493</v>
+        <v>1.5474566672250274</v>
       </c>
       <c r="P61" s="39">
-        <v>1.5474566672250274</v>
-      </c>
-      <c r="Q61" s="39">
         <v>1.4698844193448035</v>
       </c>
-      <c r="R61" s="42">
+      <c r="Q61" s="42">
         <v>62.958679235124151</v>
       </c>
-      <c r="S61" s="43">
+      <c r="R61" s="43">
         <v>37.041320764875856</v>
       </c>
-      <c r="T61" s="59">
-        <v>0</v>
-      </c>
-      <c r="U61" s="59">
-        <v>0</v>
+      <c r="S61" s="44">
+        <v>0</v>
+      </c>
+      <c r="T61" s="44">
+        <v>0</v>
+      </c>
+      <c r="U61" s="39">
+        <v>3.3890565082049267</v>
       </c>
       <c r="V61" s="39">
-        <v>3.3890565082049267</v>
+        <v>22.584935798367589</v>
       </c>
       <c r="W61" s="39">
-        <v>22.584935798367589</v>
+        <v>21.307882672239646</v>
       </c>
       <c r="X61" s="39">
-        <v>21.307882672239646</v>
+        <v>52.243318104680867</v>
       </c>
       <c r="Y61" s="39">
-        <v>52.243318104680867</v>
-      </c>
-      <c r="Z61" s="39">
         <v>0.4748069165069686</v>
       </c>
-      <c r="AA61" s="40">
+      <c r="Z61" s="40">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="41">
         <v>0</v>
       </c>
       <c r="AB61" s="41">
         <v>0</v>
       </c>
-      <c r="AC61" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:29">
+    </row>
+    <row r="62" spans="1:28">
       <c r="A62" s="2">
         <v>2022</v>
       </c>
@@ -10811,70 +10635,67 @@
         <v>0.11819355903104481</v>
       </c>
       <c r="I62" s="39">
-        <v>0</v>
+        <v>6.1857636695942233</v>
       </c>
       <c r="J62" s="39">
-        <v>6.1857636695942233</v>
+        <v>31.119964529043138</v>
       </c>
       <c r="K62" s="39">
-        <v>31.119964529043138</v>
+        <v>60.701350525748666</v>
       </c>
       <c r="L62" s="39">
-        <v>60.701350525748666</v>
+        <v>1.9929212756139749</v>
       </c>
       <c r="M62" s="39">
-        <v>1.9929212756139749</v>
+        <v>15.160353987775924</v>
       </c>
       <c r="N62" s="39">
-        <v>15.160353987775924</v>
+        <v>69.788978740626362</v>
       </c>
       <c r="O62" s="39">
-        <v>69.788978740626362</v>
+        <v>5.067113834446527</v>
       </c>
       <c r="P62" s="39">
-        <v>5.067113834446527</v>
-      </c>
-      <c r="Q62" s="39">
         <v>9.9835534371511869</v>
       </c>
-      <c r="R62" s="42">
+      <c r="Q62" s="42">
         <v>41.707246025628798</v>
       </c>
-      <c r="S62" s="43">
+      <c r="R62" s="43">
         <v>58.292753974371202</v>
       </c>
-      <c r="T62" s="59">
-        <v>0</v>
-      </c>
-      <c r="U62" s="59">
-        <v>0</v>
+      <c r="S62" s="44">
+        <v>0</v>
+      </c>
+      <c r="T62" s="44">
+        <v>0</v>
+      </c>
+      <c r="U62" s="39">
+        <v>1.9646940243295705</v>
       </c>
       <c r="V62" s="39">
-        <v>1.9646940243295705</v>
+        <v>22.856082263748217</v>
       </c>
       <c r="W62" s="39">
-        <v>22.856082263748217</v>
+        <v>25.757560134356559</v>
       </c>
       <c r="X62" s="39">
-        <v>25.757560134356559</v>
+        <v>49.03447333620332</v>
       </c>
       <c r="Y62" s="39">
-        <v>49.03447333620332</v>
-      </c>
-      <c r="Z62" s="39">
         <v>0.38719024136233221</v>
       </c>
-      <c r="AA62" s="40">
+      <c r="Z62" s="40">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="41">
         <v>0</v>
       </c>
       <c r="AB62" s="41">
         <v>0</v>
       </c>
-      <c r="AC62" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:29">
+    </row>
+    <row r="63" spans="1:28">
       <c r="A63" s="2">
         <v>2022</v>
       </c>
@@ -10900,70 +10721,67 @@
         <v>0.15384008520373949</v>
       </c>
       <c r="I63" s="39">
-        <v>0</v>
+        <v>10.402371753216419</v>
       </c>
       <c r="J63" s="39">
-        <v>10.402371753216419</v>
+        <v>17.073758120202879</v>
       </c>
       <c r="K63" s="39">
-        <v>17.073758120202879</v>
+        <v>71.04505376098524</v>
       </c>
       <c r="L63" s="39">
-        <v>71.04505376098524</v>
+        <v>1.4788163655954609</v>
       </c>
       <c r="M63" s="39">
-        <v>1.4788163655954609</v>
+        <v>14.017094726876756</v>
       </c>
       <c r="N63" s="39">
-        <v>14.017094726876756</v>
+        <v>74.068291710697594</v>
       </c>
       <c r="O63" s="39">
-        <v>74.068291710697594</v>
+        <v>5.0219133886548644</v>
       </c>
       <c r="P63" s="39">
-        <v>5.0219133886548644</v>
-      </c>
-      <c r="Q63" s="39">
         <v>6.892700173770784</v>
       </c>
-      <c r="R63" s="42">
+      <c r="Q63" s="42">
         <v>41.2366168468388</v>
       </c>
-      <c r="S63" s="43">
+      <c r="R63" s="43">
         <v>58.7633831531612</v>
       </c>
-      <c r="T63" s="59">
-        <v>0</v>
-      </c>
-      <c r="U63" s="59">
-        <v>0</v>
+      <c r="S63" s="44">
+        <v>0</v>
+      </c>
+      <c r="T63" s="44">
+        <v>0</v>
+      </c>
+      <c r="U63" s="39">
+        <v>1.7237978777957477</v>
       </c>
       <c r="V63" s="39">
-        <v>1.7237978777957477</v>
+        <v>24.844031897423335</v>
       </c>
       <c r="W63" s="39">
-        <v>24.844031897423335</v>
+        <v>17.494586531414726</v>
       </c>
       <c r="X63" s="39">
-        <v>17.494586531414726</v>
+        <v>55.390319908484877</v>
       </c>
       <c r="Y63" s="39">
-        <v>55.390319908484877</v>
-      </c>
-      <c r="Z63" s="39">
         <v>0.54726378488131888</v>
       </c>
-      <c r="AA63" s="40">
+      <c r="Z63" s="40">
+        <v>0</v>
+      </c>
+      <c r="AA63" s="41">
         <v>0</v>
       </c>
       <c r="AB63" s="41">
         <v>0</v>
       </c>
-      <c r="AC63" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:29">
+    </row>
+    <row r="64" spans="1:28">
       <c r="A64" s="2">
         <v>2023</v>
       </c>
@@ -10989,70 +10807,67 @@
         <v>6.165387441068864E-2</v>
       </c>
       <c r="I64" s="39">
-        <v>0</v>
+        <v>41.938540562957712</v>
       </c>
       <c r="J64" s="39">
-        <v>41.938540562957712</v>
+        <v>0.79608565581386193</v>
       </c>
       <c r="K64" s="39">
-        <v>0.79608565581386193</v>
+        <v>56.818290895531753</v>
       </c>
       <c r="L64" s="39">
-        <v>56.818290895531753</v>
+        <v>0.44708288569667032</v>
       </c>
       <c r="M64" s="39">
-        <v>0.44708288569667032</v>
+        <v>10.971436166088893</v>
       </c>
       <c r="N64" s="39">
-        <v>10.971436166088893</v>
+        <v>82.401941420204992</v>
       </c>
       <c r="O64" s="39">
-        <v>82.401941420204992</v>
+        <v>1.698250432869268</v>
       </c>
       <c r="P64" s="39">
-        <v>1.698250432869268</v>
-      </c>
-      <c r="Q64" s="39">
         <v>4.928371980836844</v>
       </c>
-      <c r="R64" s="42">
+      <c r="Q64" s="42">
         <v>66.446017172019239</v>
       </c>
-      <c r="S64" s="43">
+      <c r="R64" s="43">
         <v>33.553982827980768</v>
       </c>
-      <c r="T64" s="59">
-        <v>0</v>
-      </c>
-      <c r="U64" s="59">
-        <v>0</v>
+      <c r="S64" s="44">
+        <v>0</v>
+      </c>
+      <c r="T64" s="44">
+        <v>0</v>
+      </c>
+      <c r="U64" s="39">
+        <v>1.8325106663663961</v>
       </c>
       <c r="V64" s="39">
-        <v>1.8325106663663961</v>
+        <v>26.454680710459378</v>
       </c>
       <c r="W64" s="39">
-        <v>26.454680710459378</v>
+        <v>36.85424950252338</v>
       </c>
       <c r="X64" s="39">
-        <v>36.85424950252338</v>
+        <v>34.340346615374578</v>
       </c>
       <c r="Y64" s="39">
-        <v>34.340346615374578</v>
-      </c>
-      <c r="Z64" s="39">
         <v>0.51821250527626717</v>
       </c>
-      <c r="AA64" s="40">
+      <c r="Z64" s="40">
+        <v>0</v>
+      </c>
+      <c r="AA64" s="41">
         <v>0</v>
       </c>
       <c r="AB64" s="41">
         <v>0</v>
       </c>
-      <c r="AC64" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:29">
+    </row>
+    <row r="65" spans="1:28">
       <c r="A65" s="2">
         <v>2023</v>
       </c>
@@ -11078,70 +10893,67 @@
         <v>6.5138711797828444E-2</v>
       </c>
       <c r="I65" s="39">
-        <v>0</v>
+        <v>61.097933776302973</v>
       </c>
       <c r="J65" s="39">
-        <v>61.097933776302973</v>
+        <v>1.0651862293991399</v>
       </c>
       <c r="K65" s="39">
-        <v>1.0651862293991399</v>
+        <v>37.505444725150269</v>
       </c>
       <c r="L65" s="39">
-        <v>37.505444725150269</v>
+        <v>0.3314352691476134</v>
       </c>
       <c r="M65" s="39">
-        <v>0.3314352691476134</v>
+        <v>9.4080890796632577</v>
       </c>
       <c r="N65" s="39">
-        <v>9.4080890796632577</v>
+        <v>86.533115808313994</v>
       </c>
       <c r="O65" s="39">
-        <v>86.533115808313994</v>
+        <v>0.86818617396193842</v>
       </c>
       <c r="P65" s="39">
-        <v>0.86818617396193842</v>
-      </c>
-      <c r="Q65" s="39">
         <v>3.1906089380608065</v>
       </c>
-      <c r="R65" s="42">
+      <c r="Q65" s="42">
         <v>60.598602982521442</v>
       </c>
-      <c r="S65" s="43">
+      <c r="R65" s="43">
         <v>39.401397017478558</v>
       </c>
-      <c r="T65" s="59">
-        <v>0</v>
-      </c>
-      <c r="U65" s="59">
-        <v>0</v>
+      <c r="S65" s="44">
+        <v>0</v>
+      </c>
+      <c r="T65" s="44">
+        <v>0</v>
+      </c>
+      <c r="U65" s="39">
+        <v>1.1142877507543418</v>
       </c>
       <c r="V65" s="39">
-        <v>1.1142877507543418</v>
+        <v>24.239124408999835</v>
       </c>
       <c r="W65" s="39">
-        <v>24.239124408999835</v>
+        <v>17.537162724025691</v>
       </c>
       <c r="X65" s="39">
-        <v>17.537162724025691</v>
+        <v>56.514663139804696</v>
       </c>
       <c r="Y65" s="39">
-        <v>56.514663139804696</v>
-      </c>
-      <c r="Z65" s="39">
         <v>0.59476197641543049</v>
       </c>
-      <c r="AA65" s="40">
+      <c r="Z65" s="40">
+        <v>0</v>
+      </c>
+      <c r="AA65" s="41">
         <v>0</v>
       </c>
       <c r="AB65" s="41">
         <v>0</v>
       </c>
-      <c r="AC65" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:29">
+    </row>
+    <row r="66" spans="1:28">
       <c r="A66" s="2">
         <v>2024</v>
       </c>
@@ -11167,70 +10979,67 @@
         <v>1.909073553876783E-2</v>
       </c>
       <c r="I66" s="39">
-        <v>0</v>
+        <v>68.598180427509035</v>
       </c>
       <c r="J66" s="39">
-        <v>68.598180427509035</v>
+        <v>0.52487191216267315</v>
       </c>
       <c r="K66" s="39">
-        <v>0.52487191216267315</v>
+        <v>30.434389151490134</v>
       </c>
       <c r="L66" s="39">
-        <v>30.434389151490134</v>
+        <v>0.44255850883815373</v>
       </c>
       <c r="M66" s="39">
-        <v>0.44255850883815373</v>
+        <v>9.2448860938695123</v>
       </c>
       <c r="N66" s="39">
-        <v>9.2448860938695123</v>
+        <v>87.65819607201432</v>
       </c>
       <c r="O66" s="39">
-        <v>87.65819607201432</v>
+        <v>1.1753213507827831</v>
       </c>
       <c r="P66" s="39">
-        <v>1.1753213507827831</v>
-      </c>
-      <c r="Q66" s="39">
         <v>1.9215964833333952</v>
       </c>
-      <c r="R66" s="42">
+      <c r="Q66" s="42">
         <v>67.627526891317785</v>
       </c>
-      <c r="S66" s="43">
+      <c r="R66" s="43">
         <v>32.3724731086822</v>
       </c>
-      <c r="T66" s="59">
-        <v>0</v>
-      </c>
-      <c r="U66" s="59">
-        <v>0</v>
+      <c r="S66" s="44">
+        <v>0</v>
+      </c>
+      <c r="T66" s="44">
+        <v>0</v>
+      </c>
+      <c r="U66" s="39">
+        <v>0.88648064333379206</v>
       </c>
       <c r="V66" s="39">
-        <v>0.88648064333379206</v>
+        <v>24.673938510400127</v>
       </c>
       <c r="W66" s="39">
-        <v>24.673938510400127</v>
+        <v>22.875688166084647</v>
       </c>
       <c r="X66" s="39">
-        <v>22.875688166084647</v>
+        <v>51.333315978097694</v>
       </c>
       <c r="Y66" s="39">
-        <v>51.333315978097694</v>
-      </c>
-      <c r="Z66" s="39">
         <v>0.23057670208374398</v>
       </c>
-      <c r="AA66" s="40">
+      <c r="Z66" s="40">
+        <v>0</v>
+      </c>
+      <c r="AA66" s="41">
         <v>0</v>
       </c>
       <c r="AB66" s="41">
         <v>0</v>
       </c>
-      <c r="AC66" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:29">
+    </row>
+    <row r="67" spans="1:28">
       <c r="A67" s="2">
         <v>2024</v>
       </c>
@@ -11256,70 +11065,67 @@
         <v>3.9475105751730674E-2</v>
       </c>
       <c r="I67" s="39">
-        <v>0</v>
+        <v>65.065570228290767</v>
       </c>
       <c r="J67" s="39">
-        <v>65.065570228290767</v>
+        <v>3.8091399413275271</v>
       </c>
       <c r="K67" s="39">
-        <v>3.8091399413275271</v>
+        <v>30.742381304589916</v>
       </c>
       <c r="L67" s="39">
-        <v>30.742381304589916</v>
+        <v>0.38290852579178752</v>
       </c>
       <c r="M67" s="39">
-        <v>0.38290852579178752</v>
+        <v>10.761537119065229</v>
       </c>
       <c r="N67" s="39">
-        <v>10.761537119065229</v>
+        <v>85.894090368905253</v>
       </c>
       <c r="O67" s="39">
-        <v>85.894090368905253</v>
+        <v>1.0974079398981127</v>
       </c>
       <c r="P67" s="39">
-        <v>1.0974079398981127</v>
-      </c>
-      <c r="Q67" s="39">
         <v>2.2469645721314064</v>
       </c>
-      <c r="R67" s="42">
+      <c r="Q67" s="42">
         <v>65.475280273250831</v>
       </c>
-      <c r="S67" s="43">
+      <c r="R67" s="43">
         <v>34.524719726749161</v>
       </c>
-      <c r="T67" s="59">
-        <v>0</v>
-      </c>
-      <c r="U67" s="59">
-        <v>0</v>
+      <c r="S67" s="44">
+        <v>0</v>
+      </c>
+      <c r="T67" s="44">
+        <v>0</v>
+      </c>
+      <c r="U67" s="39">
+        <v>0.62683745234310884</v>
       </c>
       <c r="V67" s="39">
-        <v>0.62683745234310884</v>
+        <v>23.660672546514164</v>
       </c>
       <c r="W67" s="39">
-        <v>23.660672546514164</v>
+        <v>21.486791119975898</v>
       </c>
       <c r="X67" s="39">
-        <v>21.486791119975898</v>
+        <v>54.069041460196757</v>
       </c>
       <c r="Y67" s="39">
-        <v>54.069041460196757</v>
-      </c>
-      <c r="Z67" s="39">
         <v>0.15665742097007096</v>
       </c>
-      <c r="AA67" s="40">
+      <c r="Z67" s="40">
+        <v>0</v>
+      </c>
+      <c r="AA67" s="41">
         <v>0</v>
       </c>
       <c r="AB67" s="41">
         <v>0</v>
       </c>
-      <c r="AC67" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:29">
+    </row>
+    <row r="68" spans="1:28">
       <c r="A68" s="2">
         <v>2025</v>
       </c>
@@ -11345,70 +11151,67 @@
         <v>4.7097742181712338E-2</v>
       </c>
       <c r="I68" s="39">
-        <v>0</v>
+        <v>71.598562332050335</v>
       </c>
       <c r="J68" s="39">
-        <v>71.598562332050335</v>
+        <v>0.58778481953569373</v>
       </c>
       <c r="K68" s="39">
-        <v>0.58778481953569373</v>
+        <v>27.240984280347746</v>
       </c>
       <c r="L68" s="39">
-        <v>27.240984280347746</v>
+        <v>0.57266856806623168</v>
       </c>
       <c r="M68" s="39">
-        <v>0.57266856806623168</v>
+        <v>9.6507896055158078</v>
       </c>
       <c r="N68" s="39">
-        <v>9.6507896055158078</v>
+        <v>88.113129526286656</v>
       </c>
       <c r="O68" s="39">
-        <v>88.113129526286656</v>
+        <v>0.4339988231810839</v>
       </c>
       <c r="P68" s="39">
-        <v>0.4339988231810839</v>
-      </c>
-      <c r="Q68" s="39">
         <v>1.8020820450164468</v>
       </c>
-      <c r="R68" s="42">
+      <c r="Q68" s="42">
         <v>71.711871754222244</v>
       </c>
-      <c r="S68" s="43">
+      <c r="R68" s="43">
         <v>28.288128245777756</v>
       </c>
-      <c r="T68" s="59">
-        <v>0</v>
-      </c>
-      <c r="U68" s="59">
-        <v>0</v>
+      <c r="S68" s="44">
+        <v>0</v>
+      </c>
+      <c r="T68" s="44">
+        <v>0</v>
+      </c>
+      <c r="U68" s="39">
+        <v>1.140464955906769</v>
       </c>
       <c r="V68" s="39">
-        <v>1.140464955906769</v>
+        <v>22.755954991048931</v>
       </c>
       <c r="W68" s="39">
-        <v>22.755954991048931</v>
+        <v>27.665738453869821</v>
       </c>
       <c r="X68" s="39">
-        <v>27.665738453869821</v>
+        <v>47.766480149613407</v>
       </c>
       <c r="Y68" s="39">
-        <v>47.766480149613407</v>
-      </c>
-      <c r="Z68" s="39">
         <v>0.67136144956106647</v>
       </c>
-      <c r="AA68" s="40">
+      <c r="Z68" s="40">
+        <v>0</v>
+      </c>
+      <c r="AA68" s="41">
         <v>0</v>
       </c>
       <c r="AB68" s="41">
         <v>0</v>
       </c>
-      <c r="AC68" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:29">
+    </row>
+    <row r="69" spans="1:28">
       <c r="A69" s="2">
         <v>2025</v>
       </c>
@@ -11434,80 +11237,1943 @@
         <v>4.6728799346904999E-2</v>
       </c>
       <c r="I69" s="39">
-        <v>0</v>
+        <v>73.935488399067637</v>
       </c>
       <c r="J69" s="39">
-        <v>73.935488399067637</v>
+        <v>0.29422520695501841</v>
       </c>
       <c r="K69" s="39">
-        <v>0.29422520695501841</v>
+        <v>25.435796846083093</v>
       </c>
       <c r="L69" s="39">
-        <v>25.435796846083093</v>
+        <v>0.33448954789424884</v>
       </c>
       <c r="M69" s="39">
-        <v>0.33448954789424884</v>
+        <v>7.4769772931280958</v>
       </c>
       <c r="N69" s="39">
-        <v>7.4769772931280958</v>
+        <v>89.829559936611375</v>
       </c>
       <c r="O69" s="39">
-        <v>89.829559936611375</v>
+        <v>1.4609676001344607</v>
       </c>
       <c r="P69" s="39">
-        <v>1.4609676001344607</v>
-      </c>
-      <c r="Q69" s="39">
         <v>1.2324951701260753</v>
       </c>
-      <c r="R69" s="42">
+      <c r="Q69" s="42">
         <v>70.847508967127311</v>
       </c>
-      <c r="S69" s="43">
+      <c r="R69" s="43">
         <v>29.152491032872696</v>
       </c>
-      <c r="T69" s="59">
-        <v>0</v>
-      </c>
-      <c r="U69" s="59">
-        <v>0</v>
+      <c r="S69" s="44">
+        <v>0</v>
+      </c>
+      <c r="T69" s="44">
+        <v>0</v>
+      </c>
+      <c r="U69" s="39">
+        <v>1.6685690644266393</v>
       </c>
       <c r="V69" s="39">
-        <v>1.6685690644266393</v>
+        <v>20.53001170990466</v>
       </c>
       <c r="W69" s="39">
-        <v>20.53001170990466</v>
+        <v>19.070521700263381</v>
       </c>
       <c r="X69" s="39">
-        <v>19.070521700263381</v>
+        <v>58.524588952794673</v>
       </c>
       <c r="Y69" s="39">
-        <v>58.524588952794673</v>
-      </c>
-      <c r="Z69" s="39">
         <v>0.20630857261064381</v>
       </c>
-      <c r="AA69" s="40">
+      <c r="Z69" s="40">
+        <v>0</v>
+      </c>
+      <c r="AA69" s="41">
         <v>0</v>
       </c>
       <c r="AB69" s="41">
-        <v>0</v>
-      </c>
-      <c r="AC69" s="41">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="AA1:AC1"/>
+    <mergeCell ref="Z1:AB1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
-    <mergeCell ref="V1:Z1"/>
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="J1:M1"/>
-    <mergeCell ref="N1:Q1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="U1:Y1"/>
+    <mergeCell ref="I1:L1"/>
+    <mergeCell ref="M1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="C1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45A7C989-D0B9-4324-B446-041ECE1D888B}">
+  <dimension ref="A1:H69"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="1" width="16.19921875" style="6" customWidth="1"/>
+    <col min="2" max="2" width="14.09765625" style="7" customWidth="1"/>
+    <col min="3" max="3" width="11.69921875" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="9.59765625" style="7" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="60"/>
+    </row>
+    <row r="2" spans="1:8" ht="69">
+      <c r="A2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" s="16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="39">
+        <v>82.716435505407134</v>
+      </c>
+      <c r="B3" s="39">
+        <v>1.7755109405636886</v>
+      </c>
+      <c r="C3" s="39">
+        <v>13.706479331817652</v>
+      </c>
+      <c r="D3" s="39">
+        <v>0</v>
+      </c>
+      <c r="E3" s="39">
+        <v>0</v>
+      </c>
+      <c r="F3" s="39">
+        <v>1.7807235968932567</v>
+      </c>
+      <c r="G3" s="39">
+        <v>2.0850625318272767E-2</v>
+      </c>
+      <c r="H3" s="39">
+        <f>SUM(F3:G3)</f>
+        <v>1.8015742222115294</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="39">
+        <v>31.673089334817149</v>
+      </c>
+      <c r="B4" s="39">
+        <v>2.0979531384417807</v>
+      </c>
+      <c r="C4" s="39">
+        <v>65.689748634345847</v>
+      </c>
+      <c r="D4" s="39">
+        <v>0</v>
+      </c>
+      <c r="E4" s="39">
+        <v>0</v>
+      </c>
+      <c r="F4" s="39">
+        <v>0.17779541881564306</v>
+      </c>
+      <c r="G4" s="39">
+        <v>0.36141347357958437</v>
+      </c>
+      <c r="H4" s="39">
+        <f>SUM(F4:G4)</f>
+        <v>0.5392088923952274</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="39">
+        <v>83.466000447030495</v>
+      </c>
+      <c r="B5" s="39">
+        <v>3.0845103934589346</v>
+      </c>
+      <c r="C5" s="39">
+        <v>12.709725797264463</v>
+      </c>
+      <c r="D5" s="39">
+        <v>0</v>
+      </c>
+      <c r="E5" s="39">
+        <v>0</v>
+      </c>
+      <c r="F5" s="39">
+        <v>0.62187709545543035</v>
+      </c>
+      <c r="G5" s="39">
+        <v>0.11788626679068157</v>
+      </c>
+      <c r="H5" s="39">
+        <f>SUM(F5:G5)</f>
+        <v>0.73976336224611194</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="39">
+        <v>78.986989106511018</v>
+      </c>
+      <c r="B6" s="39">
+        <v>3.3362122605150493</v>
+      </c>
+      <c r="C6" s="39">
+        <v>16.720066122456561</v>
+      </c>
+      <c r="D6" s="39">
+        <v>0</v>
+      </c>
+      <c r="E6" s="39">
+        <v>0</v>
+      </c>
+      <c r="F6" s="39">
+        <v>0.66048161665691552</v>
+      </c>
+      <c r="G6" s="39">
+        <v>0.29625089386045561</v>
+      </c>
+      <c r="H6" s="39">
+        <f>SUM(F6:G6)</f>
+        <v>0.95673251051737118</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="39">
+        <v>85.880422588444205</v>
+      </c>
+      <c r="B7" s="39">
+        <v>1.3624337830784645</v>
+      </c>
+      <c r="C7" s="39">
+        <v>12.645557242016475</v>
+      </c>
+      <c r="D7" s="39">
+        <v>0</v>
+      </c>
+      <c r="E7" s="39">
+        <v>0</v>
+      </c>
+      <c r="F7" s="39">
+        <v>0</v>
+      </c>
+      <c r="G7" s="39">
+        <v>0.11158638646085177</v>
+      </c>
+      <c r="H7" s="39">
+        <f>SUM(F7:G7)</f>
+        <v>0.11158638646085177</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="39">
+        <v>82.821667041788587</v>
+      </c>
+      <c r="B8" s="39">
+        <v>3.8860754745292221</v>
+      </c>
+      <c r="C8" s="39">
+        <v>13.160589691649784</v>
+      </c>
+      <c r="D8" s="39">
+        <v>0</v>
+      </c>
+      <c r="E8" s="39">
+        <v>0</v>
+      </c>
+      <c r="F8" s="39">
+        <v>0</v>
+      </c>
+      <c r="G8" s="39">
+        <v>0.13166779203241052</v>
+      </c>
+      <c r="H8" s="39">
+        <f t="shared" ref="H8:H69" si="0">SUM(F8:G8)</f>
+        <v>0.13166779203241052</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="39">
+        <v>88.015355458272026</v>
+      </c>
+      <c r="B9" s="39">
+        <v>1.5512888049263409</v>
+      </c>
+      <c r="C9" s="39">
+        <v>10.318310899590077</v>
+      </c>
+      <c r="D9" s="39">
+        <v>0</v>
+      </c>
+      <c r="E9" s="39">
+        <v>0</v>
+      </c>
+      <c r="F9" s="39">
+        <v>0</v>
+      </c>
+      <c r="G9" s="39">
+        <v>0.11504483721155535</v>
+      </c>
+      <c r="H9" s="39">
+        <f t="shared" si="0"/>
+        <v>0.11504483721155535</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="39">
+        <v>84.397790197875395</v>
+      </c>
+      <c r="B10" s="39">
+        <v>1.6891906427615642</v>
+      </c>
+      <c r="C10" s="39">
+        <v>13.767161892960559</v>
+      </c>
+      <c r="D10" s="39">
+        <v>0</v>
+      </c>
+      <c r="E10" s="39">
+        <v>0</v>
+      </c>
+      <c r="F10" s="39">
+        <v>0</v>
+      </c>
+      <c r="G10" s="39">
+        <v>0.14585726640248861</v>
+      </c>
+      <c r="H10" s="39">
+        <f t="shared" si="0"/>
+        <v>0.14585726640248861</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="39">
+        <v>87.320112103753502</v>
+      </c>
+      <c r="B11" s="39">
+        <v>0.63572033236626047</v>
+      </c>
+      <c r="C11" s="39">
+        <v>11.908147247129602</v>
+      </c>
+      <c r="D11" s="39">
+        <v>0</v>
+      </c>
+      <c r="E11" s="39">
+        <v>0</v>
+      </c>
+      <c r="F11" s="39">
+        <v>0</v>
+      </c>
+      <c r="G11" s="39">
+        <v>0.13602031675063489</v>
+      </c>
+      <c r="H11" s="39">
+        <f t="shared" si="0"/>
+        <v>0.13602031675063489</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="39">
+        <v>83.924707717737519</v>
+      </c>
+      <c r="B12" s="39">
+        <v>2.0192780929917262</v>
+      </c>
+      <c r="C12" s="39">
+        <v>13.945276588631868</v>
+      </c>
+      <c r="D12" s="39">
+        <v>0</v>
+      </c>
+      <c r="E12" s="39">
+        <v>0</v>
+      </c>
+      <c r="F12" s="39">
+        <v>0</v>
+      </c>
+      <c r="G12" s="39">
+        <v>0.11073760063888864</v>
+      </c>
+      <c r="H12" s="39">
+        <f t="shared" si="0"/>
+        <v>0.11073760063888864</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="39">
+        <v>87.061623246492985</v>
+      </c>
+      <c r="B13" s="39">
+        <v>1.7607796237636566</v>
+      </c>
+      <c r="C13" s="39">
+        <v>11.050730493244554</v>
+      </c>
+      <c r="D13" s="39">
+        <v>0</v>
+      </c>
+      <c r="E13" s="39">
+        <v>0</v>
+      </c>
+      <c r="F13" s="39">
+        <v>0</v>
+      </c>
+      <c r="G13" s="39">
+        <v>0.12686663649880406</v>
+      </c>
+      <c r="H13" s="39">
+        <f t="shared" si="0"/>
+        <v>0.12686663649880406</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="39">
+        <v>88.701638632176511</v>
+      </c>
+      <c r="B14" s="39">
+        <v>1.2332804098078278</v>
+      </c>
+      <c r="C14" s="39">
+        <v>9.7069110135853691</v>
+      </c>
+      <c r="D14" s="39">
+        <v>0</v>
+      </c>
+      <c r="E14" s="39">
+        <v>0</v>
+      </c>
+      <c r="F14" s="39">
+        <v>0</v>
+      </c>
+      <c r="G14" s="39">
+        <v>0.3581699444302982</v>
+      </c>
+      <c r="H14" s="39">
+        <f t="shared" si="0"/>
+        <v>0.3581699444302982</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="39">
+        <v>92.258589881634663</v>
+      </c>
+      <c r="B15" s="39">
+        <v>0.61401782234006019</v>
+      </c>
+      <c r="C15" s="39">
+        <v>6.6627301602003755</v>
+      </c>
+      <c r="D15" s="39">
+        <v>0</v>
+      </c>
+      <c r="E15" s="39">
+        <v>0</v>
+      </c>
+      <c r="F15" s="39">
+        <v>0</v>
+      </c>
+      <c r="G15" s="39">
+        <v>0.46466213582491039</v>
+      </c>
+      <c r="H15" s="39">
+        <f t="shared" si="0"/>
+        <v>0.46466213582491039</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="39">
+        <v>89.192010722848352</v>
+      </c>
+      <c r="B16" s="39">
+        <v>1.0279209378716656</v>
+      </c>
+      <c r="C16" s="39">
+        <v>9.5467331181212369</v>
+      </c>
+      <c r="D16" s="39">
+        <v>0</v>
+      </c>
+      <c r="E16" s="39">
+        <v>0</v>
+      </c>
+      <c r="F16" s="39">
+        <v>0</v>
+      </c>
+      <c r="G16" s="39">
+        <v>0.23333522115874722</v>
+      </c>
+      <c r="H16" s="39">
+        <f t="shared" si="0"/>
+        <v>0.23333522115874722</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="39">
+        <v>93.506417804306523</v>
+      </c>
+      <c r="B17" s="39">
+        <v>0.9964792426874336</v>
+      </c>
+      <c r="C17" s="39">
+        <v>5.3537078704081518</v>
+      </c>
+      <c r="D17" s="39">
+        <v>0</v>
+      </c>
+      <c r="E17" s="39">
+        <v>0</v>
+      </c>
+      <c r="F17" s="39">
+        <v>0</v>
+      </c>
+      <c r="G17" s="39">
+        <v>0.14339508259789921</v>
+      </c>
+      <c r="H17" s="39">
+        <f t="shared" si="0"/>
+        <v>0.14339508259789921</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="39">
+        <v>89.125559910152973</v>
+      </c>
+      <c r="B18" s="39">
+        <v>1.342664080048247</v>
+      </c>
+      <c r="C18" s="39">
+        <v>9.4944331067241503</v>
+      </c>
+      <c r="D18" s="39">
+        <v>0</v>
+      </c>
+      <c r="E18" s="39">
+        <v>0</v>
+      </c>
+      <c r="F18" s="39">
+        <v>0</v>
+      </c>
+      <c r="G18" s="39">
+        <v>3.7342903074627926E-2</v>
+      </c>
+      <c r="H18" s="39">
+        <f t="shared" si="0"/>
+        <v>3.7342903074627926E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="39">
+        <v>93.536226553880098</v>
+      </c>
+      <c r="B19" s="39">
+        <v>0.82444526173838417</v>
+      </c>
+      <c r="C19" s="39">
+        <v>5.5890646070859384</v>
+      </c>
+      <c r="D19" s="39">
+        <v>0</v>
+      </c>
+      <c r="E19" s="39">
+        <v>0</v>
+      </c>
+      <c r="F19" s="39">
+        <v>0</v>
+      </c>
+      <c r="G19" s="39">
+        <v>5.0263577295574353E-2</v>
+      </c>
+      <c r="H19" s="39">
+        <f t="shared" si="0"/>
+        <v>5.0263577295574353E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="39">
+        <v>90.486072417287843</v>
+      </c>
+      <c r="B20" s="39">
+        <v>1.1573779554159409</v>
+      </c>
+      <c r="C20" s="39">
+        <v>8.2216391946614955</v>
+      </c>
+      <c r="D20" s="39">
+        <v>0</v>
+      </c>
+      <c r="E20" s="39">
+        <v>0</v>
+      </c>
+      <c r="F20" s="39">
+        <v>0</v>
+      </c>
+      <c r="G20" s="39">
+        <v>0.13491043263472396</v>
+      </c>
+      <c r="H20" s="39">
+        <f t="shared" si="0"/>
+        <v>0.13491043263472396</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="39">
+        <v>92.724213967988447</v>
+      </c>
+      <c r="B21" s="39">
+        <v>1.0100242050970105</v>
+      </c>
+      <c r="C21" s="39">
+        <v>6.2236246815952549</v>
+      </c>
+      <c r="D21" s="39">
+        <v>0</v>
+      </c>
+      <c r="E21" s="39">
+        <v>0</v>
+      </c>
+      <c r="F21" s="39">
+        <v>0</v>
+      </c>
+      <c r="G21" s="39">
+        <v>4.2137145319291844E-2</v>
+      </c>
+      <c r="H21" s="39">
+        <f t="shared" si="0"/>
+        <v>4.2137145319291844E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="39">
+        <v>90.18292395551795</v>
+      </c>
+      <c r="B22" s="39">
+        <v>1.8896882690562011</v>
+      </c>
+      <c r="C22" s="39">
+        <v>7.5720722843671426</v>
+      </c>
+      <c r="D22" s="39">
+        <v>0</v>
+      </c>
+      <c r="E22" s="39">
+        <v>0</v>
+      </c>
+      <c r="F22" s="39">
+        <v>0</v>
+      </c>
+      <c r="G22" s="39">
+        <v>0.35531549105871313</v>
+      </c>
+      <c r="H22" s="39">
+        <f t="shared" si="0"/>
+        <v>0.35531549105871313</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="39">
+        <v>92.395407526386876</v>
+      </c>
+      <c r="B23" s="39">
+        <v>1.4341704340711732</v>
+      </c>
+      <c r="C23" s="39">
+        <v>6.1316200290563891</v>
+      </c>
+      <c r="D23" s="39">
+        <v>0</v>
+      </c>
+      <c r="E23" s="39">
+        <v>0</v>
+      </c>
+      <c r="F23" s="39">
+        <v>0</v>
+      </c>
+      <c r="G23" s="39">
+        <v>3.880201048556655E-2</v>
+      </c>
+      <c r="H23" s="39">
+        <f t="shared" si="0"/>
+        <v>3.880201048556655E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="39">
+        <v>91.950201130403784</v>
+      </c>
+      <c r="B24" s="39">
+        <v>1.7495799175110749</v>
+      </c>
+      <c r="C24" s="39">
+        <v>6.2742502164061316</v>
+      </c>
+      <c r="D24" s="39">
+        <v>0</v>
+      </c>
+      <c r="E24" s="39">
+        <v>0</v>
+      </c>
+      <c r="F24" s="39">
+        <v>0</v>
+      </c>
+      <c r="G24" s="39">
+        <v>2.5968735679006059E-2</v>
+      </c>
+      <c r="H24" s="39">
+        <f t="shared" si="0"/>
+        <v>2.5968735679006059E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="39">
+        <v>93.253031680867949</v>
+      </c>
+      <c r="B25" s="39">
+        <v>1.3890276018313612</v>
+      </c>
+      <c r="C25" s="39">
+        <v>5.2283682276691144</v>
+      </c>
+      <c r="D25" s="39">
+        <v>0</v>
+      </c>
+      <c r="E25" s="39">
+        <v>0</v>
+      </c>
+      <c r="F25" s="39">
+        <v>0</v>
+      </c>
+      <c r="G25" s="39">
+        <v>0.12957248963157258</v>
+      </c>
+      <c r="H25" s="39">
+        <f t="shared" si="0"/>
+        <v>0.12957248963157258</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="39">
+        <v>91.561704138193306</v>
+      </c>
+      <c r="B26" s="39">
+        <v>1.9582761945369547</v>
+      </c>
+      <c r="C26" s="39">
+        <v>6.4245134079306725</v>
+      </c>
+      <c r="D26" s="39">
+        <v>0</v>
+      </c>
+      <c r="E26" s="39">
+        <v>0</v>
+      </c>
+      <c r="F26" s="39">
+        <v>0</v>
+      </c>
+      <c r="G26" s="39">
+        <v>5.5506259339072182E-2</v>
+      </c>
+      <c r="H26" s="39">
+        <f t="shared" si="0"/>
+        <v>5.5506259339072182E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="39">
+        <v>93.022948936384907</v>
+      </c>
+      <c r="B27" s="39">
+        <v>1.9886749541060085</v>
+      </c>
+      <c r="C27" s="39">
+        <v>4.9472364636981441</v>
+      </c>
+      <c r="D27" s="39">
+        <v>0</v>
+      </c>
+      <c r="E27" s="39">
+        <v>0</v>
+      </c>
+      <c r="F27" s="39">
+        <v>0</v>
+      </c>
+      <c r="G27" s="39">
+        <v>4.1139645810936161E-2</v>
+      </c>
+      <c r="H27" s="39">
+        <f t="shared" si="0"/>
+        <v>4.1139645810936161E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="39">
+        <v>92.708444576117614</v>
+      </c>
+      <c r="B28" s="39">
+        <v>1.6780292199627258</v>
+      </c>
+      <c r="C28" s="39">
+        <v>5.5325701647713768</v>
+      </c>
+      <c r="D28" s="39">
+        <v>0</v>
+      </c>
+      <c r="E28" s="39">
+        <v>0</v>
+      </c>
+      <c r="F28" s="39">
+        <v>0</v>
+      </c>
+      <c r="G28" s="39">
+        <v>8.0956039148273568E-2</v>
+      </c>
+      <c r="H28" s="39">
+        <f t="shared" si="0"/>
+        <v>8.0956039148273568E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="39">
+        <v>94.765193641286217</v>
+      </c>
+      <c r="B29" s="39">
+        <v>1.1724194014239526</v>
+      </c>
+      <c r="C29" s="39">
+        <v>3.7901029968060613</v>
+      </c>
+      <c r="D29" s="39">
+        <v>0</v>
+      </c>
+      <c r="E29" s="39">
+        <v>0</v>
+      </c>
+      <c r="F29" s="39">
+        <v>0</v>
+      </c>
+      <c r="G29" s="39">
+        <v>0.27228396048377373</v>
+      </c>
+      <c r="H29" s="39">
+        <f t="shared" si="0"/>
+        <v>0.27228396048377373</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="39">
+        <v>93.559243493540464</v>
+      </c>
+      <c r="B30" s="39">
+        <v>1.3989585605879955</v>
+      </c>
+      <c r="C30" s="39">
+        <v>4.8329350563253328</v>
+      </c>
+      <c r="D30" s="39">
+        <v>0</v>
+      </c>
+      <c r="E30" s="39">
+        <v>0</v>
+      </c>
+      <c r="F30" s="39">
+        <v>0</v>
+      </c>
+      <c r="G30" s="39">
+        <v>0.20886288954620097</v>
+      </c>
+      <c r="H30" s="39">
+        <f t="shared" si="0"/>
+        <v>0.20886288954620097</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="39">
+        <v>96.214142011453987</v>
+      </c>
+      <c r="B31" s="39">
+        <v>0.80216481658835703</v>
+      </c>
+      <c r="C31" s="39">
+        <v>2.9406282338876069</v>
+      </c>
+      <c r="D31" s="39">
+        <v>0</v>
+      </c>
+      <c r="E31" s="39">
+        <v>0</v>
+      </c>
+      <c r="F31" s="39">
+        <v>0</v>
+      </c>
+      <c r="G31" s="39">
+        <v>4.3064938070048013E-2</v>
+      </c>
+      <c r="H31" s="39">
+        <f t="shared" si="0"/>
+        <v>4.3064938070048013E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="39">
+        <v>94.033945929070185</v>
+      </c>
+      <c r="B32" s="39">
+        <v>0.99784460761652027</v>
+      </c>
+      <c r="C32" s="39">
+        <v>4.8743488293437558</v>
+      </c>
+      <c r="D32" s="39">
+        <v>0</v>
+      </c>
+      <c r="E32" s="39">
+        <v>0</v>
+      </c>
+      <c r="F32" s="39">
+        <v>0</v>
+      </c>
+      <c r="G32" s="39">
+        <v>9.3860633969544319E-2</v>
+      </c>
+      <c r="H32" s="39">
+        <f t="shared" si="0"/>
+        <v>9.3860633969544319E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="39">
+        <v>95.944825479485928</v>
+      </c>
+      <c r="B33" s="39">
+        <v>0.83569106341505983</v>
+      </c>
+      <c r="C33" s="39">
+        <v>3.1965728665876312</v>
+      </c>
+      <c r="D33" s="39">
+        <v>0</v>
+      </c>
+      <c r="E33" s="39">
+        <v>0</v>
+      </c>
+      <c r="F33" s="39">
+        <v>0</v>
+      </c>
+      <c r="G33" s="39">
+        <v>2.2910590511378927E-2</v>
+      </c>
+      <c r="H33" s="39">
+        <f t="shared" si="0"/>
+        <v>2.2910590511378927E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="39">
+        <v>94.877853345492383</v>
+      </c>
+      <c r="B34" s="39">
+        <v>1.100560184598582</v>
+      </c>
+      <c r="C34" s="39">
+        <v>3.9723316278546839</v>
+      </c>
+      <c r="D34" s="39">
+        <v>0</v>
+      </c>
+      <c r="E34" s="39">
+        <v>0</v>
+      </c>
+      <c r="F34" s="39">
+        <v>0</v>
+      </c>
+      <c r="G34" s="39">
+        <v>4.9254842054355215E-2</v>
+      </c>
+      <c r="H34" s="39">
+        <f t="shared" si="0"/>
+        <v>4.9254842054355215E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="39">
+        <v>96.196812065345327</v>
+      </c>
+      <c r="B35" s="39">
+        <v>0.59800721747715979</v>
+      </c>
+      <c r="C35" s="39">
+        <v>3.0598826405446307</v>
+      </c>
+      <c r="D35" s="39">
+        <v>0</v>
+      </c>
+      <c r="E35" s="39">
+        <v>0</v>
+      </c>
+      <c r="F35" s="39">
+        <v>0</v>
+      </c>
+      <c r="G35" s="39">
+        <v>0.14529807663287875</v>
+      </c>
+      <c r="H35" s="39">
+        <f t="shared" si="0"/>
+        <v>0.14529807663287875</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="39">
+        <v>94.758040276525406</v>
+      </c>
+      <c r="B36" s="39">
+        <v>1.0352300950753801</v>
+      </c>
+      <c r="C36" s="39">
+        <v>4.1138689826459744</v>
+      </c>
+      <c r="D36" s="39">
+        <v>0</v>
+      </c>
+      <c r="E36" s="39">
+        <v>0</v>
+      </c>
+      <c r="F36" s="39">
+        <v>0</v>
+      </c>
+      <c r="G36" s="39">
+        <v>9.2860645753246956E-2</v>
+      </c>
+      <c r="H36" s="39">
+        <f t="shared" si="0"/>
+        <v>9.2860645753246956E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="39">
+        <v>95.384838340362009</v>
+      </c>
+      <c r="B37" s="39">
+        <v>1.0408243119864353</v>
+      </c>
+      <c r="C37" s="39">
+        <v>3.5120212164688489</v>
+      </c>
+      <c r="D37" s="39">
+        <v>0</v>
+      </c>
+      <c r="E37" s="39">
+        <v>0</v>
+      </c>
+      <c r="F37" s="39">
+        <v>0</v>
+      </c>
+      <c r="G37" s="39">
+        <v>6.2316131182702197E-2</v>
+      </c>
+      <c r="H37" s="39">
+        <f t="shared" si="0"/>
+        <v>6.2316131182702197E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="39">
+        <v>94.597549762679861</v>
+      </c>
+      <c r="B38" s="39">
+        <v>1.1524315996123355</v>
+      </c>
+      <c r="C38" s="39">
+        <v>3.9073954424591837</v>
+      </c>
+      <c r="D38" s="39">
+        <v>0</v>
+      </c>
+      <c r="E38" s="39">
+        <v>0</v>
+      </c>
+      <c r="F38" s="39">
+        <v>0</v>
+      </c>
+      <c r="G38" s="39">
+        <v>0.342623195248627</v>
+      </c>
+      <c r="H38" s="39">
+        <f t="shared" si="0"/>
+        <v>0.342623195248627</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="44">
+        <v>94.041215088995315</v>
+      </c>
+      <c r="B39" s="44">
+        <v>1.7931084146473195</v>
+      </c>
+      <c r="C39" s="44">
+        <v>3.6915949543321456</v>
+      </c>
+      <c r="D39" s="44">
+        <v>0</v>
+      </c>
+      <c r="E39" s="44">
+        <v>0</v>
+      </c>
+      <c r="F39" s="44">
+        <v>0</v>
+      </c>
+      <c r="G39" s="44">
+        <v>0.47408154202522834</v>
+      </c>
+      <c r="H39" s="39">
+        <f t="shared" si="0"/>
+        <v>0.47408154202522834</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="39">
+        <v>94.935933952879353</v>
+      </c>
+      <c r="B40" s="39">
+        <v>1.4921819866851453</v>
+      </c>
+      <c r="C40" s="39">
+        <v>2.8732651435924033</v>
+      </c>
+      <c r="D40" s="39">
+        <v>0.52176771842114966</v>
+      </c>
+      <c r="E40" s="39">
+        <v>0</v>
+      </c>
+      <c r="F40" s="39">
+        <v>0.17685119842194316</v>
+      </c>
+      <c r="G40" s="39">
+        <v>0</v>
+      </c>
+      <c r="H40" s="39">
+        <f t="shared" si="0"/>
+        <v>0.17685119842194316</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="39">
+        <v>96.809272737692709</v>
+      </c>
+      <c r="B41" s="39">
+        <v>0.6850576782951131</v>
+      </c>
+      <c r="C41" s="39">
+        <v>2.037161360045193</v>
+      </c>
+      <c r="D41" s="39">
+        <v>0.36903465609981745</v>
+      </c>
+      <c r="E41" s="39">
+        <v>0</v>
+      </c>
+      <c r="F41" s="39">
+        <v>9.9473567867172083E-2</v>
+      </c>
+      <c r="G41" s="39">
+        <v>0</v>
+      </c>
+      <c r="H41" s="39">
+        <f t="shared" si="0"/>
+        <v>9.9473567867172083E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="39">
+        <v>94.987430117864903</v>
+      </c>
+      <c r="B42" s="39">
+        <v>1.4290496029626465</v>
+      </c>
+      <c r="C42" s="39">
+        <v>2.7797599971513014</v>
+      </c>
+      <c r="D42" s="39">
+        <v>0.55891464587116757</v>
+      </c>
+      <c r="E42" s="39">
+        <v>0</v>
+      </c>
+      <c r="F42" s="39">
+        <v>0.244845636149984</v>
+      </c>
+      <c r="G42" s="39">
+        <v>0</v>
+      </c>
+      <c r="H42" s="39">
+        <f t="shared" si="0"/>
+        <v>0.244845636149984</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="39">
+        <v>97.259026394763836</v>
+      </c>
+      <c r="B43" s="39">
+        <v>0.88357445781281718</v>
+      </c>
+      <c r="C43" s="39">
+        <v>1.6335566272199089</v>
+      </c>
+      <c r="D43" s="39">
+        <v>0.16431577157090266</v>
+      </c>
+      <c r="E43" s="39">
+        <v>0</v>
+      </c>
+      <c r="F43" s="39">
+        <v>5.9526748632530685E-2</v>
+      </c>
+      <c r="G43" s="39">
+        <v>0</v>
+      </c>
+      <c r="H43" s="39">
+        <f t="shared" si="0"/>
+        <v>5.9526748632530685E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="39">
+        <v>97.007958852539971</v>
+      </c>
+      <c r="B44" s="39">
+        <v>0.71905442931628261</v>
+      </c>
+      <c r="C44" s="39">
+        <v>1.7730091645449471</v>
+      </c>
+      <c r="D44" s="39">
+        <v>0.49997755359879942</v>
+      </c>
+      <c r="E44" s="39">
+        <v>0</v>
+      </c>
+      <c r="F44" s="39">
+        <v>0</v>
+      </c>
+      <c r="G44" s="39">
+        <v>0</v>
+      </c>
+      <c r="H44" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="39">
+        <v>96.218608485455064</v>
+      </c>
+      <c r="B45" s="39">
+        <v>1.8965043463885098</v>
+      </c>
+      <c r="C45" s="39">
+        <v>0.99550281158053944</v>
+      </c>
+      <c r="D45" s="39">
+        <v>0.88938435657588133</v>
+      </c>
+      <c r="E45" s="39">
+        <v>0</v>
+      </c>
+      <c r="F45" s="39">
+        <v>0</v>
+      </c>
+      <c r="G45" s="39">
+        <v>0</v>
+      </c>
+      <c r="H45" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="39">
+        <v>96.084994526239512</v>
+      </c>
+      <c r="B46" s="39">
+        <v>0.87518751276315121</v>
+      </c>
+      <c r="C46" s="39">
+        <v>2.0351948213465909</v>
+      </c>
+      <c r="D46" s="39">
+        <v>0.91863980506349718</v>
+      </c>
+      <c r="E46" s="39">
+        <v>0</v>
+      </c>
+      <c r="F46" s="39">
+        <v>8.598333458725696E-2</v>
+      </c>
+      <c r="G46" s="39">
+        <v>0</v>
+      </c>
+      <c r="H46" s="39">
+        <f t="shared" si="0"/>
+        <v>8.598333458725696E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="39">
+        <v>95.877359183842998</v>
+      </c>
+      <c r="B47" s="39">
+        <v>1.9084347512133404</v>
+      </c>
+      <c r="C47" s="39">
+        <v>1.6378095654980047</v>
+      </c>
+      <c r="D47" s="39">
+        <v>0.43325590534828212</v>
+      </c>
+      <c r="E47" s="39">
+        <v>0</v>
+      </c>
+      <c r="F47" s="39">
+        <v>0.14314059409736754</v>
+      </c>
+      <c r="G47" s="39">
+        <v>0</v>
+      </c>
+      <c r="H47" s="39">
+        <f t="shared" si="0"/>
+        <v>0.14314059409736754</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="39">
+        <v>95.461322813366365</v>
+      </c>
+      <c r="B48" s="39">
+        <v>1.7984121683712428</v>
+      </c>
+      <c r="C48" s="39">
+        <v>1.7814570050710175</v>
+      </c>
+      <c r="D48" s="39">
+        <v>0.66189851234620634</v>
+      </c>
+      <c r="E48" s="39">
+        <v>0</v>
+      </c>
+      <c r="F48" s="39">
+        <v>0.29690950084516959</v>
+      </c>
+      <c r="G48" s="39">
+        <v>0</v>
+      </c>
+      <c r="H48" s="39">
+        <f t="shared" si="0"/>
+        <v>0.29690950084516959</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="39">
+        <v>95.974302108342243</v>
+      </c>
+      <c r="B49" s="39">
+        <v>1.5659652728944664</v>
+      </c>
+      <c r="C49" s="39">
+        <v>1.6127757134951379</v>
+      </c>
+      <c r="D49" s="39">
+        <v>0.84695690526815104</v>
+      </c>
+      <c r="E49" s="39">
+        <v>0</v>
+      </c>
+      <c r="F49" s="39">
+        <v>0</v>
+      </c>
+      <c r="G49" s="39">
+        <v>0</v>
+      </c>
+      <c r="H49" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="39">
+        <v>95.243814525036214</v>
+      </c>
+      <c r="B50" s="39">
+        <v>1.6228728645974564</v>
+      </c>
+      <c r="C50" s="39">
+        <v>2.0314680458462577</v>
+      </c>
+      <c r="D50" s="39">
+        <v>1.1018445645200758</v>
+      </c>
+      <c r="E50" s="39">
+        <v>0</v>
+      </c>
+      <c r="F50" s="39">
+        <v>0</v>
+      </c>
+      <c r="G50" s="39">
+        <v>0</v>
+      </c>
+      <c r="H50" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="39">
+        <v>97.230080089692152</v>
+      </c>
+      <c r="B51" s="39">
+        <v>0.76819665834453621</v>
+      </c>
+      <c r="C51" s="39">
+        <v>1.1878500355550481</v>
+      </c>
+      <c r="D51" s="39">
+        <v>0.81387321640826549</v>
+      </c>
+      <c r="E51" s="39">
+        <v>0</v>
+      </c>
+      <c r="F51" s="39">
+        <v>0</v>
+      </c>
+      <c r="G51" s="39">
+        <v>0</v>
+      </c>
+      <c r="H51" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="39">
+        <v>94.977845604877658</v>
+      </c>
+      <c r="B52" s="39">
+        <v>1.7030500077411364</v>
+      </c>
+      <c r="C52" s="39">
+        <v>2.2709176564262492</v>
+      </c>
+      <c r="D52" s="39">
+        <v>1.0481867309549613</v>
+      </c>
+      <c r="E52" s="39">
+        <v>0</v>
+      </c>
+      <c r="F52" s="39">
+        <v>0</v>
+      </c>
+      <c r="G52" s="39">
+        <v>0</v>
+      </c>
+      <c r="H52" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" s="39">
+        <v>96.681960316791304</v>
+      </c>
+      <c r="B53" s="39">
+        <v>0.95856263773316797</v>
+      </c>
+      <c r="C53" s="39">
+        <v>1.5213368496686375</v>
+      </c>
+      <c r="D53" s="39">
+        <v>0.83814019580689059</v>
+      </c>
+      <c r="E53" s="39">
+        <v>0</v>
+      </c>
+      <c r="F53" s="39">
+        <v>0</v>
+      </c>
+      <c r="G53" s="39">
+        <v>0</v>
+      </c>
+      <c r="H53" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" s="39">
+        <v>96.183551636637787</v>
+      </c>
+      <c r="B54" s="39">
+        <v>1.1474974932215811</v>
+      </c>
+      <c r="C54" s="39">
+        <v>1.6085348873111298</v>
+      </c>
+      <c r="D54" s="39">
+        <v>1.0604159828295046</v>
+      </c>
+      <c r="E54" s="39">
+        <v>0</v>
+      </c>
+      <c r="F54" s="39">
+        <v>0</v>
+      </c>
+      <c r="G54" s="39">
+        <v>0</v>
+      </c>
+      <c r="H54" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" s="39">
+        <v>96.446411228505767</v>
+      </c>
+      <c r="B55" s="39">
+        <v>0.98912947509518057</v>
+      </c>
+      <c r="C55" s="39">
+        <v>1.3990148837632403</v>
+      </c>
+      <c r="D55" s="39">
+        <v>1.1654444126358146</v>
+      </c>
+      <c r="E55" s="39">
+        <v>0</v>
+      </c>
+      <c r="F55" s="39">
+        <v>0</v>
+      </c>
+      <c r="G55" s="39">
+        <v>0</v>
+      </c>
+      <c r="H55" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" s="39">
+        <v>97.13312487383476</v>
+      </c>
+      <c r="B56" s="39">
+        <v>0.74783396855995832</v>
+      </c>
+      <c r="C56" s="39">
+        <v>0.94194460895128118</v>
+      </c>
+      <c r="D56" s="39">
+        <v>1.1770965486539924</v>
+      </c>
+      <c r="E56" s="39">
+        <v>0</v>
+      </c>
+      <c r="F56" s="39">
+        <v>0</v>
+      </c>
+      <c r="G56" s="39">
+        <v>0</v>
+      </c>
+      <c r="H56" s="39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" s="39">
+        <v>97.67827034529121</v>
+      </c>
+      <c r="B57" s="39">
+        <v>0.88260966208193958</v>
+      </c>
+      <c r="C57" s="39">
+        <v>0.76631987552384617</v>
+      </c>
+      <c r="D57" s="39">
+        <v>0.62834434788265847</v>
+      </c>
+      <c r="E57" s="39">
+        <v>0</v>
+      </c>
+      <c r="F57" s="39">
+        <v>4.4455769220343395E-2</v>
+      </c>
+      <c r="G57" s="39">
+        <v>0</v>
+      </c>
+      <c r="H57" s="39">
+        <f t="shared" si="0"/>
+        <v>4.4455769220343395E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" s="39">
+        <v>97.82252661356361</v>
+      </c>
+      <c r="B58" s="39">
+        <v>0.51459093277748824</v>
+      </c>
+      <c r="C58" s="39">
+        <v>0.4502504493199051</v>
+      </c>
+      <c r="D58" s="39">
+        <v>1.1892354648998733</v>
+      </c>
+      <c r="E58" s="39">
+        <v>0</v>
+      </c>
+      <c r="F58" s="39">
+        <v>2.339653943912114E-2</v>
+      </c>
+      <c r="G58" s="39">
+        <v>0</v>
+      </c>
+      <c r="H58" s="39">
+        <f t="shared" si="0"/>
+        <v>2.339653943912114E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" s="39">
+        <v>96.425518296559005</v>
+      </c>
+      <c r="B59" s="39">
+        <v>0.90112799919334685</v>
+      </c>
+      <c r="C59" s="39">
+        <v>1.0578554424974682</v>
+      </c>
+      <c r="D59" s="39">
+        <v>1.5120362292473137</v>
+      </c>
+      <c r="E59" s="39">
+        <v>0</v>
+      </c>
+      <c r="F59" s="39">
+        <v>0.10346203250286055</v>
+      </c>
+      <c r="G59" s="39">
+        <v>0</v>
+      </c>
+      <c r="H59" s="39">
+        <f t="shared" si="0"/>
+        <v>0.10346203250286055</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" s="39">
+        <v>96.495248234316577</v>
+      </c>
+      <c r="B60" s="39">
+        <v>0.60189031990029074</v>
+      </c>
+      <c r="C60" s="39">
+        <v>0.95009347735770655</v>
+      </c>
+      <c r="D60" s="39">
+        <v>1.5701599501454093</v>
+      </c>
+      <c r="E60" s="39">
+        <v>0</v>
+      </c>
+      <c r="F60" s="39">
+        <v>0.38260801828001662</v>
+      </c>
+      <c r="G60" s="39">
+        <v>0</v>
+      </c>
+      <c r="H60" s="39">
+        <f t="shared" si="0"/>
+        <v>0.38260801828001662</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" s="39">
+        <v>95.183332103608009</v>
+      </c>
+      <c r="B61" s="39">
+        <v>0.84731398078039033</v>
+      </c>
+      <c r="C61" s="39">
+        <v>1.3390711652012994</v>
+      </c>
+      <c r="D61" s="39">
+        <v>2.1598629620692886</v>
+      </c>
+      <c r="E61" s="39">
+        <v>0</v>
+      </c>
+      <c r="F61" s="39">
+        <v>0.47041978834100745</v>
+      </c>
+      <c r="G61" s="39">
+        <v>0</v>
+      </c>
+      <c r="H61" s="39">
+        <f t="shared" si="0"/>
+        <v>0.47041978834100745</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" s="39">
+        <v>95.114494371305653</v>
+      </c>
+      <c r="B62" s="39">
+        <v>1.1070495948938319</v>
+      </c>
+      <c r="C62" s="39">
+        <v>1.4069802512354255</v>
+      </c>
+      <c r="D62" s="39">
+        <v>1.7774145900088418</v>
+      </c>
+      <c r="E62" s="39">
+        <v>0.47586763352520994</v>
+      </c>
+      <c r="F62" s="39">
+        <v>0.11819355903104481</v>
+      </c>
+      <c r="G62" s="39">
+        <v>0</v>
+      </c>
+      <c r="H62" s="39">
+        <f t="shared" si="0"/>
+        <v>0.11819355903104481</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" s="39">
+        <v>94.463625435724524</v>
+      </c>
+      <c r="B63" s="39">
+        <v>1.2952878428962629</v>
+      </c>
+      <c r="C63" s="39">
+        <v>1.6505110355866788</v>
+      </c>
+      <c r="D63" s="39">
+        <v>2.2818574581299607</v>
+      </c>
+      <c r="E63" s="39">
+        <v>0.15487814245882547</v>
+      </c>
+      <c r="F63" s="39">
+        <v>0.15384008520373949</v>
+      </c>
+      <c r="G63" s="39">
+        <v>0</v>
+      </c>
+      <c r="H63" s="39">
+        <f t="shared" si="0"/>
+        <v>0.15384008520373949</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" s="39">
+        <v>95.121098792642385</v>
+      </c>
+      <c r="B64" s="39">
+        <v>1.1629323616387379</v>
+      </c>
+      <c r="C64" s="39">
+        <v>1.4565574002493229</v>
+      </c>
+      <c r="D64" s="39">
+        <v>1.8491239858183783</v>
+      </c>
+      <c r="E64" s="39">
+        <v>0.34863358524048088</v>
+      </c>
+      <c r="F64" s="39">
+        <v>6.165387441068864E-2</v>
+      </c>
+      <c r="G64" s="39">
+        <v>0</v>
+      </c>
+      <c r="H64" s="39">
+        <f t="shared" si="0"/>
+        <v>6.165387441068864E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" s="39">
+        <v>95.002930252080873</v>
+      </c>
+      <c r="B65" s="39">
+        <v>1.0099470178745378</v>
+      </c>
+      <c r="C65" s="39">
+        <v>1.9420839636015172</v>
+      </c>
+      <c r="D65" s="39">
+        <v>1.811212569989467</v>
+      </c>
+      <c r="E65" s="39">
+        <v>0.16868748465577457</v>
+      </c>
+      <c r="F65" s="39">
+        <v>6.5138711797828444E-2</v>
+      </c>
+      <c r="G65" s="39">
+        <v>0</v>
+      </c>
+      <c r="H65" s="39">
+        <f t="shared" si="0"/>
+        <v>6.5138711797828444E-2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" s="39">
+        <v>94.251085320711951</v>
+      </c>
+      <c r="B66" s="39">
+        <v>0.72867106166803441</v>
+      </c>
+      <c r="C66" s="39">
+        <v>1.8437435692733373</v>
+      </c>
+      <c r="D66" s="39">
+        <v>3.0082784371381748</v>
+      </c>
+      <c r="E66" s="39">
+        <v>0.14913087566972533</v>
+      </c>
+      <c r="F66" s="39">
+        <v>1.909073553876783E-2</v>
+      </c>
+      <c r="G66" s="39">
+        <v>0</v>
+      </c>
+      <c r="H66" s="39">
+        <f t="shared" si="0"/>
+        <v>1.909073553876783E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" s="39">
+        <v>93.585087551629286</v>
+      </c>
+      <c r="B67" s="39">
+        <v>1.2983154518029736</v>
+      </c>
+      <c r="C67" s="39">
+        <v>2.3845041511190153</v>
+      </c>
+      <c r="D67" s="39">
+        <v>2.5895669373135322</v>
+      </c>
+      <c r="E67" s="39">
+        <v>0.10305080238346533</v>
+      </c>
+      <c r="F67" s="39">
+        <v>3.9475105751730674E-2</v>
+      </c>
+      <c r="G67" s="39">
+        <v>0</v>
+      </c>
+      <c r="H67" s="39">
+        <f t="shared" si="0"/>
+        <v>3.9475105751730674E-2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" s="39">
+        <v>95.209272633463385</v>
+      </c>
+      <c r="B68" s="39">
+        <v>0.89685594462205009</v>
+      </c>
+      <c r="C68" s="39">
+        <v>1.4004394956418971</v>
+      </c>
+      <c r="D68" s="39">
+        <v>2.3988616588149609</v>
+      </c>
+      <c r="E68" s="39">
+        <v>4.7472525275996512E-2</v>
+      </c>
+      <c r="F68" s="39">
+        <v>4.7097742181712338E-2</v>
+      </c>
+      <c r="G68" s="39">
+        <v>0</v>
+      </c>
+      <c r="H68" s="39">
+        <f t="shared" si="0"/>
+        <v>4.7097742181712338E-2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" s="39">
+        <v>95.561133459667332</v>
+      </c>
+      <c r="B69" s="39">
+        <v>0.88563080185142096</v>
+      </c>
+      <c r="C69" s="39">
+        <v>0.92330935942758141</v>
+      </c>
+      <c r="D69" s="39">
+        <v>2.1340100697792108</v>
+      </c>
+      <c r="E69" s="39">
+        <v>0.44918750992756112</v>
+      </c>
+      <c r="F69" s="39">
+        <v>4.6728799346904999E-2</v>
+      </c>
+      <c r="G69" s="39">
+        <v>0</v>
+      </c>
+      <c r="H69" s="39">
+        <f t="shared" si="0"/>
+        <v>4.6728799346904999E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/paddy_production_data.xlsx
+++ b/data/paddy_production_data.xlsx
@@ -8,14 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\My Research Documents\Research Project\Forecastig_Paddy_Production\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50957DDE-4F9D-43F6-A754-76260CBA83EA}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AB8B741-E2B5-47C6-96A3-2845BABEDC1E}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{985DDFCC-FB2F-4E8D-9C1B-C306315BC8C0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="44">
   <si>
     <t>Year</t>
   </si>
@@ -151,9 +150,6 @@
     <t>USE OF FUNGICIDE</t>
   </si>
   <si>
-    <t>ROW SEEDED</t>
-  </si>
-  <si>
     <t>METHOD OF WEEDING</t>
   </si>
   <si>
@@ -211,9 +207,6 @@
       </rPr>
       <t>(HECTARES)</t>
     </r>
-  </si>
-  <si>
-    <t>OTHER--</t>
   </si>
 </sst>
 </file>
@@ -880,25 +873,25 @@
         <v>1</v>
       </c>
       <c r="C1" s="53" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D1" s="53"/>
       <c r="E1" s="53"/>
       <c r="F1" s="53"/>
       <c r="G1" s="50" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H1" s="50"/>
       <c r="I1" s="50"/>
       <c r="J1" s="50"/>
       <c r="K1" s="51" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L1" s="51"/>
       <c r="M1" s="51"/>
       <c r="N1" s="51"/>
       <c r="O1" s="49" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="22.2" customHeight="1">
@@ -5427,7 +5420,7 @@
       <c r="K1" s="59"/>
       <c r="L1" s="60"/>
       <c r="M1" s="61" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N1" s="62"/>
       <c r="O1" s="62"/>
@@ -11311,1870 +11304,4 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45A7C989-D0B9-4324-B446-041ECE1D888B}">
-  <dimension ref="A1:H69"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
-  <cols>
-    <col min="1" max="1" width="16.19921875" style="6" customWidth="1"/>
-    <col min="2" max="2" width="14.09765625" style="7" customWidth="1"/>
-    <col min="3" max="3" width="11.69921875" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.59765625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="9.59765625" style="7" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="60"/>
-    </row>
-    <row r="2" spans="1:8" ht="69">
-      <c r="A2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="H2" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="39">
-        <v>82.716435505407134</v>
-      </c>
-      <c r="B3" s="39">
-        <v>1.7755109405636886</v>
-      </c>
-      <c r="C3" s="39">
-        <v>13.706479331817652</v>
-      </c>
-      <c r="D3" s="39">
-        <v>0</v>
-      </c>
-      <c r="E3" s="39">
-        <v>0</v>
-      </c>
-      <c r="F3" s="39">
-        <v>1.7807235968932567</v>
-      </c>
-      <c r="G3" s="39">
-        <v>2.0850625318272767E-2</v>
-      </c>
-      <c r="H3" s="39">
-        <f>SUM(F3:G3)</f>
-        <v>1.8015742222115294</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="39">
-        <v>31.673089334817149</v>
-      </c>
-      <c r="B4" s="39">
-        <v>2.0979531384417807</v>
-      </c>
-      <c r="C4" s="39">
-        <v>65.689748634345847</v>
-      </c>
-      <c r="D4" s="39">
-        <v>0</v>
-      </c>
-      <c r="E4" s="39">
-        <v>0</v>
-      </c>
-      <c r="F4" s="39">
-        <v>0.17779541881564306</v>
-      </c>
-      <c r="G4" s="39">
-        <v>0.36141347357958437</v>
-      </c>
-      <c r="H4" s="39">
-        <f>SUM(F4:G4)</f>
-        <v>0.5392088923952274</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="39">
-        <v>83.466000447030495</v>
-      </c>
-      <c r="B5" s="39">
-        <v>3.0845103934589346</v>
-      </c>
-      <c r="C5" s="39">
-        <v>12.709725797264463</v>
-      </c>
-      <c r="D5" s="39">
-        <v>0</v>
-      </c>
-      <c r="E5" s="39">
-        <v>0</v>
-      </c>
-      <c r="F5" s="39">
-        <v>0.62187709545543035</v>
-      </c>
-      <c r="G5" s="39">
-        <v>0.11788626679068157</v>
-      </c>
-      <c r="H5" s="39">
-        <f>SUM(F5:G5)</f>
-        <v>0.73976336224611194</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="39">
-        <v>78.986989106511018</v>
-      </c>
-      <c r="B6" s="39">
-        <v>3.3362122605150493</v>
-      </c>
-      <c r="C6" s="39">
-        <v>16.720066122456561</v>
-      </c>
-      <c r="D6" s="39">
-        <v>0</v>
-      </c>
-      <c r="E6" s="39">
-        <v>0</v>
-      </c>
-      <c r="F6" s="39">
-        <v>0.66048161665691552</v>
-      </c>
-      <c r="G6" s="39">
-        <v>0.29625089386045561</v>
-      </c>
-      <c r="H6" s="39">
-        <f>SUM(F6:G6)</f>
-        <v>0.95673251051737118</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="39">
-        <v>85.880422588444205</v>
-      </c>
-      <c r="B7" s="39">
-        <v>1.3624337830784645</v>
-      </c>
-      <c r="C7" s="39">
-        <v>12.645557242016475</v>
-      </c>
-      <c r="D7" s="39">
-        <v>0</v>
-      </c>
-      <c r="E7" s="39">
-        <v>0</v>
-      </c>
-      <c r="F7" s="39">
-        <v>0</v>
-      </c>
-      <c r="G7" s="39">
-        <v>0.11158638646085177</v>
-      </c>
-      <c r="H7" s="39">
-        <f>SUM(F7:G7)</f>
-        <v>0.11158638646085177</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="39">
-        <v>82.821667041788587</v>
-      </c>
-      <c r="B8" s="39">
-        <v>3.8860754745292221</v>
-      </c>
-      <c r="C8" s="39">
-        <v>13.160589691649784</v>
-      </c>
-      <c r="D8" s="39">
-        <v>0</v>
-      </c>
-      <c r="E8" s="39">
-        <v>0</v>
-      </c>
-      <c r="F8" s="39">
-        <v>0</v>
-      </c>
-      <c r="G8" s="39">
-        <v>0.13166779203241052</v>
-      </c>
-      <c r="H8" s="39">
-        <f t="shared" ref="H8:H69" si="0">SUM(F8:G8)</f>
-        <v>0.13166779203241052</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="39">
-        <v>88.015355458272026</v>
-      </c>
-      <c r="B9" s="39">
-        <v>1.5512888049263409</v>
-      </c>
-      <c r="C9" s="39">
-        <v>10.318310899590077</v>
-      </c>
-      <c r="D9" s="39">
-        <v>0</v>
-      </c>
-      <c r="E9" s="39">
-        <v>0</v>
-      </c>
-      <c r="F9" s="39">
-        <v>0</v>
-      </c>
-      <c r="G9" s="39">
-        <v>0.11504483721155535</v>
-      </c>
-      <c r="H9" s="39">
-        <f t="shared" si="0"/>
-        <v>0.11504483721155535</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="39">
-        <v>84.397790197875395</v>
-      </c>
-      <c r="B10" s="39">
-        <v>1.6891906427615642</v>
-      </c>
-      <c r="C10" s="39">
-        <v>13.767161892960559</v>
-      </c>
-      <c r="D10" s="39">
-        <v>0</v>
-      </c>
-      <c r="E10" s="39">
-        <v>0</v>
-      </c>
-      <c r="F10" s="39">
-        <v>0</v>
-      </c>
-      <c r="G10" s="39">
-        <v>0.14585726640248861</v>
-      </c>
-      <c r="H10" s="39">
-        <f t="shared" si="0"/>
-        <v>0.14585726640248861</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="39">
-        <v>87.320112103753502</v>
-      </c>
-      <c r="B11" s="39">
-        <v>0.63572033236626047</v>
-      </c>
-      <c r="C11" s="39">
-        <v>11.908147247129602</v>
-      </c>
-      <c r="D11" s="39">
-        <v>0</v>
-      </c>
-      <c r="E11" s="39">
-        <v>0</v>
-      </c>
-      <c r="F11" s="39">
-        <v>0</v>
-      </c>
-      <c r="G11" s="39">
-        <v>0.13602031675063489</v>
-      </c>
-      <c r="H11" s="39">
-        <f t="shared" si="0"/>
-        <v>0.13602031675063489</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="39">
-        <v>83.924707717737519</v>
-      </c>
-      <c r="B12" s="39">
-        <v>2.0192780929917262</v>
-      </c>
-      <c r="C12" s="39">
-        <v>13.945276588631868</v>
-      </c>
-      <c r="D12" s="39">
-        <v>0</v>
-      </c>
-      <c r="E12" s="39">
-        <v>0</v>
-      </c>
-      <c r="F12" s="39">
-        <v>0</v>
-      </c>
-      <c r="G12" s="39">
-        <v>0.11073760063888864</v>
-      </c>
-      <c r="H12" s="39">
-        <f t="shared" si="0"/>
-        <v>0.11073760063888864</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="39">
-        <v>87.061623246492985</v>
-      </c>
-      <c r="B13" s="39">
-        <v>1.7607796237636566</v>
-      </c>
-      <c r="C13" s="39">
-        <v>11.050730493244554</v>
-      </c>
-      <c r="D13" s="39">
-        <v>0</v>
-      </c>
-      <c r="E13" s="39">
-        <v>0</v>
-      </c>
-      <c r="F13" s="39">
-        <v>0</v>
-      </c>
-      <c r="G13" s="39">
-        <v>0.12686663649880406</v>
-      </c>
-      <c r="H13" s="39">
-        <f t="shared" si="0"/>
-        <v>0.12686663649880406</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="39">
-        <v>88.701638632176511</v>
-      </c>
-      <c r="B14" s="39">
-        <v>1.2332804098078278</v>
-      </c>
-      <c r="C14" s="39">
-        <v>9.7069110135853691</v>
-      </c>
-      <c r="D14" s="39">
-        <v>0</v>
-      </c>
-      <c r="E14" s="39">
-        <v>0</v>
-      </c>
-      <c r="F14" s="39">
-        <v>0</v>
-      </c>
-      <c r="G14" s="39">
-        <v>0.3581699444302982</v>
-      </c>
-      <c r="H14" s="39">
-        <f t="shared" si="0"/>
-        <v>0.3581699444302982</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="39">
-        <v>92.258589881634663</v>
-      </c>
-      <c r="B15" s="39">
-        <v>0.61401782234006019</v>
-      </c>
-      <c r="C15" s="39">
-        <v>6.6627301602003755</v>
-      </c>
-      <c r="D15" s="39">
-        <v>0</v>
-      </c>
-      <c r="E15" s="39">
-        <v>0</v>
-      </c>
-      <c r="F15" s="39">
-        <v>0</v>
-      </c>
-      <c r="G15" s="39">
-        <v>0.46466213582491039</v>
-      </c>
-      <c r="H15" s="39">
-        <f t="shared" si="0"/>
-        <v>0.46466213582491039</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="39">
-        <v>89.192010722848352</v>
-      </c>
-      <c r="B16" s="39">
-        <v>1.0279209378716656</v>
-      </c>
-      <c r="C16" s="39">
-        <v>9.5467331181212369</v>
-      </c>
-      <c r="D16" s="39">
-        <v>0</v>
-      </c>
-      <c r="E16" s="39">
-        <v>0</v>
-      </c>
-      <c r="F16" s="39">
-        <v>0</v>
-      </c>
-      <c r="G16" s="39">
-        <v>0.23333522115874722</v>
-      </c>
-      <c r="H16" s="39">
-        <f t="shared" si="0"/>
-        <v>0.23333522115874722</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="39">
-        <v>93.506417804306523</v>
-      </c>
-      <c r="B17" s="39">
-        <v>0.9964792426874336</v>
-      </c>
-      <c r="C17" s="39">
-        <v>5.3537078704081518</v>
-      </c>
-      <c r="D17" s="39">
-        <v>0</v>
-      </c>
-      <c r="E17" s="39">
-        <v>0</v>
-      </c>
-      <c r="F17" s="39">
-        <v>0</v>
-      </c>
-      <c r="G17" s="39">
-        <v>0.14339508259789921</v>
-      </c>
-      <c r="H17" s="39">
-        <f t="shared" si="0"/>
-        <v>0.14339508259789921</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="39">
-        <v>89.125559910152973</v>
-      </c>
-      <c r="B18" s="39">
-        <v>1.342664080048247</v>
-      </c>
-      <c r="C18" s="39">
-        <v>9.4944331067241503</v>
-      </c>
-      <c r="D18" s="39">
-        <v>0</v>
-      </c>
-      <c r="E18" s="39">
-        <v>0</v>
-      </c>
-      <c r="F18" s="39">
-        <v>0</v>
-      </c>
-      <c r="G18" s="39">
-        <v>3.7342903074627926E-2</v>
-      </c>
-      <c r="H18" s="39">
-        <f t="shared" si="0"/>
-        <v>3.7342903074627926E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="39">
-        <v>93.536226553880098</v>
-      </c>
-      <c r="B19" s="39">
-        <v>0.82444526173838417</v>
-      </c>
-      <c r="C19" s="39">
-        <v>5.5890646070859384</v>
-      </c>
-      <c r="D19" s="39">
-        <v>0</v>
-      </c>
-      <c r="E19" s="39">
-        <v>0</v>
-      </c>
-      <c r="F19" s="39">
-        <v>0</v>
-      </c>
-      <c r="G19" s="39">
-        <v>5.0263577295574353E-2</v>
-      </c>
-      <c r="H19" s="39">
-        <f t="shared" si="0"/>
-        <v>5.0263577295574353E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="39">
-        <v>90.486072417287843</v>
-      </c>
-      <c r="B20" s="39">
-        <v>1.1573779554159409</v>
-      </c>
-      <c r="C20" s="39">
-        <v>8.2216391946614955</v>
-      </c>
-      <c r="D20" s="39">
-        <v>0</v>
-      </c>
-      <c r="E20" s="39">
-        <v>0</v>
-      </c>
-      <c r="F20" s="39">
-        <v>0</v>
-      </c>
-      <c r="G20" s="39">
-        <v>0.13491043263472396</v>
-      </c>
-      <c r="H20" s="39">
-        <f t="shared" si="0"/>
-        <v>0.13491043263472396</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="39">
-        <v>92.724213967988447</v>
-      </c>
-      <c r="B21" s="39">
-        <v>1.0100242050970105</v>
-      </c>
-      <c r="C21" s="39">
-        <v>6.2236246815952549</v>
-      </c>
-      <c r="D21" s="39">
-        <v>0</v>
-      </c>
-      <c r="E21" s="39">
-        <v>0</v>
-      </c>
-      <c r="F21" s="39">
-        <v>0</v>
-      </c>
-      <c r="G21" s="39">
-        <v>4.2137145319291844E-2</v>
-      </c>
-      <c r="H21" s="39">
-        <f t="shared" si="0"/>
-        <v>4.2137145319291844E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="39">
-        <v>90.18292395551795</v>
-      </c>
-      <c r="B22" s="39">
-        <v>1.8896882690562011</v>
-      </c>
-      <c r="C22" s="39">
-        <v>7.5720722843671426</v>
-      </c>
-      <c r="D22" s="39">
-        <v>0</v>
-      </c>
-      <c r="E22" s="39">
-        <v>0</v>
-      </c>
-      <c r="F22" s="39">
-        <v>0</v>
-      </c>
-      <c r="G22" s="39">
-        <v>0.35531549105871313</v>
-      </c>
-      <c r="H22" s="39">
-        <f t="shared" si="0"/>
-        <v>0.35531549105871313</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="39">
-        <v>92.395407526386876</v>
-      </c>
-      <c r="B23" s="39">
-        <v>1.4341704340711732</v>
-      </c>
-      <c r="C23" s="39">
-        <v>6.1316200290563891</v>
-      </c>
-      <c r="D23" s="39">
-        <v>0</v>
-      </c>
-      <c r="E23" s="39">
-        <v>0</v>
-      </c>
-      <c r="F23" s="39">
-        <v>0</v>
-      </c>
-      <c r="G23" s="39">
-        <v>3.880201048556655E-2</v>
-      </c>
-      <c r="H23" s="39">
-        <f t="shared" si="0"/>
-        <v>3.880201048556655E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="39">
-        <v>91.950201130403784</v>
-      </c>
-      <c r="B24" s="39">
-        <v>1.7495799175110749</v>
-      </c>
-      <c r="C24" s="39">
-        <v>6.2742502164061316</v>
-      </c>
-      <c r="D24" s="39">
-        <v>0</v>
-      </c>
-      <c r="E24" s="39">
-        <v>0</v>
-      </c>
-      <c r="F24" s="39">
-        <v>0</v>
-      </c>
-      <c r="G24" s="39">
-        <v>2.5968735679006059E-2</v>
-      </c>
-      <c r="H24" s="39">
-        <f t="shared" si="0"/>
-        <v>2.5968735679006059E-2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="39">
-        <v>93.253031680867949</v>
-      </c>
-      <c r="B25" s="39">
-        <v>1.3890276018313612</v>
-      </c>
-      <c r="C25" s="39">
-        <v>5.2283682276691144</v>
-      </c>
-      <c r="D25" s="39">
-        <v>0</v>
-      </c>
-      <c r="E25" s="39">
-        <v>0</v>
-      </c>
-      <c r="F25" s="39">
-        <v>0</v>
-      </c>
-      <c r="G25" s="39">
-        <v>0.12957248963157258</v>
-      </c>
-      <c r="H25" s="39">
-        <f t="shared" si="0"/>
-        <v>0.12957248963157258</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="39">
-        <v>91.561704138193306</v>
-      </c>
-      <c r="B26" s="39">
-        <v>1.9582761945369547</v>
-      </c>
-      <c r="C26" s="39">
-        <v>6.4245134079306725</v>
-      </c>
-      <c r="D26" s="39">
-        <v>0</v>
-      </c>
-      <c r="E26" s="39">
-        <v>0</v>
-      </c>
-      <c r="F26" s="39">
-        <v>0</v>
-      </c>
-      <c r="G26" s="39">
-        <v>5.5506259339072182E-2</v>
-      </c>
-      <c r="H26" s="39">
-        <f t="shared" si="0"/>
-        <v>5.5506259339072182E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="39">
-        <v>93.022948936384907</v>
-      </c>
-      <c r="B27" s="39">
-        <v>1.9886749541060085</v>
-      </c>
-      <c r="C27" s="39">
-        <v>4.9472364636981441</v>
-      </c>
-      <c r="D27" s="39">
-        <v>0</v>
-      </c>
-      <c r="E27" s="39">
-        <v>0</v>
-      </c>
-      <c r="F27" s="39">
-        <v>0</v>
-      </c>
-      <c r="G27" s="39">
-        <v>4.1139645810936161E-2</v>
-      </c>
-      <c r="H27" s="39">
-        <f t="shared" si="0"/>
-        <v>4.1139645810936161E-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="39">
-        <v>92.708444576117614</v>
-      </c>
-      <c r="B28" s="39">
-        <v>1.6780292199627258</v>
-      </c>
-      <c r="C28" s="39">
-        <v>5.5325701647713768</v>
-      </c>
-      <c r="D28" s="39">
-        <v>0</v>
-      </c>
-      <c r="E28" s="39">
-        <v>0</v>
-      </c>
-      <c r="F28" s="39">
-        <v>0</v>
-      </c>
-      <c r="G28" s="39">
-        <v>8.0956039148273568E-2</v>
-      </c>
-      <c r="H28" s="39">
-        <f t="shared" si="0"/>
-        <v>8.0956039148273568E-2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="39">
-        <v>94.765193641286217</v>
-      </c>
-      <c r="B29" s="39">
-        <v>1.1724194014239526</v>
-      </c>
-      <c r="C29" s="39">
-        <v>3.7901029968060613</v>
-      </c>
-      <c r="D29" s="39">
-        <v>0</v>
-      </c>
-      <c r="E29" s="39">
-        <v>0</v>
-      </c>
-      <c r="F29" s="39">
-        <v>0</v>
-      </c>
-      <c r="G29" s="39">
-        <v>0.27228396048377373</v>
-      </c>
-      <c r="H29" s="39">
-        <f t="shared" si="0"/>
-        <v>0.27228396048377373</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="39">
-        <v>93.559243493540464</v>
-      </c>
-      <c r="B30" s="39">
-        <v>1.3989585605879955</v>
-      </c>
-      <c r="C30" s="39">
-        <v>4.8329350563253328</v>
-      </c>
-      <c r="D30" s="39">
-        <v>0</v>
-      </c>
-      <c r="E30" s="39">
-        <v>0</v>
-      </c>
-      <c r="F30" s="39">
-        <v>0</v>
-      </c>
-      <c r="G30" s="39">
-        <v>0.20886288954620097</v>
-      </c>
-      <c r="H30" s="39">
-        <f t="shared" si="0"/>
-        <v>0.20886288954620097</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="39">
-        <v>96.214142011453987</v>
-      </c>
-      <c r="B31" s="39">
-        <v>0.80216481658835703</v>
-      </c>
-      <c r="C31" s="39">
-        <v>2.9406282338876069</v>
-      </c>
-      <c r="D31" s="39">
-        <v>0</v>
-      </c>
-      <c r="E31" s="39">
-        <v>0</v>
-      </c>
-      <c r="F31" s="39">
-        <v>0</v>
-      </c>
-      <c r="G31" s="39">
-        <v>4.3064938070048013E-2</v>
-      </c>
-      <c r="H31" s="39">
-        <f t="shared" si="0"/>
-        <v>4.3064938070048013E-2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="39">
-        <v>94.033945929070185</v>
-      </c>
-      <c r="B32" s="39">
-        <v>0.99784460761652027</v>
-      </c>
-      <c r="C32" s="39">
-        <v>4.8743488293437558</v>
-      </c>
-      <c r="D32" s="39">
-        <v>0</v>
-      </c>
-      <c r="E32" s="39">
-        <v>0</v>
-      </c>
-      <c r="F32" s="39">
-        <v>0</v>
-      </c>
-      <c r="G32" s="39">
-        <v>9.3860633969544319E-2</v>
-      </c>
-      <c r="H32" s="39">
-        <f t="shared" si="0"/>
-        <v>9.3860633969544319E-2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="39">
-        <v>95.944825479485928</v>
-      </c>
-      <c r="B33" s="39">
-        <v>0.83569106341505983</v>
-      </c>
-      <c r="C33" s="39">
-        <v>3.1965728665876312</v>
-      </c>
-      <c r="D33" s="39">
-        <v>0</v>
-      </c>
-      <c r="E33" s="39">
-        <v>0</v>
-      </c>
-      <c r="F33" s="39">
-        <v>0</v>
-      </c>
-      <c r="G33" s="39">
-        <v>2.2910590511378927E-2</v>
-      </c>
-      <c r="H33" s="39">
-        <f t="shared" si="0"/>
-        <v>2.2910590511378927E-2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="39">
-        <v>94.877853345492383</v>
-      </c>
-      <c r="B34" s="39">
-        <v>1.100560184598582</v>
-      </c>
-      <c r="C34" s="39">
-        <v>3.9723316278546839</v>
-      </c>
-      <c r="D34" s="39">
-        <v>0</v>
-      </c>
-      <c r="E34" s="39">
-        <v>0</v>
-      </c>
-      <c r="F34" s="39">
-        <v>0</v>
-      </c>
-      <c r="G34" s="39">
-        <v>4.9254842054355215E-2</v>
-      </c>
-      <c r="H34" s="39">
-        <f t="shared" si="0"/>
-        <v>4.9254842054355215E-2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="39">
-        <v>96.196812065345327</v>
-      </c>
-      <c r="B35" s="39">
-        <v>0.59800721747715979</v>
-      </c>
-      <c r="C35" s="39">
-        <v>3.0598826405446307</v>
-      </c>
-      <c r="D35" s="39">
-        <v>0</v>
-      </c>
-      <c r="E35" s="39">
-        <v>0</v>
-      </c>
-      <c r="F35" s="39">
-        <v>0</v>
-      </c>
-      <c r="G35" s="39">
-        <v>0.14529807663287875</v>
-      </c>
-      <c r="H35" s="39">
-        <f t="shared" si="0"/>
-        <v>0.14529807663287875</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="39">
-        <v>94.758040276525406</v>
-      </c>
-      <c r="B36" s="39">
-        <v>1.0352300950753801</v>
-      </c>
-      <c r="C36" s="39">
-        <v>4.1138689826459744</v>
-      </c>
-      <c r="D36" s="39">
-        <v>0</v>
-      </c>
-      <c r="E36" s="39">
-        <v>0</v>
-      </c>
-      <c r="F36" s="39">
-        <v>0</v>
-      </c>
-      <c r="G36" s="39">
-        <v>9.2860645753246956E-2</v>
-      </c>
-      <c r="H36" s="39">
-        <f t="shared" si="0"/>
-        <v>9.2860645753246956E-2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="39">
-        <v>95.384838340362009</v>
-      </c>
-      <c r="B37" s="39">
-        <v>1.0408243119864353</v>
-      </c>
-      <c r="C37" s="39">
-        <v>3.5120212164688489</v>
-      </c>
-      <c r="D37" s="39">
-        <v>0</v>
-      </c>
-      <c r="E37" s="39">
-        <v>0</v>
-      </c>
-      <c r="F37" s="39">
-        <v>0</v>
-      </c>
-      <c r="G37" s="39">
-        <v>6.2316131182702197E-2</v>
-      </c>
-      <c r="H37" s="39">
-        <f t="shared" si="0"/>
-        <v>6.2316131182702197E-2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="39">
-        <v>94.597549762679861</v>
-      </c>
-      <c r="B38" s="39">
-        <v>1.1524315996123355</v>
-      </c>
-      <c r="C38" s="39">
-        <v>3.9073954424591837</v>
-      </c>
-      <c r="D38" s="39">
-        <v>0</v>
-      </c>
-      <c r="E38" s="39">
-        <v>0</v>
-      </c>
-      <c r="F38" s="39">
-        <v>0</v>
-      </c>
-      <c r="G38" s="39">
-        <v>0.342623195248627</v>
-      </c>
-      <c r="H38" s="39">
-        <f t="shared" si="0"/>
-        <v>0.342623195248627</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="44">
-        <v>94.041215088995315</v>
-      </c>
-      <c r="B39" s="44">
-        <v>1.7931084146473195</v>
-      </c>
-      <c r="C39" s="44">
-        <v>3.6915949543321456</v>
-      </c>
-      <c r="D39" s="44">
-        <v>0</v>
-      </c>
-      <c r="E39" s="44">
-        <v>0</v>
-      </c>
-      <c r="F39" s="44">
-        <v>0</v>
-      </c>
-      <c r="G39" s="44">
-        <v>0.47408154202522834</v>
-      </c>
-      <c r="H39" s="39">
-        <f t="shared" si="0"/>
-        <v>0.47408154202522834</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="39">
-        <v>94.935933952879353</v>
-      </c>
-      <c r="B40" s="39">
-        <v>1.4921819866851453</v>
-      </c>
-      <c r="C40" s="39">
-        <v>2.8732651435924033</v>
-      </c>
-      <c r="D40" s="39">
-        <v>0.52176771842114966</v>
-      </c>
-      <c r="E40" s="39">
-        <v>0</v>
-      </c>
-      <c r="F40" s="39">
-        <v>0.17685119842194316</v>
-      </c>
-      <c r="G40" s="39">
-        <v>0</v>
-      </c>
-      <c r="H40" s="39">
-        <f t="shared" si="0"/>
-        <v>0.17685119842194316</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8">
-      <c r="A41" s="39">
-        <v>96.809272737692709</v>
-      </c>
-      <c r="B41" s="39">
-        <v>0.6850576782951131</v>
-      </c>
-      <c r="C41" s="39">
-        <v>2.037161360045193</v>
-      </c>
-      <c r="D41" s="39">
-        <v>0.36903465609981745</v>
-      </c>
-      <c r="E41" s="39">
-        <v>0</v>
-      </c>
-      <c r="F41" s="39">
-        <v>9.9473567867172083E-2</v>
-      </c>
-      <c r="G41" s="39">
-        <v>0</v>
-      </c>
-      <c r="H41" s="39">
-        <f t="shared" si="0"/>
-        <v>9.9473567867172083E-2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8">
-      <c r="A42" s="39">
-        <v>94.987430117864903</v>
-      </c>
-      <c r="B42" s="39">
-        <v>1.4290496029626465</v>
-      </c>
-      <c r="C42" s="39">
-        <v>2.7797599971513014</v>
-      </c>
-      <c r="D42" s="39">
-        <v>0.55891464587116757</v>
-      </c>
-      <c r="E42" s="39">
-        <v>0</v>
-      </c>
-      <c r="F42" s="39">
-        <v>0.244845636149984</v>
-      </c>
-      <c r="G42" s="39">
-        <v>0</v>
-      </c>
-      <c r="H42" s="39">
-        <f t="shared" si="0"/>
-        <v>0.244845636149984</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8">
-      <c r="A43" s="39">
-        <v>97.259026394763836</v>
-      </c>
-      <c r="B43" s="39">
-        <v>0.88357445781281718</v>
-      </c>
-      <c r="C43" s="39">
-        <v>1.6335566272199089</v>
-      </c>
-      <c r="D43" s="39">
-        <v>0.16431577157090266</v>
-      </c>
-      <c r="E43" s="39">
-        <v>0</v>
-      </c>
-      <c r="F43" s="39">
-        <v>5.9526748632530685E-2</v>
-      </c>
-      <c r="G43" s="39">
-        <v>0</v>
-      </c>
-      <c r="H43" s="39">
-        <f t="shared" si="0"/>
-        <v>5.9526748632530685E-2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8">
-      <c r="A44" s="39">
-        <v>97.007958852539971</v>
-      </c>
-      <c r="B44" s="39">
-        <v>0.71905442931628261</v>
-      </c>
-      <c r="C44" s="39">
-        <v>1.7730091645449471</v>
-      </c>
-      <c r="D44" s="39">
-        <v>0.49997755359879942</v>
-      </c>
-      <c r="E44" s="39">
-        <v>0</v>
-      </c>
-      <c r="F44" s="39">
-        <v>0</v>
-      </c>
-      <c r="G44" s="39">
-        <v>0</v>
-      </c>
-      <c r="H44" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8">
-      <c r="A45" s="39">
-        <v>96.218608485455064</v>
-      </c>
-      <c r="B45" s="39">
-        <v>1.8965043463885098</v>
-      </c>
-      <c r="C45" s="39">
-        <v>0.99550281158053944</v>
-      </c>
-      <c r="D45" s="39">
-        <v>0.88938435657588133</v>
-      </c>
-      <c r="E45" s="39">
-        <v>0</v>
-      </c>
-      <c r="F45" s="39">
-        <v>0</v>
-      </c>
-      <c r="G45" s="39">
-        <v>0</v>
-      </c>
-      <c r="H45" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8">
-      <c r="A46" s="39">
-        <v>96.084994526239512</v>
-      </c>
-      <c r="B46" s="39">
-        <v>0.87518751276315121</v>
-      </c>
-      <c r="C46" s="39">
-        <v>2.0351948213465909</v>
-      </c>
-      <c r="D46" s="39">
-        <v>0.91863980506349718</v>
-      </c>
-      <c r="E46" s="39">
-        <v>0</v>
-      </c>
-      <c r="F46" s="39">
-        <v>8.598333458725696E-2</v>
-      </c>
-      <c r="G46" s="39">
-        <v>0</v>
-      </c>
-      <c r="H46" s="39">
-        <f t="shared" si="0"/>
-        <v>8.598333458725696E-2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8">
-      <c r="A47" s="39">
-        <v>95.877359183842998</v>
-      </c>
-      <c r="B47" s="39">
-        <v>1.9084347512133404</v>
-      </c>
-      <c r="C47" s="39">
-        <v>1.6378095654980047</v>
-      </c>
-      <c r="D47" s="39">
-        <v>0.43325590534828212</v>
-      </c>
-      <c r="E47" s="39">
-        <v>0</v>
-      </c>
-      <c r="F47" s="39">
-        <v>0.14314059409736754</v>
-      </c>
-      <c r="G47" s="39">
-        <v>0</v>
-      </c>
-      <c r="H47" s="39">
-        <f t="shared" si="0"/>
-        <v>0.14314059409736754</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8">
-      <c r="A48" s="39">
-        <v>95.461322813366365</v>
-      </c>
-      <c r="B48" s="39">
-        <v>1.7984121683712428</v>
-      </c>
-      <c r="C48" s="39">
-        <v>1.7814570050710175</v>
-      </c>
-      <c r="D48" s="39">
-        <v>0.66189851234620634</v>
-      </c>
-      <c r="E48" s="39">
-        <v>0</v>
-      </c>
-      <c r="F48" s="39">
-        <v>0.29690950084516959</v>
-      </c>
-      <c r="G48" s="39">
-        <v>0</v>
-      </c>
-      <c r="H48" s="39">
-        <f t="shared" si="0"/>
-        <v>0.29690950084516959</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8">
-      <c r="A49" s="39">
-        <v>95.974302108342243</v>
-      </c>
-      <c r="B49" s="39">
-        <v>1.5659652728944664</v>
-      </c>
-      <c r="C49" s="39">
-        <v>1.6127757134951379</v>
-      </c>
-      <c r="D49" s="39">
-        <v>0.84695690526815104</v>
-      </c>
-      <c r="E49" s="39">
-        <v>0</v>
-      </c>
-      <c r="F49" s="39">
-        <v>0</v>
-      </c>
-      <c r="G49" s="39">
-        <v>0</v>
-      </c>
-      <c r="H49" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8">
-      <c r="A50" s="39">
-        <v>95.243814525036214</v>
-      </c>
-      <c r="B50" s="39">
-        <v>1.6228728645974564</v>
-      </c>
-      <c r="C50" s="39">
-        <v>2.0314680458462577</v>
-      </c>
-      <c r="D50" s="39">
-        <v>1.1018445645200758</v>
-      </c>
-      <c r="E50" s="39">
-        <v>0</v>
-      </c>
-      <c r="F50" s="39">
-        <v>0</v>
-      </c>
-      <c r="G50" s="39">
-        <v>0</v>
-      </c>
-      <c r="H50" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8">
-      <c r="A51" s="39">
-        <v>97.230080089692152</v>
-      </c>
-      <c r="B51" s="39">
-        <v>0.76819665834453621</v>
-      </c>
-      <c r="C51" s="39">
-        <v>1.1878500355550481</v>
-      </c>
-      <c r="D51" s="39">
-        <v>0.81387321640826549</v>
-      </c>
-      <c r="E51" s="39">
-        <v>0</v>
-      </c>
-      <c r="F51" s="39">
-        <v>0</v>
-      </c>
-      <c r="G51" s="39">
-        <v>0</v>
-      </c>
-      <c r="H51" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8">
-      <c r="A52" s="39">
-        <v>94.977845604877658</v>
-      </c>
-      <c r="B52" s="39">
-        <v>1.7030500077411364</v>
-      </c>
-      <c r="C52" s="39">
-        <v>2.2709176564262492</v>
-      </c>
-      <c r="D52" s="39">
-        <v>1.0481867309549613</v>
-      </c>
-      <c r="E52" s="39">
-        <v>0</v>
-      </c>
-      <c r="F52" s="39">
-        <v>0</v>
-      </c>
-      <c r="G52" s="39">
-        <v>0</v>
-      </c>
-      <c r="H52" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8">
-      <c r="A53" s="39">
-        <v>96.681960316791304</v>
-      </c>
-      <c r="B53" s="39">
-        <v>0.95856263773316797</v>
-      </c>
-      <c r="C53" s="39">
-        <v>1.5213368496686375</v>
-      </c>
-      <c r="D53" s="39">
-        <v>0.83814019580689059</v>
-      </c>
-      <c r="E53" s="39">
-        <v>0</v>
-      </c>
-      <c r="F53" s="39">
-        <v>0</v>
-      </c>
-      <c r="G53" s="39">
-        <v>0</v>
-      </c>
-      <c r="H53" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8">
-      <c r="A54" s="39">
-        <v>96.183551636637787</v>
-      </c>
-      <c r="B54" s="39">
-        <v>1.1474974932215811</v>
-      </c>
-      <c r="C54" s="39">
-        <v>1.6085348873111298</v>
-      </c>
-      <c r="D54" s="39">
-        <v>1.0604159828295046</v>
-      </c>
-      <c r="E54" s="39">
-        <v>0</v>
-      </c>
-      <c r="F54" s="39">
-        <v>0</v>
-      </c>
-      <c r="G54" s="39">
-        <v>0</v>
-      </c>
-      <c r="H54" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8">
-      <c r="A55" s="39">
-        <v>96.446411228505767</v>
-      </c>
-      <c r="B55" s="39">
-        <v>0.98912947509518057</v>
-      </c>
-      <c r="C55" s="39">
-        <v>1.3990148837632403</v>
-      </c>
-      <c r="D55" s="39">
-        <v>1.1654444126358146</v>
-      </c>
-      <c r="E55" s="39">
-        <v>0</v>
-      </c>
-      <c r="F55" s="39">
-        <v>0</v>
-      </c>
-      <c r="G55" s="39">
-        <v>0</v>
-      </c>
-      <c r="H55" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8">
-      <c r="A56" s="39">
-        <v>97.13312487383476</v>
-      </c>
-      <c r="B56" s="39">
-        <v>0.74783396855995832</v>
-      </c>
-      <c r="C56" s="39">
-        <v>0.94194460895128118</v>
-      </c>
-      <c r="D56" s="39">
-        <v>1.1770965486539924</v>
-      </c>
-      <c r="E56" s="39">
-        <v>0</v>
-      </c>
-      <c r="F56" s="39">
-        <v>0</v>
-      </c>
-      <c r="G56" s="39">
-        <v>0</v>
-      </c>
-      <c r="H56" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8">
-      <c r="A57" s="39">
-        <v>97.67827034529121</v>
-      </c>
-      <c r="B57" s="39">
-        <v>0.88260966208193958</v>
-      </c>
-      <c r="C57" s="39">
-        <v>0.76631987552384617</v>
-      </c>
-      <c r="D57" s="39">
-        <v>0.62834434788265847</v>
-      </c>
-      <c r="E57" s="39">
-        <v>0</v>
-      </c>
-      <c r="F57" s="39">
-        <v>4.4455769220343395E-2</v>
-      </c>
-      <c r="G57" s="39">
-        <v>0</v>
-      </c>
-      <c r="H57" s="39">
-        <f t="shared" si="0"/>
-        <v>4.4455769220343395E-2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8">
-      <c r="A58" s="39">
-        <v>97.82252661356361</v>
-      </c>
-      <c r="B58" s="39">
-        <v>0.51459093277748824</v>
-      </c>
-      <c r="C58" s="39">
-        <v>0.4502504493199051</v>
-      </c>
-      <c r="D58" s="39">
-        <v>1.1892354648998733</v>
-      </c>
-      <c r="E58" s="39">
-        <v>0</v>
-      </c>
-      <c r="F58" s="39">
-        <v>2.339653943912114E-2</v>
-      </c>
-      <c r="G58" s="39">
-        <v>0</v>
-      </c>
-      <c r="H58" s="39">
-        <f t="shared" si="0"/>
-        <v>2.339653943912114E-2</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8">
-      <c r="A59" s="39">
-        <v>96.425518296559005</v>
-      </c>
-      <c r="B59" s="39">
-        <v>0.90112799919334685</v>
-      </c>
-      <c r="C59" s="39">
-        <v>1.0578554424974682</v>
-      </c>
-      <c r="D59" s="39">
-        <v>1.5120362292473137</v>
-      </c>
-      <c r="E59" s="39">
-        <v>0</v>
-      </c>
-      <c r="F59" s="39">
-        <v>0.10346203250286055</v>
-      </c>
-      <c r="G59" s="39">
-        <v>0</v>
-      </c>
-      <c r="H59" s="39">
-        <f t="shared" si="0"/>
-        <v>0.10346203250286055</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8">
-      <c r="A60" s="39">
-        <v>96.495248234316577</v>
-      </c>
-      <c r="B60" s="39">
-        <v>0.60189031990029074</v>
-      </c>
-      <c r="C60" s="39">
-        <v>0.95009347735770655</v>
-      </c>
-      <c r="D60" s="39">
-        <v>1.5701599501454093</v>
-      </c>
-      <c r="E60" s="39">
-        <v>0</v>
-      </c>
-      <c r="F60" s="39">
-        <v>0.38260801828001662</v>
-      </c>
-      <c r="G60" s="39">
-        <v>0</v>
-      </c>
-      <c r="H60" s="39">
-        <f t="shared" si="0"/>
-        <v>0.38260801828001662</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8">
-      <c r="A61" s="39">
-        <v>95.183332103608009</v>
-      </c>
-      <c r="B61" s="39">
-        <v>0.84731398078039033</v>
-      </c>
-      <c r="C61" s="39">
-        <v>1.3390711652012994</v>
-      </c>
-      <c r="D61" s="39">
-        <v>2.1598629620692886</v>
-      </c>
-      <c r="E61" s="39">
-        <v>0</v>
-      </c>
-      <c r="F61" s="39">
-        <v>0.47041978834100745</v>
-      </c>
-      <c r="G61" s="39">
-        <v>0</v>
-      </c>
-      <c r="H61" s="39">
-        <f t="shared" si="0"/>
-        <v>0.47041978834100745</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8">
-      <c r="A62" s="39">
-        <v>95.114494371305653</v>
-      </c>
-      <c r="B62" s="39">
-        <v>1.1070495948938319</v>
-      </c>
-      <c r="C62" s="39">
-        <v>1.4069802512354255</v>
-      </c>
-      <c r="D62" s="39">
-        <v>1.7774145900088418</v>
-      </c>
-      <c r="E62" s="39">
-        <v>0.47586763352520994</v>
-      </c>
-      <c r="F62" s="39">
-        <v>0.11819355903104481</v>
-      </c>
-      <c r="G62" s="39">
-        <v>0</v>
-      </c>
-      <c r="H62" s="39">
-        <f t="shared" si="0"/>
-        <v>0.11819355903104481</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8">
-      <c r="A63" s="39">
-        <v>94.463625435724524</v>
-      </c>
-      <c r="B63" s="39">
-        <v>1.2952878428962629</v>
-      </c>
-      <c r="C63" s="39">
-        <v>1.6505110355866788</v>
-      </c>
-      <c r="D63" s="39">
-        <v>2.2818574581299607</v>
-      </c>
-      <c r="E63" s="39">
-        <v>0.15487814245882547</v>
-      </c>
-      <c r="F63" s="39">
-        <v>0.15384008520373949</v>
-      </c>
-      <c r="G63" s="39">
-        <v>0</v>
-      </c>
-      <c r="H63" s="39">
-        <f t="shared" si="0"/>
-        <v>0.15384008520373949</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8">
-      <c r="A64" s="39">
-        <v>95.121098792642385</v>
-      </c>
-      <c r="B64" s="39">
-        <v>1.1629323616387379</v>
-      </c>
-      <c r="C64" s="39">
-        <v>1.4565574002493229</v>
-      </c>
-      <c r="D64" s="39">
-        <v>1.8491239858183783</v>
-      </c>
-      <c r="E64" s="39">
-        <v>0.34863358524048088</v>
-      </c>
-      <c r="F64" s="39">
-        <v>6.165387441068864E-2</v>
-      </c>
-      <c r="G64" s="39">
-        <v>0</v>
-      </c>
-      <c r="H64" s="39">
-        <f t="shared" si="0"/>
-        <v>6.165387441068864E-2</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8">
-      <c r="A65" s="39">
-        <v>95.002930252080873</v>
-      </c>
-      <c r="B65" s="39">
-        <v>1.0099470178745378</v>
-      </c>
-      <c r="C65" s="39">
-        <v>1.9420839636015172</v>
-      </c>
-      <c r="D65" s="39">
-        <v>1.811212569989467</v>
-      </c>
-      <c r="E65" s="39">
-        <v>0.16868748465577457</v>
-      </c>
-      <c r="F65" s="39">
-        <v>6.5138711797828444E-2</v>
-      </c>
-      <c r="G65" s="39">
-        <v>0</v>
-      </c>
-      <c r="H65" s="39">
-        <f t="shared" si="0"/>
-        <v>6.5138711797828444E-2</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8">
-      <c r="A66" s="39">
-        <v>94.251085320711951</v>
-      </c>
-      <c r="B66" s="39">
-        <v>0.72867106166803441</v>
-      </c>
-      <c r="C66" s="39">
-        <v>1.8437435692733373</v>
-      </c>
-      <c r="D66" s="39">
-        <v>3.0082784371381748</v>
-      </c>
-      <c r="E66" s="39">
-        <v>0.14913087566972533</v>
-      </c>
-      <c r="F66" s="39">
-        <v>1.909073553876783E-2</v>
-      </c>
-      <c r="G66" s="39">
-        <v>0</v>
-      </c>
-      <c r="H66" s="39">
-        <f t="shared" si="0"/>
-        <v>1.909073553876783E-2</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8">
-      <c r="A67" s="39">
-        <v>93.585087551629286</v>
-      </c>
-      <c r="B67" s="39">
-        <v>1.2983154518029736</v>
-      </c>
-      <c r="C67" s="39">
-        <v>2.3845041511190153</v>
-      </c>
-      <c r="D67" s="39">
-        <v>2.5895669373135322</v>
-      </c>
-      <c r="E67" s="39">
-        <v>0.10305080238346533</v>
-      </c>
-      <c r="F67" s="39">
-        <v>3.9475105751730674E-2</v>
-      </c>
-      <c r="G67" s="39">
-        <v>0</v>
-      </c>
-      <c r="H67" s="39">
-        <f t="shared" si="0"/>
-        <v>3.9475105751730674E-2</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8">
-      <c r="A68" s="39">
-        <v>95.209272633463385</v>
-      </c>
-      <c r="B68" s="39">
-        <v>0.89685594462205009</v>
-      </c>
-      <c r="C68" s="39">
-        <v>1.4004394956418971</v>
-      </c>
-      <c r="D68" s="39">
-        <v>2.3988616588149609</v>
-      </c>
-      <c r="E68" s="39">
-        <v>4.7472525275996512E-2</v>
-      </c>
-      <c r="F68" s="39">
-        <v>4.7097742181712338E-2</v>
-      </c>
-      <c r="G68" s="39">
-        <v>0</v>
-      </c>
-      <c r="H68" s="39">
-        <f t="shared" si="0"/>
-        <v>4.7097742181712338E-2</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8">
-      <c r="A69" s="39">
-        <v>95.561133459667332</v>
-      </c>
-      <c r="B69" s="39">
-        <v>0.88563080185142096</v>
-      </c>
-      <c r="C69" s="39">
-        <v>0.92330935942758141</v>
-      </c>
-      <c r="D69" s="39">
-        <v>2.1340100697792108</v>
-      </c>
-      <c r="E69" s="39">
-        <v>0.44918750992756112</v>
-      </c>
-      <c r="F69" s="39">
-        <v>4.6728799346904999E-2</v>
-      </c>
-      <c r="G69" s="39">
-        <v>0</v>
-      </c>
-      <c r="H69" s="39">
-        <f t="shared" si="0"/>
-        <v>4.6728799346904999E-2</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>